--- a/historico_dados/03 - Mar 2026.xlsx
+++ b/historico_dados/03 - Mar 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JFMELO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F335650-1C94-4361-A851-9C1FD22E5A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DD2604-5AD0-42C3-A5BF-5BAA5DF7C36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="1" activeTab="5" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="2" activeTab="7" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
   </bookViews>
   <sheets>
     <sheet name="TURNOS" sheetId="16" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="243">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -1139,12 +1139,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1232,15 +1232,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="23" formatCode="h:mm\ AM/PM"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1582,6 +1573,15 @@
       </fill>
       <protection locked="0" hidden="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1606,14 +1606,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}" name="tblTurnos" displayName="tblTurnos" ref="A2:E5" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}" name="tblTurnos" displayName="tblTurnos" ref="A2:E5" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60" tableBorderDxfId="59">
   <autoFilter ref="A2:E5" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{66C8A751-944C-4ED0-9B93-7EF7890BAC2C}" name="ID_TURNO" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{CE79B6B8-84BE-42CD-8597-D513FB5454F3}" name="TURNO" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{72B36434-A91F-4B46-ABFB-CA8660948243}" name="HORARIO_INICIO" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{39895036-CC40-4170-867E-4FB900291AD1}" name="HORARIO_FIM" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{883890C6-E58B-43F9-93BF-FE0182EAC856}" name="DESCRICAO" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{66C8A751-944C-4ED0-9B93-7EF7890BAC2C}" name="ID_TURNO" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{CE79B6B8-84BE-42CD-8597-D513FB5454F3}" name="TURNO" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{72B36434-A91F-4B46-ABFB-CA8660948243}" name="HORARIO_INICIO" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{39895036-CC40-4170-867E-4FB900291AD1}" name="HORARIO_FIM" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{883890C6-E58B-43F9-93BF-FE0182EAC856}" name="DESCRICAO" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1669,35 +1669,35 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}" name="tblModalidades" displayName="tblModalidades" ref="A2:D4" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}" name="tblModalidades" displayName="tblModalidades" ref="A2:D4" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="A2:D4" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B42A8C1C-387F-4E3D-A54F-CF1D913A6676}" name="ID_MODALIDADE" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{409E0C8E-C00D-45B9-8113-E86B37049A97}" name="MODALIDADE" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{9B83D5E8-C0D6-41D3-A5EB-27263A3A1DDA}" name="TIPO" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{D7FE0EEE-44EA-4C6B-B889-B4C030F1B758}" name=" DESCRICAO" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{B42A8C1C-387F-4E3D-A54F-CF1D913A6676}" name="ID_MODALIDADE" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{409E0C8E-C00D-45B9-8113-E86B37049A97}" name="MODALIDADE" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{9B83D5E8-C0D6-41D3-A5EB-27263A3A1DDA}" name="TIPO" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{D7FE0EEE-44EA-4C6B-B889-B4C030F1B758}" name=" DESCRICAO" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}" name="tblCalendario" displayName="tblCalendario" ref="A1:G366" totalsRowShown="0" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}" name="tblCalendario" displayName="tblCalendario" ref="A1:G366" totalsRowShown="0" dataDxfId="47">
   <autoFilter ref="A1:G366" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F779E569-925E-439D-B1E1-8D86C934DF94}" name="DATA" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{9910EA8A-79F0-4CBA-B0EA-76C6A01D1DA2}" name="DIA_SEMANA" dataDxfId="48">
+    <tableColumn id="1" xr3:uid="{F779E569-925E-439D-B1E1-8D86C934DF94}" name="DATA" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{9910EA8A-79F0-4CBA-B0EA-76C6A01D1DA2}" name="DIA_SEMANA" dataDxfId="45">
       <calculatedColumnFormula>TEXT(A2,"dddd")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B5623804-AA40-4BA7-B2EB-75E1D43E1DDA}" name="MÊS" dataDxfId="47">
+    <tableColumn id="3" xr3:uid="{B5623804-AA40-4BA7-B2EB-75E1D43E1DDA}" name="MÊS" dataDxfId="44">
       <calculatedColumnFormula>TEXT(A2,"mmmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{353E7915-D743-4718-B4A3-CE0D53F4A516}" name="ANO" dataDxfId="46">
+    <tableColumn id="4" xr3:uid="{353E7915-D743-4718-B4A3-CE0D53F4A516}" name="ANO" dataDxfId="43">
       <calculatedColumnFormula>YEAR(A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{816AC587-9819-42DF-80FD-264F991CF8F3}" name="TIPO_DIA" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{7A6D793C-B684-4E23-A357-D584AE0AC6FD}" name="DESCRICAO" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{5B786348-03B6-441E-A7B1-194F3AA43107}" name="DIA_UTIL" dataDxfId="43">
+    <tableColumn id="5" xr3:uid="{816AC587-9819-42DF-80FD-264F991CF8F3}" name="TIPO_DIA" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{7A6D793C-B684-4E23-A357-D584AE0AC6FD}" name="DESCRICAO" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{5B786348-03B6-441E-A7B1-194F3AA43107}" name="DIA_UTIL" dataDxfId="40">
       <calculatedColumnFormula>IF(OR(E2="Feriado",E2="Recesso",B2="domingo",B2="sábado"),"NÃO","SIM")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1706,41 +1706,41 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}" name="tblInstrutores" displayName="tblInstrutores" ref="A1:I14" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}" name="tblInstrutores" displayName="tblInstrutores" ref="A1:I14" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
   <autoFilter ref="A1:I14" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G14">
     <sortCondition ref="B1:B14"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E0F79A67-2297-4B4A-A8E9-7102EE99B694}" name="ID" dataDxfId="37">
+    <tableColumn id="1" xr3:uid="{E0F79A67-2297-4B4A-A8E9-7102EE99B694}" name="ID" dataDxfId="34">
       <calculatedColumnFormula>IF(B2&lt;&gt;"",ROW()-1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{532A9770-E647-4D50-B202-8BBE5806648D}" name="NOME_COMPLETO" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{DD24D10E-34AA-4D8E-B5F7-9B0E7D84B23A}" name="NOME_PADRONIZADO" dataDxfId="35">
+    <tableColumn id="2" xr3:uid="{532A9770-E647-4D50-B202-8BBE5806648D}" name="NOME_COMPLETO" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{DD24D10E-34AA-4D8E-B5F7-9B0E7D84B23A}" name="NOME_PADRONIZADO" dataDxfId="32">
       <calculatedColumnFormula>UPPER(B2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0DC783F1-8A1B-443E-A9AF-DB40A28DED0F}" name="STATUS" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{8E33C3CA-EB70-43F9-B178-A5FD7FB25151}" name="TELEFONE" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{6BB804C3-6D00-4CBA-AADC-80AA2AA5F0B3}" name="EMAIL" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{066724F8-E631-4356-AF06-A44B57F600FB}" name="CARGA_HORARIA_SEMANAL" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{18D3697E-D2C6-4E06-9624-B784D6581D8D}" name="HABILITADO_EAD" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{0523A053-C6F6-4529-94E2-81C8ABD9D627}" name="OBSERVAÇÃO" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{0DC783F1-8A1B-443E-A9AF-DB40A28DED0F}" name="STATUS" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{8E33C3CA-EB70-43F9-B178-A5FD7FB25151}" name="TELEFONE" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{6BB804C3-6D00-4CBA-AADC-80AA2AA5F0B3}" name="EMAIL" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{066724F8-E631-4356-AF06-A44B57F600FB}" name="CARGA_HORARIA_SEMANAL" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{18D3697E-D2C6-4E06-9624-B784D6581D8D}" name="HABILITADO_EAD" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{0523A053-C6F6-4529-94E2-81C8ABD9D627}" name="OBSERVAÇÃO" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}" name="tblAmbientes" displayName="tblAmbientes" ref="A1:E17" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}" name="tblAmbientes" displayName="tblAmbientes" ref="A1:E17" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A1:E17" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4CC770AA-6DA6-4EFC-AAF1-5A329E637763}" name="ID" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{4CC770AA-6DA6-4EFC-AAF1-5A329E637763}" name="ID" dataDxfId="23">
       <calculatedColumnFormula>IF(B2&lt;&gt;"",ROW()-1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B3952270-EACA-4683-9C35-CB58270B3617}" name="NOME_AMBIENTE" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{1B401582-0E5F-494F-8433-828BC136B12C}" name="TIPO" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{81780B59-8350-421A-B267-D808DA35B87C}" name="CAPACIDADE" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{7A3E5A22-F966-4BA3-A1AA-3C3AF64EA9D1}" name="VIRTUAL" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{B3952270-EACA-4683-9C35-CB58270B3617}" name="NOME_AMBIENTE" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{1B401582-0E5F-494F-8433-828BC136B12C}" name="TIPO" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{81780B59-8350-421A-B267-D808DA35B87C}" name="CAPACIDADE" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{7A3E5A22-F966-4BA3-A1AA-3C3AF64EA9D1}" name="VIRTUAL" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1750,14 +1750,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{27B64AF7-6011-40DE-B8EB-AFCA2AA948F7}" name="tblDisciplinas" displayName="tblDisciplinas" ref="A2:G29" totalsRowShown="0">
   <autoFilter ref="A2:G29" xr:uid="{27B64AF7-6011-40DE-B8EB-AFCA2AA948F7}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EAB3743F-4C6C-47DC-9FAE-3B30927E6D25}" name="ID_DISCIPLINA" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{EAB3743F-4C6C-47DC-9FAE-3B30927E6D25}" name="ID_DISCIPLINA" dataDxfId="64">
       <calculatedColumnFormula>IF(E3&lt;&gt;"",ROW()-2,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{AB44C0DC-4B9E-4D40-B9CB-D5B9E3AB1664}" name="ID_TURMA" dataDxfId="20">
+    <tableColumn id="7" xr3:uid="{AB44C0DC-4B9E-4D40-B9CB-D5B9E3AB1664}" name="ID_TURMA" dataDxfId="63">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{71F544AA-7A31-4153-B640-2C9D09A01400}" name="TURMA"/>
-    <tableColumn id="10" xr3:uid="{6CF7FD1A-08A6-4FC7-8349-E61A732E9B9A}" name="NOME_TURMA" dataDxfId="19">
+    <tableColumn id="10" xr3:uid="{6CF7FD1A-08A6-4FC7-8349-E61A732E9B9A}" name="NOME_TURMA" dataDxfId="62">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{912B15BB-5B7F-4D54-B4D5-F1F5D64871C5}" name="NOME_DISCIPLINA"/>
@@ -2192,13 +2192,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="25" t="s">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B3" s="2">
         <f ca="1">TODAY()</f>
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="B15" s="4">
         <f>AVERAGEIFS(tblOcupacao[PERCENTUAL_OCUPACAO], tblOcupacao[ID_TURNO], 1)</f>
-        <v>0.77499999999999991</v>
+        <v>0.77976190476190477</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -3072,12 +3072,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
@@ -12610,15 +12610,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.6">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -15149,90 +15149,142 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" t="str">
+      <c r="B22" s="2">
+        <v>46111</v>
+      </c>
+      <c r="C22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v/>
-      </c>
-      <c r="E22" t="str">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>194</v>
+      </c>
+      <c r="E22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="40"/>
-      <c r="G22" t="str">
+        <v>2</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="G22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H22" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v/>
-      </c>
-      <c r="I22" t="str">
+        <v>Deilson dos Santos de Aquino</v>
+      </c>
+      <c r="I22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="K22" t="str">
+        <v>4</v>
+      </c>
+      <c r="J22" t="s">
+        <v>106</v>
+      </c>
+      <c r="K22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],['#VALOR!]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L22" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="M22" t="str">
+        <v>MANHÃ</v>
+      </c>
+      <c r="M22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[MODALIDADE]], tblModalidades[MODALIDADE], tblModalidades[ID_MODALIDADE],"")</f>
-        <v/>
-      </c>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="N22" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="32">
+        <v>0.375</v>
+      </c>
+      <c r="P22" s="32">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q22" s="33">
         <f>($P22-$O22)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>#VALUE!</v>
+        <v>0.23958333333333329</v>
+      </c>
+      <c r="R22">
+        <v>21</v>
+      </c>
+      <c r="S22" t="s">
+        <v>192</v>
+      </c>
+      <c r="T22" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" t="str">
+      <c r="B23" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v/>
-      </c>
-      <c r="E23" t="str">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>203</v>
+      </c>
+      <c r="E23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="40"/>
-      <c r="G23" t="str">
+        <v>11</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="G23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="H23" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v/>
-      </c>
-      <c r="I23" t="str">
+        <v>Raphael Barreto de Oliveira</v>
+      </c>
+      <c r="I23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="K23" t="str">
+        <v>4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>106</v>
+      </c>
+      <c r="K23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],['#VALOR!]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L23" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="M23" t="str">
+        <v>MANHÃ</v>
+      </c>
+      <c r="M23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[MODALIDADE]], tblModalidades[MODALIDADE], tblModalidades[ID_MODALIDADE],"")</f>
-        <v/>
-      </c>
-      <c r="O23" s="32"/>
-      <c r="P23" s="32"/>
-      <c r="Q23" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="N23" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P23" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="Q23" s="33">
         <f>($P23-$O23)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>#VALUE!</v>
+        <v>0.15625000000000003</v>
+      </c>
+      <c r="R23">
+        <v>15</v>
+      </c>
+      <c r="S23" t="s">
+        <v>192</v>
+      </c>
+      <c r="T23" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.35">
@@ -27194,7 +27246,7 @@
         <v>24</v>
       </c>
       <c r="H2" s="35">
-        <f>$F2/$G2</f>
+        <f t="shared" ref="H2:H18" si="0">$F2/$G2</f>
         <v>0.91666666666666663</v>
       </c>
       <c r="I2" t="str">
@@ -27230,7 +27282,7 @@
         <v>24</v>
       </c>
       <c r="H3" s="35">
-        <f>$F3/$G3</f>
+        <f t="shared" si="0"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="I3" t="str">
@@ -27266,7 +27318,7 @@
         <v>24</v>
       </c>
       <c r="H4" s="35">
-        <f>$F4/$G4</f>
+        <f t="shared" si="0"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="I4" t="str">
@@ -27302,7 +27354,7 @@
         <v>24</v>
       </c>
       <c r="H5" s="35">
-        <f>$F5/$G5</f>
+        <f t="shared" si="0"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="I5" t="str">
@@ -27338,7 +27390,7 @@
         <v>24</v>
       </c>
       <c r="H6" s="35">
-        <f>$F6/$G6</f>
+        <f t="shared" si="0"/>
         <v>0.875</v>
       </c>
       <c r="I6" t="str">
@@ -27374,7 +27426,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="35">
-        <f>$F7/$G7</f>
+        <f t="shared" si="0"/>
         <v>0.875</v>
       </c>
       <c r="I7" t="str">
@@ -27410,7 +27462,7 @@
         <v>24</v>
       </c>
       <c r="H8" s="35">
-        <f>$F8/$G8</f>
+        <f t="shared" si="0"/>
         <v>0.875</v>
       </c>
       <c r="I8" t="str">
@@ -27446,7 +27498,7 @@
         <v>24</v>
       </c>
       <c r="H9" s="35">
-        <f>$F9/$G9</f>
+        <f t="shared" si="0"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="I9" t="str">
@@ -27482,7 +27534,7 @@
         <v>24</v>
       </c>
       <c r="H10" s="35">
-        <f>$F10/$G10</f>
+        <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="I10" t="str">
@@ -27518,7 +27570,7 @@
         <v>24</v>
       </c>
       <c r="H11" s="35">
-        <f>$F11/$G11</f>
+        <f t="shared" si="0"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="I11" t="str">
@@ -27554,7 +27606,7 @@
         <v>24</v>
       </c>
       <c r="H12" s="35">
-        <f>$F12/$G12</f>
+        <f t="shared" si="0"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="I12" t="str">
@@ -27590,7 +27642,7 @@
         <v>24</v>
       </c>
       <c r="H13" s="35">
-        <f>$F13/$G13</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
       <c r="I13" t="str">
@@ -27626,7 +27678,7 @@
         <v>24</v>
       </c>
       <c r="H14" s="35">
-        <f>$F14/$G14</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
       <c r="I14" t="str">
@@ -27662,7 +27714,7 @@
         <v>24</v>
       </c>
       <c r="H15" s="35">
-        <f>$F15/$G15</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
       <c r="I15" t="str">
@@ -27698,7 +27750,7 @@
         <v>24</v>
       </c>
       <c r="H16" s="35">
-        <f>$F16/$G16</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
       <c r="I16" t="str">
@@ -27734,7 +27786,7 @@
         <v>24</v>
       </c>
       <c r="H17" s="35">
-        <f>$F17/$G17</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
       <c r="I17" t="str">
@@ -27770,7 +27822,7 @@
         <v>24</v>
       </c>
       <c r="H18" s="35">
-        <f>$F18/$G18</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
       <c r="I18" t="str">
@@ -27806,7 +27858,7 @@
         <v>24</v>
       </c>
       <c r="H19" s="35">
-        <f t="shared" ref="H19:H21" si="0">$F19/$G19</f>
+        <f t="shared" ref="H19:H21" si="1">$F19/$G19</f>
         <v>0.625</v>
       </c>
       <c r="I19" t="str">
@@ -27842,7 +27894,7 @@
         <v>24</v>
       </c>
       <c r="H20" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
       <c r="I20" t="str">
@@ -27878,7 +27930,7 @@
         <v>24</v>
       </c>
       <c r="H21" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
       <c r="I21" t="str">
@@ -27890,22 +27942,39 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="35" t="e">
-        <f>$F22/$G22</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I22" t="e">
-        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
-        <v>#DIV/0!</v>
+      <c r="A22" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B22">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22">
+        <v>21</v>
+      </c>
+      <c r="G22">
+        <v>24</v>
+      </c>
+      <c r="H22" s="35">
+        <f t="shared" ref="H22:H85" si="2">$F22/$G22</f>
+        <v>0.875</v>
+      </c>
+      <c r="I22" t="str">
+        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
+        <v>ALTA</v>
+      </c>
+      <c r="J22" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
@@ -27919,7 +27988,7 @@
         <v/>
       </c>
       <c r="H23" s="35" t="e">
-        <f>$F23/$G23</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I23" t="e">
@@ -27938,7 +28007,7 @@
         <v/>
       </c>
       <c r="H24" s="35" t="e">
-        <f>$F24/$G24</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I24" t="e">
@@ -27957,7 +28026,7 @@
         <v/>
       </c>
       <c r="H25" s="35" t="e">
-        <f>$F25/$G25</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I25" t="e">
@@ -27976,7 +28045,7 @@
         <v/>
       </c>
       <c r="H26" s="35" t="e">
-        <f>$F26/$G26</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I26" t="e">
@@ -27995,7 +28064,7 @@
         <v/>
       </c>
       <c r="H27" s="35" t="e">
-        <f>$F27/$G27</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I27" t="e">
@@ -28014,7 +28083,7 @@
         <v/>
       </c>
       <c r="H28" s="35" t="e">
-        <f>$F28/$G28</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" t="e">
@@ -28033,7 +28102,7 @@
         <v/>
       </c>
       <c r="H29" s="35" t="e">
-        <f>$F29/$G29</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I29" t="e">
@@ -28052,7 +28121,7 @@
         <v/>
       </c>
       <c r="H30" s="35" t="e">
-        <f>$F30/$G30</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I30" t="e">
@@ -28071,7 +28140,7 @@
         <v/>
       </c>
       <c r="H31" s="35" t="e">
-        <f>$F31/$G31</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I31" t="e">
@@ -28090,7 +28159,7 @@
         <v/>
       </c>
       <c r="H32" s="35" t="e">
-        <f>$F32/$G32</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I32" t="e">
@@ -28109,7 +28178,7 @@
         <v/>
       </c>
       <c r="H33" s="35" t="e">
-        <f>$F33/$G33</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I33" t="e">
@@ -28128,7 +28197,7 @@
         <v/>
       </c>
       <c r="H34" s="35" t="e">
-        <f>$F34/$G34</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I34" t="e">
@@ -28147,7 +28216,7 @@
         <v/>
       </c>
       <c r="H35" s="35" t="e">
-        <f>$F35/$G35</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I35" t="e">
@@ -28166,7 +28235,7 @@
         <v/>
       </c>
       <c r="H36" s="35" t="e">
-        <f>$F36/$G36</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I36" t="e">
@@ -28185,7 +28254,7 @@
         <v/>
       </c>
       <c r="H37" s="35" t="e">
-        <f>$F37/$G37</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I37" t="e">
@@ -28204,7 +28273,7 @@
         <v/>
       </c>
       <c r="H38" s="35" t="e">
-        <f>$F38/$G38</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I38" t="e">
@@ -28223,7 +28292,7 @@
         <v/>
       </c>
       <c r="H39" s="35" t="e">
-        <f>$F39/$G39</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I39" t="e">
@@ -28242,7 +28311,7 @@
         <v/>
       </c>
       <c r="H40" s="35" t="e">
-        <f>$F40/$G40</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I40" t="e">
@@ -28261,7 +28330,7 @@
         <v/>
       </c>
       <c r="H41" s="35" t="e">
-        <f>$F41/$G41</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I41" t="e">
@@ -28280,7 +28349,7 @@
         <v/>
       </c>
       <c r="H42" s="35" t="e">
-        <f>$F42/$G42</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I42" t="e">
@@ -28299,7 +28368,7 @@
         <v/>
       </c>
       <c r="H43" s="35" t="e">
-        <f>$F43/$G43</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I43" t="e">
@@ -28318,7 +28387,7 @@
         <v/>
       </c>
       <c r="H44" s="35" t="e">
-        <f>$F44/$G44</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I44" t="e">
@@ -28337,7 +28406,7 @@
         <v/>
       </c>
       <c r="H45" s="35" t="e">
-        <f>$F45/$G45</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I45" t="e">
@@ -28356,7 +28425,7 @@
         <v/>
       </c>
       <c r="H46" s="35" t="e">
-        <f>$F46/$G46</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I46" t="e">
@@ -28375,7 +28444,7 @@
         <v/>
       </c>
       <c r="H47" s="35" t="e">
-        <f>$F47/$G47</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I47" t="e">
@@ -28394,7 +28463,7 @@
         <v/>
       </c>
       <c r="H48" s="35" t="e">
-        <f>$F48/$G48</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I48" t="e">
@@ -28413,7 +28482,7 @@
         <v/>
       </c>
       <c r="H49" s="35" t="e">
-        <f>$F49/$G49</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I49" t="e">
@@ -28432,7 +28501,7 @@
         <v/>
       </c>
       <c r="H50" s="35" t="e">
-        <f>$F50/$G50</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I50" t="e">
@@ -28451,7 +28520,7 @@
         <v/>
       </c>
       <c r="H51" s="35" t="e">
-        <f>$F51/$G51</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I51" t="e">
@@ -28470,7 +28539,7 @@
         <v/>
       </c>
       <c r="H52" s="35" t="e">
-        <f>$F52/$G52</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I52" t="e">
@@ -28489,7 +28558,7 @@
         <v/>
       </c>
       <c r="H53" s="35" t="e">
-        <f>$F53/$G53</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I53" t="e">
@@ -28508,7 +28577,7 @@
         <v/>
       </c>
       <c r="H54" s="35" t="e">
-        <f>$F54/$G54</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I54" t="e">
@@ -28527,7 +28596,7 @@
         <v/>
       </c>
       <c r="H55" s="35" t="e">
-        <f>$F55/$G55</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I55" t="e">
@@ -28546,7 +28615,7 @@
         <v/>
       </c>
       <c r="H56" s="35" t="e">
-        <f>$F56/$G56</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I56" t="e">
@@ -28565,7 +28634,7 @@
         <v/>
       </c>
       <c r="H57" s="35" t="e">
-        <f>$F57/$G57</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I57" t="e">
@@ -28584,7 +28653,7 @@
         <v/>
       </c>
       <c r="H58" s="35" t="e">
-        <f>$F58/$G58</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I58" t="e">
@@ -28603,7 +28672,7 @@
         <v/>
       </c>
       <c r="H59" s="35" t="e">
-        <f>$F59/$G59</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I59" t="e">
@@ -28622,7 +28691,7 @@
         <v/>
       </c>
       <c r="H60" s="35" t="e">
-        <f>$F60/$G60</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I60" t="e">
@@ -28641,7 +28710,7 @@
         <v/>
       </c>
       <c r="H61" s="35" t="e">
-        <f>$F61/$G61</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I61" t="e">
@@ -28660,7 +28729,7 @@
         <v/>
       </c>
       <c r="H62" s="35" t="e">
-        <f>$F62/$G62</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I62" t="e">
@@ -28679,7 +28748,7 @@
         <v/>
       </c>
       <c r="H63" s="35" t="e">
-        <f>$F63/$G63</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I63" t="e">
@@ -28698,7 +28767,7 @@
         <v/>
       </c>
       <c r="H64" s="35" t="e">
-        <f>$F64/$G64</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I64" t="e">
@@ -28717,7 +28786,7 @@
         <v/>
       </c>
       <c r="H65" s="35" t="e">
-        <f>$F65/$G65</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I65" t="e">
@@ -28736,7 +28805,7 @@
         <v/>
       </c>
       <c r="H66" s="35" t="e">
-        <f>$F66/$G66</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I66" t="e">
@@ -28755,7 +28824,7 @@
         <v/>
       </c>
       <c r="H67" s="35" t="e">
-        <f>$F67/$G67</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I67" t="e">
@@ -28774,7 +28843,7 @@
         <v/>
       </c>
       <c r="H68" s="35" t="e">
-        <f>$F68/$G68</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I68" t="e">
@@ -28793,7 +28862,7 @@
         <v/>
       </c>
       <c r="H69" s="35" t="e">
-        <f>$F69/$G69</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I69" t="e">
@@ -28812,7 +28881,7 @@
         <v/>
       </c>
       <c r="H70" s="35" t="e">
-        <f>$F70/$G70</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I70" t="e">
@@ -28831,7 +28900,7 @@
         <v/>
       </c>
       <c r="H71" s="35" t="e">
-        <f>$F71/$G71</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I71" t="e">
@@ -28850,7 +28919,7 @@
         <v/>
       </c>
       <c r="H72" s="35" t="e">
-        <f>$F72/$G72</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I72" t="e">
@@ -28869,7 +28938,7 @@
         <v/>
       </c>
       <c r="H73" s="35" t="e">
-        <f>$F73/$G73</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I73" t="e">
@@ -28888,7 +28957,7 @@
         <v/>
       </c>
       <c r="H74" s="35" t="e">
-        <f>$F74/$G74</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I74" t="e">
@@ -28907,7 +28976,7 @@
         <v/>
       </c>
       <c r="H75" s="35" t="e">
-        <f>$F75/$G75</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I75" t="e">
@@ -28926,7 +28995,7 @@
         <v/>
       </c>
       <c r="H76" s="35" t="e">
-        <f>$F76/$G76</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I76" t="e">
@@ -28945,7 +29014,7 @@
         <v/>
       </c>
       <c r="H77" s="35" t="e">
-        <f>$F77/$G77</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I77" t="e">
@@ -28964,7 +29033,7 @@
         <v/>
       </c>
       <c r="H78" s="35" t="e">
-        <f>$F78/$G78</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I78" t="e">
@@ -28983,7 +29052,7 @@
         <v/>
       </c>
       <c r="H79" s="35" t="e">
-        <f>$F79/$G79</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I79" t="e">
@@ -29002,7 +29071,7 @@
         <v/>
       </c>
       <c r="H80" s="35" t="e">
-        <f>$F80/$G80</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I80" t="e">
@@ -29021,7 +29090,7 @@
         <v/>
       </c>
       <c r="H81" s="35" t="e">
-        <f>$F81/$G81</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I81" t="e">
@@ -29040,7 +29109,7 @@
         <v/>
       </c>
       <c r="H82" s="35" t="e">
-        <f>$F82/$G82</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I82" t="e">
@@ -29059,7 +29128,7 @@
         <v/>
       </c>
       <c r="H83" s="35" t="e">
-        <f>$F83/$G83</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I83" t="e">
@@ -29078,7 +29147,7 @@
         <v/>
       </c>
       <c r="H84" s="35" t="e">
-        <f>$F84/$G84</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I84" t="e">
@@ -29097,7 +29166,7 @@
         <v/>
       </c>
       <c r="H85" s="35" t="e">
-        <f>$F85/$G85</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I85" t="e">
@@ -29116,7 +29185,7 @@
         <v/>
       </c>
       <c r="H86" s="35" t="e">
-        <f>$F86/$G86</f>
+        <f t="shared" ref="H86:H149" si="3">$F86/$G86</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I86" t="e">
@@ -29135,7 +29204,7 @@
         <v/>
       </c>
       <c r="H87" s="35" t="e">
-        <f>$F87/$G87</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I87" t="e">
@@ -29154,7 +29223,7 @@
         <v/>
       </c>
       <c r="H88" s="35" t="e">
-        <f>$F88/$G88</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I88" t="e">
@@ -29173,7 +29242,7 @@
         <v/>
       </c>
       <c r="H89" s="35" t="e">
-        <f>$F89/$G89</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I89" t="e">
@@ -29192,7 +29261,7 @@
         <v/>
       </c>
       <c r="H90" s="35" t="e">
-        <f>$F90/$G90</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I90" t="e">
@@ -29211,7 +29280,7 @@
         <v/>
       </c>
       <c r="H91" s="35" t="e">
-        <f>$F91/$G91</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I91" t="e">
@@ -29230,7 +29299,7 @@
         <v/>
       </c>
       <c r="H92" s="35" t="e">
-        <f>$F92/$G92</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I92" t="e">
@@ -29249,7 +29318,7 @@
         <v/>
       </c>
       <c r="H93" s="35" t="e">
-        <f>$F93/$G93</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I93" t="e">
@@ -29268,7 +29337,7 @@
         <v/>
       </c>
       <c r="H94" s="35" t="e">
-        <f>$F94/$G94</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I94" t="e">
@@ -29287,7 +29356,7 @@
         <v/>
       </c>
       <c r="H95" s="35" t="e">
-        <f>$F95/$G95</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I95" t="e">
@@ -29306,7 +29375,7 @@
         <v/>
       </c>
       <c r="H96" s="35" t="e">
-        <f>$F96/$G96</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I96" t="e">
@@ -29325,7 +29394,7 @@
         <v/>
       </c>
       <c r="H97" s="35" t="e">
-        <f>$F97/$G97</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I97" t="e">
@@ -29344,7 +29413,7 @@
         <v/>
       </c>
       <c r="H98" s="35" t="e">
-        <f>$F98/$G98</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I98" t="e">
@@ -29363,7 +29432,7 @@
         <v/>
       </c>
       <c r="H99" s="35" t="e">
-        <f>$F99/$G99</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I99" t="e">
@@ -29382,7 +29451,7 @@
         <v/>
       </c>
       <c r="H100" s="35" t="e">
-        <f>$F100/$G100</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I100" t="e">
@@ -29401,7 +29470,7 @@
         <v/>
       </c>
       <c r="H101" s="35" t="e">
-        <f>$F101/$G101</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I101" t="e">
@@ -29420,7 +29489,7 @@
         <v/>
       </c>
       <c r="H102" s="35" t="e">
-        <f>$F102/$G102</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I102" t="e">
@@ -29439,7 +29508,7 @@
         <v/>
       </c>
       <c r="H103" s="35" t="e">
-        <f>$F103/$G103</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I103" t="e">
@@ -29458,7 +29527,7 @@
         <v/>
       </c>
       <c r="H104" s="35" t="e">
-        <f>$F104/$G104</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I104" t="e">
@@ -29477,7 +29546,7 @@
         <v/>
       </c>
       <c r="H105" s="35" t="e">
-        <f>$F105/$G105</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I105" t="e">
@@ -29496,7 +29565,7 @@
         <v/>
       </c>
       <c r="H106" s="35" t="e">
-        <f>$F106/$G106</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I106" t="e">
@@ -29515,7 +29584,7 @@
         <v/>
       </c>
       <c r="H107" s="35" t="e">
-        <f>$F107/$G107</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I107" t="e">
@@ -29534,7 +29603,7 @@
         <v/>
       </c>
       <c r="H108" s="35" t="e">
-        <f>$F108/$G108</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I108" t="e">
@@ -29553,7 +29622,7 @@
         <v/>
       </c>
       <c r="H109" s="35" t="e">
-        <f>$F109/$G109</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I109" t="e">
@@ -29572,7 +29641,7 @@
         <v/>
       </c>
       <c r="H110" s="35" t="e">
-        <f>$F110/$G110</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I110" t="e">
@@ -29591,7 +29660,7 @@
         <v/>
       </c>
       <c r="H111" s="35" t="e">
-        <f>$F111/$G111</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I111" t="e">
@@ -29610,7 +29679,7 @@
         <v/>
       </c>
       <c r="H112" s="35" t="e">
-        <f>$F112/$G112</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I112" t="e">
@@ -29629,7 +29698,7 @@
         <v/>
       </c>
       <c r="H113" s="35" t="e">
-        <f>$F113/$G113</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I113" t="e">
@@ -29648,7 +29717,7 @@
         <v/>
       </c>
       <c r="H114" s="35" t="e">
-        <f>$F114/$G114</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I114" t="e">
@@ -29667,7 +29736,7 @@
         <v/>
       </c>
       <c r="H115" s="35" t="e">
-        <f>$F115/$G115</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I115" t="e">
@@ -29686,7 +29755,7 @@
         <v/>
       </c>
       <c r="H116" s="35" t="e">
-        <f>$F116/$G116</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I116" t="e">
@@ -29705,7 +29774,7 @@
         <v/>
       </c>
       <c r="H117" s="35" t="e">
-        <f>$F117/$G117</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I117" t="e">
@@ -29724,7 +29793,7 @@
         <v/>
       </c>
       <c r="H118" s="35" t="e">
-        <f>$F118/$G118</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I118" t="e">
@@ -29743,7 +29812,7 @@
         <v/>
       </c>
       <c r="H119" s="35" t="e">
-        <f>$F119/$G119</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I119" t="e">
@@ -29762,7 +29831,7 @@
         <v/>
       </c>
       <c r="H120" s="35" t="e">
-        <f>$F120/$G120</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I120" t="e">
@@ -29781,7 +29850,7 @@
         <v/>
       </c>
       <c r="H121" s="35" t="e">
-        <f>$F121/$G121</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I121" t="e">
@@ -29800,7 +29869,7 @@
         <v/>
       </c>
       <c r="H122" s="35" t="e">
-        <f>$F122/$G122</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I122" t="e">
@@ -29819,7 +29888,7 @@
         <v/>
       </c>
       <c r="H123" s="35" t="e">
-        <f>$F123/$G123</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I123" t="e">
@@ -29838,7 +29907,7 @@
         <v/>
       </c>
       <c r="H124" s="35" t="e">
-        <f>$F124/$G124</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I124" t="e">
@@ -29857,7 +29926,7 @@
         <v/>
       </c>
       <c r="H125" s="35" t="e">
-        <f>$F125/$G125</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I125" t="e">
@@ -29876,7 +29945,7 @@
         <v/>
       </c>
       <c r="H126" s="35" t="e">
-        <f>$F126/$G126</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I126" t="e">
@@ -29895,7 +29964,7 @@
         <v/>
       </c>
       <c r="H127" s="35" t="e">
-        <f>$F127/$G127</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I127" t="e">
@@ -29914,7 +29983,7 @@
         <v/>
       </c>
       <c r="H128" s="35" t="e">
-        <f>$F128/$G128</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I128" t="e">
@@ -29933,7 +30002,7 @@
         <v/>
       </c>
       <c r="H129" s="35" t="e">
-        <f>$F129/$G129</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I129" t="e">
@@ -29952,7 +30021,7 @@
         <v/>
       </c>
       <c r="H130" s="35" t="e">
-        <f>$F130/$G130</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I130" t="e">
@@ -29971,7 +30040,7 @@
         <v/>
       </c>
       <c r="H131" s="35" t="e">
-        <f>$F131/$G131</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I131" t="e">
@@ -29990,7 +30059,7 @@
         <v/>
       </c>
       <c r="H132" s="35" t="e">
-        <f>$F132/$G132</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I132" t="e">
@@ -30009,7 +30078,7 @@
         <v/>
       </c>
       <c r="H133" s="35" t="e">
-        <f>$F133/$G133</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I133" t="e">
@@ -30028,7 +30097,7 @@
         <v/>
       </c>
       <c r="H134" s="35" t="e">
-        <f>$F134/$G134</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I134" t="e">
@@ -30047,7 +30116,7 @@
         <v/>
       </c>
       <c r="H135" s="35" t="e">
-        <f>$F135/$G135</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I135" t="e">
@@ -30066,7 +30135,7 @@
         <v/>
       </c>
       <c r="H136" s="35" t="e">
-        <f>$F136/$G136</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I136" t="e">
@@ -30085,7 +30154,7 @@
         <v/>
       </c>
       <c r="H137" s="35" t="e">
-        <f>$F137/$G137</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I137" t="e">
@@ -30104,7 +30173,7 @@
         <v/>
       </c>
       <c r="H138" s="35" t="e">
-        <f>$F138/$G138</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I138" t="e">
@@ -30123,7 +30192,7 @@
         <v/>
       </c>
       <c r="H139" s="35" t="e">
-        <f>$F139/$G139</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I139" t="e">
@@ -30142,7 +30211,7 @@
         <v/>
       </c>
       <c r="H140" s="35" t="e">
-        <f>$F140/$G140</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I140" t="e">
@@ -30161,7 +30230,7 @@
         <v/>
       </c>
       <c r="H141" s="35" t="e">
-        <f>$F141/$G141</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I141" t="e">
@@ -30180,7 +30249,7 @@
         <v/>
       </c>
       <c r="H142" s="35" t="e">
-        <f>$F142/$G142</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I142" t="e">
@@ -30199,7 +30268,7 @@
         <v/>
       </c>
       <c r="H143" s="35" t="e">
-        <f>$F143/$G143</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I143" t="e">
@@ -30218,7 +30287,7 @@
         <v/>
       </c>
       <c r="H144" s="35" t="e">
-        <f>$F144/$G144</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I144" t="e">
@@ -30237,7 +30306,7 @@
         <v/>
       </c>
       <c r="H145" s="35" t="e">
-        <f>$F145/$G145</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I145" t="e">
@@ -30256,7 +30325,7 @@
         <v/>
       </c>
       <c r="H146" s="35" t="e">
-        <f>$F146/$G146</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I146" t="e">
@@ -30275,7 +30344,7 @@
         <v/>
       </c>
       <c r="H147" s="35" t="e">
-        <f>$F147/$G147</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I147" t="e">
@@ -30294,7 +30363,7 @@
         <v/>
       </c>
       <c r="H148" s="35" t="e">
-        <f>$F148/$G148</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I148" t="e">
@@ -30313,7 +30382,7 @@
         <v/>
       </c>
       <c r="H149" s="35" t="e">
-        <f>$F149/$G149</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I149" t="e">
@@ -30332,7 +30401,7 @@
         <v/>
       </c>
       <c r="H150" s="35" t="e">
-        <f>$F150/$G150</f>
+        <f t="shared" ref="H150:H213" si="4">$F150/$G150</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I150" t="e">
@@ -30351,7 +30420,7 @@
         <v/>
       </c>
       <c r="H151" s="35" t="e">
-        <f>$F151/$G151</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I151" t="e">
@@ -30370,7 +30439,7 @@
         <v/>
       </c>
       <c r="H152" s="35" t="e">
-        <f>$F152/$G152</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I152" t="e">
@@ -30389,7 +30458,7 @@
         <v/>
       </c>
       <c r="H153" s="35" t="e">
-        <f>$F153/$G153</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I153" t="e">
@@ -30408,7 +30477,7 @@
         <v/>
       </c>
       <c r="H154" s="35" t="e">
-        <f>$F154/$G154</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I154" t="e">
@@ -30427,7 +30496,7 @@
         <v/>
       </c>
       <c r="H155" s="35" t="e">
-        <f>$F155/$G155</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I155" t="e">
@@ -30446,7 +30515,7 @@
         <v/>
       </c>
       <c r="H156" s="35" t="e">
-        <f>$F156/$G156</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I156" t="e">
@@ -30465,7 +30534,7 @@
         <v/>
       </c>
       <c r="H157" s="35" t="e">
-        <f>$F157/$G157</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I157" t="e">
@@ -30484,7 +30553,7 @@
         <v/>
       </c>
       <c r="H158" s="35" t="e">
-        <f>$F158/$G158</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I158" t="e">
@@ -30503,7 +30572,7 @@
         <v/>
       </c>
       <c r="H159" s="35" t="e">
-        <f>$F159/$G159</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I159" t="e">
@@ -30522,7 +30591,7 @@
         <v/>
       </c>
       <c r="H160" s="35" t="e">
-        <f>$F160/$G160</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I160" t="e">
@@ -30541,7 +30610,7 @@
         <v/>
       </c>
       <c r="H161" s="35" t="e">
-        <f>$F161/$G161</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I161" t="e">
@@ -30560,7 +30629,7 @@
         <v/>
       </c>
       <c r="H162" s="35" t="e">
-        <f>$F162/$G162</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I162" t="e">
@@ -30579,7 +30648,7 @@
         <v/>
       </c>
       <c r="H163" s="35" t="e">
-        <f>$F163/$G163</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I163" t="e">
@@ -30598,7 +30667,7 @@
         <v/>
       </c>
       <c r="H164" s="35" t="e">
-        <f>$F164/$G164</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I164" t="e">
@@ -30617,7 +30686,7 @@
         <v/>
       </c>
       <c r="H165" s="35" t="e">
-        <f>$F165/$G165</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I165" t="e">
@@ -30636,7 +30705,7 @@
         <v/>
       </c>
       <c r="H166" s="35" t="e">
-        <f>$F166/$G166</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I166" t="e">
@@ -30655,7 +30724,7 @@
         <v/>
       </c>
       <c r="H167" s="35" t="e">
-        <f>$F167/$G167</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I167" t="e">
@@ -30674,7 +30743,7 @@
         <v/>
       </c>
       <c r="H168" s="35" t="e">
-        <f>$F168/$G168</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I168" t="e">
@@ -30693,7 +30762,7 @@
         <v/>
       </c>
       <c r="H169" s="35" t="e">
-        <f>$F169/$G169</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I169" t="e">
@@ -30712,7 +30781,7 @@
         <v/>
       </c>
       <c r="H170" s="35" t="e">
-        <f>$F170/$G170</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I170" t="e">
@@ -30731,7 +30800,7 @@
         <v/>
       </c>
       <c r="H171" s="35" t="e">
-        <f>$F171/$G171</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I171" t="e">
@@ -30750,7 +30819,7 @@
         <v/>
       </c>
       <c r="H172" s="35" t="e">
-        <f>$F172/$G172</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I172" t="e">
@@ -30769,7 +30838,7 @@
         <v/>
       </c>
       <c r="H173" s="35" t="e">
-        <f>$F173/$G173</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I173" t="e">
@@ -30788,7 +30857,7 @@
         <v/>
       </c>
       <c r="H174" s="35" t="e">
-        <f>$F174/$G174</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I174" t="e">
@@ -30807,7 +30876,7 @@
         <v/>
       </c>
       <c r="H175" s="35" t="e">
-        <f>$F175/$G175</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I175" t="e">
@@ -30826,7 +30895,7 @@
         <v/>
       </c>
       <c r="H176" s="35" t="e">
-        <f>$F176/$G176</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I176" t="e">
@@ -30845,7 +30914,7 @@
         <v/>
       </c>
       <c r="H177" s="35" t="e">
-        <f>$F177/$G177</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I177" t="e">
@@ -30864,7 +30933,7 @@
         <v/>
       </c>
       <c r="H178" s="35" t="e">
-        <f>$F178/$G178</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I178" t="e">
@@ -30883,7 +30952,7 @@
         <v/>
       </c>
       <c r="H179" s="35" t="e">
-        <f>$F179/$G179</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I179" t="e">
@@ -30902,7 +30971,7 @@
         <v/>
       </c>
       <c r="H180" s="35" t="e">
-        <f>$F180/$G180</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I180" t="e">
@@ -30921,7 +30990,7 @@
         <v/>
       </c>
       <c r="H181" s="35" t="e">
-        <f>$F181/$G181</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I181" t="e">
@@ -30940,7 +31009,7 @@
         <v/>
       </c>
       <c r="H182" s="35" t="e">
-        <f>$F182/$G182</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I182" t="e">
@@ -30959,7 +31028,7 @@
         <v/>
       </c>
       <c r="H183" s="35" t="e">
-        <f>$F183/$G183</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I183" t="e">
@@ -30978,7 +31047,7 @@
         <v/>
       </c>
       <c r="H184" s="35" t="e">
-        <f>$F184/$G184</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I184" t="e">
@@ -30997,7 +31066,7 @@
         <v/>
       </c>
       <c r="H185" s="35" t="e">
-        <f>$F185/$G185</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I185" t="e">
@@ -31016,7 +31085,7 @@
         <v/>
       </c>
       <c r="H186" s="35" t="e">
-        <f>$F186/$G186</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I186" t="e">
@@ -31035,7 +31104,7 @@
         <v/>
       </c>
       <c r="H187" s="35" t="e">
-        <f>$F187/$G187</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I187" t="e">
@@ -31054,7 +31123,7 @@
         <v/>
       </c>
       <c r="H188" s="35" t="e">
-        <f>$F188/$G188</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I188" t="e">
@@ -31073,7 +31142,7 @@
         <v/>
       </c>
       <c r="H189" s="35" t="e">
-        <f>$F189/$G189</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I189" t="e">
@@ -31092,7 +31161,7 @@
         <v/>
       </c>
       <c r="H190" s="35" t="e">
-        <f>$F190/$G190</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I190" t="e">
@@ -31111,7 +31180,7 @@
         <v/>
       </c>
       <c r="H191" s="35" t="e">
-        <f>$F191/$G191</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I191" t="e">
@@ -31130,7 +31199,7 @@
         <v/>
       </c>
       <c r="H192" s="35" t="e">
-        <f>$F192/$G192</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I192" t="e">
@@ -31149,7 +31218,7 @@
         <v/>
       </c>
       <c r="H193" s="35" t="e">
-        <f>$F193/$G193</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I193" t="e">
@@ -31168,7 +31237,7 @@
         <v/>
       </c>
       <c r="H194" s="35" t="e">
-        <f>$F194/$G194</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I194" t="e">
@@ -31187,7 +31256,7 @@
         <v/>
       </c>
       <c r="H195" s="35" t="e">
-        <f>$F195/$G195</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I195" t="e">
@@ -31206,7 +31275,7 @@
         <v/>
       </c>
       <c r="H196" s="35" t="e">
-        <f>$F196/$G196</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I196" t="e">
@@ -31225,7 +31294,7 @@
         <v/>
       </c>
       <c r="H197" s="35" t="e">
-        <f>$F197/$G197</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I197" t="e">
@@ -31244,7 +31313,7 @@
         <v/>
       </c>
       <c r="H198" s="35" t="e">
-        <f>$F198/$G198</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I198" t="e">
@@ -31263,7 +31332,7 @@
         <v/>
       </c>
       <c r="H199" s="35" t="e">
-        <f>$F199/$G199</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I199" t="e">
@@ -31282,7 +31351,7 @@
         <v/>
       </c>
       <c r="H200" s="35" t="e">
-        <f>$F200/$G200</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I200" t="e">
@@ -31301,7 +31370,7 @@
         <v/>
       </c>
       <c r="H201" s="35" t="e">
-        <f>$F201/$G201</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I201" t="e">
@@ -31320,7 +31389,7 @@
         <v/>
       </c>
       <c r="H202" s="35" t="e">
-        <f>$F202/$G202</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I202" t="e">
@@ -31339,7 +31408,7 @@
         <v/>
       </c>
       <c r="H203" s="35" t="e">
-        <f>$F203/$G203</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I203" t="e">
@@ -31358,7 +31427,7 @@
         <v/>
       </c>
       <c r="H204" s="35" t="e">
-        <f>$F204/$G204</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I204" t="e">
@@ -31377,7 +31446,7 @@
         <v/>
       </c>
       <c r="H205" s="35" t="e">
-        <f>$F205/$G205</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I205" t="e">
@@ -31396,7 +31465,7 @@
         <v/>
       </c>
       <c r="H206" s="35" t="e">
-        <f>$F206/$G206</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I206" t="e">
@@ -31415,7 +31484,7 @@
         <v/>
       </c>
       <c r="H207" s="35" t="e">
-        <f>$F207/$G207</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I207" t="e">
@@ -31434,7 +31503,7 @@
         <v/>
       </c>
       <c r="H208" s="35" t="e">
-        <f>$F208/$G208</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I208" t="e">
@@ -31453,7 +31522,7 @@
         <v/>
       </c>
       <c r="H209" s="35" t="e">
-        <f>$F209/$G209</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I209" t="e">
@@ -31472,7 +31541,7 @@
         <v/>
       </c>
       <c r="H210" s="35" t="e">
-        <f>$F210/$G210</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I210" t="e">
@@ -31491,7 +31560,7 @@
         <v/>
       </c>
       <c r="H211" s="35" t="e">
-        <f>$F211/$G211</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I211" t="e">
@@ -31510,7 +31579,7 @@
         <v/>
       </c>
       <c r="H212" s="35" t="e">
-        <f>$F212/$G212</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I212" t="e">
@@ -31529,7 +31598,7 @@
         <v/>
       </c>
       <c r="H213" s="35" t="e">
-        <f>$F213/$G213</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I213" t="e">
@@ -31548,7 +31617,7 @@
         <v/>
       </c>
       <c r="H214" s="35" t="e">
-        <f>$F214/$G214</f>
+        <f t="shared" ref="H214:H277" si="5">$F214/$G214</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I214" t="e">
@@ -31567,7 +31636,7 @@
         <v/>
       </c>
       <c r="H215" s="35" t="e">
-        <f>$F215/$G215</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I215" t="e">
@@ -31586,7 +31655,7 @@
         <v/>
       </c>
       <c r="H216" s="35" t="e">
-        <f>$F216/$G216</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I216" t="e">
@@ -31605,7 +31674,7 @@
         <v/>
       </c>
       <c r="H217" s="35" t="e">
-        <f>$F217/$G217</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I217" t="e">
@@ -31624,7 +31693,7 @@
         <v/>
       </c>
       <c r="H218" s="35" t="e">
-        <f>$F218/$G218</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I218" t="e">
@@ -31643,7 +31712,7 @@
         <v/>
       </c>
       <c r="H219" s="35" t="e">
-        <f>$F219/$G219</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I219" t="e">
@@ -31662,7 +31731,7 @@
         <v/>
       </c>
       <c r="H220" s="35" t="e">
-        <f>$F220/$G220</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I220" t="e">
@@ -31681,7 +31750,7 @@
         <v/>
       </c>
       <c r="H221" s="35" t="e">
-        <f>$F221/$G221</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I221" t="e">
@@ -31700,7 +31769,7 @@
         <v/>
       </c>
       <c r="H222" s="35" t="e">
-        <f>$F222/$G222</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I222" t="e">
@@ -31719,7 +31788,7 @@
         <v/>
       </c>
       <c r="H223" s="35" t="e">
-        <f>$F223/$G223</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I223" t="e">
@@ -31738,7 +31807,7 @@
         <v/>
       </c>
       <c r="H224" s="35" t="e">
-        <f>$F224/$G224</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I224" t="e">
@@ -31757,7 +31826,7 @@
         <v/>
       </c>
       <c r="H225" s="35" t="e">
-        <f>$F225/$G225</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I225" t="e">
@@ -31776,7 +31845,7 @@
         <v/>
       </c>
       <c r="H226" s="35" t="e">
-        <f>$F226/$G226</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I226" t="e">
@@ -31795,7 +31864,7 @@
         <v/>
       </c>
       <c r="H227" s="35" t="e">
-        <f>$F227/$G227</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I227" t="e">
@@ -31814,7 +31883,7 @@
         <v/>
       </c>
       <c r="H228" s="35" t="e">
-        <f>$F228/$G228</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I228" t="e">
@@ -31833,7 +31902,7 @@
         <v/>
       </c>
       <c r="H229" s="35" t="e">
-        <f>$F229/$G229</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I229" t="e">
@@ -31852,7 +31921,7 @@
         <v/>
       </c>
       <c r="H230" s="35" t="e">
-        <f>$F230/$G230</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I230" t="e">
@@ -31871,7 +31940,7 @@
         <v/>
       </c>
       <c r="H231" s="35" t="e">
-        <f>$F231/$G231</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I231" t="e">
@@ -31890,7 +31959,7 @@
         <v/>
       </c>
       <c r="H232" s="35" t="e">
-        <f>$F232/$G232</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I232" t="e">
@@ -31909,7 +31978,7 @@
         <v/>
       </c>
       <c r="H233" s="35" t="e">
-        <f>$F233/$G233</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I233" t="e">
@@ -31928,7 +31997,7 @@
         <v/>
       </c>
       <c r="H234" s="35" t="e">
-        <f>$F234/$G234</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I234" t="e">
@@ -31947,7 +32016,7 @@
         <v/>
       </c>
       <c r="H235" s="35" t="e">
-        <f>$F235/$G235</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I235" t="e">
@@ -31966,7 +32035,7 @@
         <v/>
       </c>
       <c r="H236" s="35" t="e">
-        <f>$F236/$G236</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I236" t="e">
@@ -31985,7 +32054,7 @@
         <v/>
       </c>
       <c r="H237" s="35" t="e">
-        <f>$F237/$G237</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I237" t="e">
@@ -32004,7 +32073,7 @@
         <v/>
       </c>
       <c r="H238" s="35" t="e">
-        <f>$F238/$G238</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I238" t="e">
@@ -32023,7 +32092,7 @@
         <v/>
       </c>
       <c r="H239" s="35" t="e">
-        <f>$F239/$G239</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I239" t="e">
@@ -32042,7 +32111,7 @@
         <v/>
       </c>
       <c r="H240" s="35" t="e">
-        <f>$F240/$G240</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I240" t="e">
@@ -32061,7 +32130,7 @@
         <v/>
       </c>
       <c r="H241" s="35" t="e">
-        <f>$F241/$G241</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I241" t="e">
@@ -32080,7 +32149,7 @@
         <v/>
       </c>
       <c r="H242" s="35" t="e">
-        <f>$F242/$G242</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I242" t="e">
@@ -32099,7 +32168,7 @@
         <v/>
       </c>
       <c r="H243" s="35" t="e">
-        <f>$F243/$G243</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I243" t="e">
@@ -32118,7 +32187,7 @@
         <v/>
       </c>
       <c r="H244" s="35" t="e">
-        <f>$F244/$G244</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I244" t="e">
@@ -32137,7 +32206,7 @@
         <v/>
       </c>
       <c r="H245" s="35" t="e">
-        <f>$F245/$G245</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I245" t="e">
@@ -32156,7 +32225,7 @@
         <v/>
       </c>
       <c r="H246" s="35" t="e">
-        <f>$F246/$G246</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I246" t="e">
@@ -32175,7 +32244,7 @@
         <v/>
       </c>
       <c r="H247" s="35" t="e">
-        <f>$F247/$G247</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I247" t="e">
@@ -32194,7 +32263,7 @@
         <v/>
       </c>
       <c r="H248" s="35" t="e">
-        <f>$F248/$G248</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I248" t="e">
@@ -32213,7 +32282,7 @@
         <v/>
       </c>
       <c r="H249" s="35" t="e">
-        <f>$F249/$G249</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I249" t="e">
@@ -32232,7 +32301,7 @@
         <v/>
       </c>
       <c r="H250" s="35" t="e">
-        <f>$F250/$G250</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I250" t="e">
@@ -32251,7 +32320,7 @@
         <v/>
       </c>
       <c r="H251" s="35" t="e">
-        <f>$F251/$G251</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I251" t="e">
@@ -32270,7 +32339,7 @@
         <v/>
       </c>
       <c r="H252" s="35" t="e">
-        <f>$F252/$G252</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I252" t="e">
@@ -32289,7 +32358,7 @@
         <v/>
       </c>
       <c r="H253" s="35" t="e">
-        <f>$F253/$G253</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I253" t="e">
@@ -32308,7 +32377,7 @@
         <v/>
       </c>
       <c r="H254" s="35" t="e">
-        <f>$F254/$G254</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I254" t="e">
@@ -32327,7 +32396,7 @@
         <v/>
       </c>
       <c r="H255" s="35" t="e">
-        <f>$F255/$G255</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I255" t="e">
@@ -32346,7 +32415,7 @@
         <v/>
       </c>
       <c r="H256" s="35" t="e">
-        <f>$F256/$G256</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I256" t="e">
@@ -32365,7 +32434,7 @@
         <v/>
       </c>
       <c r="H257" s="35" t="e">
-        <f>$F257/$G257</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I257" t="e">
@@ -32384,7 +32453,7 @@
         <v/>
       </c>
       <c r="H258" s="35" t="e">
-        <f>$F258/$G258</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I258" t="e">
@@ -32403,7 +32472,7 @@
         <v/>
       </c>
       <c r="H259" s="35" t="e">
-        <f>$F259/$G259</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I259" t="e">
@@ -32422,7 +32491,7 @@
         <v/>
       </c>
       <c r="H260" s="35" t="e">
-        <f>$F260/$G260</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I260" t="e">
@@ -32441,7 +32510,7 @@
         <v/>
       </c>
       <c r="H261" s="35" t="e">
-        <f>$F261/$G261</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I261" t="e">
@@ -32460,7 +32529,7 @@
         <v/>
       </c>
       <c r="H262" s="35" t="e">
-        <f>$F262/$G262</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I262" t="e">
@@ -32479,7 +32548,7 @@
         <v/>
       </c>
       <c r="H263" s="35" t="e">
-        <f>$F263/$G263</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I263" t="e">
@@ -32498,7 +32567,7 @@
         <v/>
       </c>
       <c r="H264" s="35" t="e">
-        <f>$F264/$G264</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I264" t="e">
@@ -32517,7 +32586,7 @@
         <v/>
       </c>
       <c r="H265" s="35" t="e">
-        <f>$F265/$G265</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I265" t="e">
@@ -32536,7 +32605,7 @@
         <v/>
       </c>
       <c r="H266" s="35" t="e">
-        <f>$F266/$G266</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I266" t="e">
@@ -32555,7 +32624,7 @@
         <v/>
       </c>
       <c r="H267" s="35" t="e">
-        <f>$F267/$G267</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I267" t="e">
@@ -32574,7 +32643,7 @@
         <v/>
       </c>
       <c r="H268" s="35" t="e">
-        <f>$F268/$G268</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I268" t="e">
@@ -32593,7 +32662,7 @@
         <v/>
       </c>
       <c r="H269" s="35" t="e">
-        <f>$F269/$G269</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I269" t="e">
@@ -32612,7 +32681,7 @@
         <v/>
       </c>
       <c r="H270" s="35" t="e">
-        <f>$F270/$G270</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I270" t="e">
@@ -32631,7 +32700,7 @@
         <v/>
       </c>
       <c r="H271" s="35" t="e">
-        <f>$F271/$G271</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I271" t="e">
@@ -32650,7 +32719,7 @@
         <v/>
       </c>
       <c r="H272" s="35" t="e">
-        <f>$F272/$G272</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I272" t="e">
@@ -32669,7 +32738,7 @@
         <v/>
       </c>
       <c r="H273" s="35" t="e">
-        <f>$F273/$G273</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I273" t="e">
@@ -32688,7 +32757,7 @@
         <v/>
       </c>
       <c r="H274" s="35" t="e">
-        <f>$F274/$G274</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I274" t="e">
@@ -32707,7 +32776,7 @@
         <v/>
       </c>
       <c r="H275" s="35" t="e">
-        <f>$F275/$G275</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I275" t="e">
@@ -32726,7 +32795,7 @@
         <v/>
       </c>
       <c r="H276" s="35" t="e">
-        <f>$F276/$G276</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I276" t="e">
@@ -32745,7 +32814,7 @@
         <v/>
       </c>
       <c r="H277" s="35" t="e">
-        <f>$F277/$G277</f>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I277" t="e">
@@ -32764,7 +32833,7 @@
         <v/>
       </c>
       <c r="H278" s="35" t="e">
-        <f>$F278/$G278</f>
+        <f t="shared" ref="H278:H341" si="6">$F278/$G278</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I278" t="e">
@@ -32783,7 +32852,7 @@
         <v/>
       </c>
       <c r="H279" s="35" t="e">
-        <f>$F279/$G279</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I279" t="e">
@@ -32802,7 +32871,7 @@
         <v/>
       </c>
       <c r="H280" s="35" t="e">
-        <f>$F280/$G280</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I280" t="e">
@@ -32821,7 +32890,7 @@
         <v/>
       </c>
       <c r="H281" s="35" t="e">
-        <f>$F281/$G281</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I281" t="e">
@@ -32840,7 +32909,7 @@
         <v/>
       </c>
       <c r="H282" s="35" t="e">
-        <f>$F282/$G282</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I282" t="e">
@@ -32859,7 +32928,7 @@
         <v/>
       </c>
       <c r="H283" s="35" t="e">
-        <f>$F283/$G283</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I283" t="e">
@@ -32878,7 +32947,7 @@
         <v/>
       </c>
       <c r="H284" s="35" t="e">
-        <f>$F284/$G284</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I284" t="e">
@@ -32897,7 +32966,7 @@
         <v/>
       </c>
       <c r="H285" s="35" t="e">
-        <f>$F285/$G285</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I285" t="e">
@@ -32916,7 +32985,7 @@
         <v/>
       </c>
       <c r="H286" s="35" t="e">
-        <f>$F286/$G286</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I286" t="e">
@@ -32935,7 +33004,7 @@
         <v/>
       </c>
       <c r="H287" s="35" t="e">
-        <f>$F287/$G287</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I287" t="e">
@@ -32954,7 +33023,7 @@
         <v/>
       </c>
       <c r="H288" s="35" t="e">
-        <f>$F288/$G288</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I288" t="e">
@@ -32973,7 +33042,7 @@
         <v/>
       </c>
       <c r="H289" s="35" t="e">
-        <f>$F289/$G289</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I289" t="e">
@@ -32992,7 +33061,7 @@
         <v/>
       </c>
       <c r="H290" s="35" t="e">
-        <f>$F290/$G290</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I290" t="e">
@@ -33011,7 +33080,7 @@
         <v/>
       </c>
       <c r="H291" s="35" t="e">
-        <f>$F291/$G291</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I291" t="e">
@@ -33030,7 +33099,7 @@
         <v/>
       </c>
       <c r="H292" s="35" t="e">
-        <f>$F292/$G292</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I292" t="e">
@@ -33049,7 +33118,7 @@
         <v/>
       </c>
       <c r="H293" s="35" t="e">
-        <f>$F293/$G293</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I293" t="e">
@@ -33068,7 +33137,7 @@
         <v/>
       </c>
       <c r="H294" s="35" t="e">
-        <f>$F294/$G294</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I294" t="e">
@@ -33087,7 +33156,7 @@
         <v/>
       </c>
       <c r="H295" s="35" t="e">
-        <f>$F295/$G295</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I295" t="e">
@@ -33106,7 +33175,7 @@
         <v/>
       </c>
       <c r="H296" s="35" t="e">
-        <f>$F296/$G296</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I296" t="e">
@@ -33125,7 +33194,7 @@
         <v/>
       </c>
       <c r="H297" s="35" t="e">
-        <f>$F297/$G297</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I297" t="e">
@@ -33144,7 +33213,7 @@
         <v/>
       </c>
       <c r="H298" s="35" t="e">
-        <f>$F298/$G298</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I298" t="e">
@@ -33163,7 +33232,7 @@
         <v/>
       </c>
       <c r="H299" s="35" t="e">
-        <f>$F299/$G299</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I299" t="e">
@@ -33182,7 +33251,7 @@
         <v/>
       </c>
       <c r="H300" s="35" t="e">
-        <f>$F300/$G300</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I300" t="e">
@@ -33201,7 +33270,7 @@
         <v/>
       </c>
       <c r="H301" s="35" t="e">
-        <f>$F301/$G301</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I301" t="e">
@@ -33220,7 +33289,7 @@
         <v/>
       </c>
       <c r="H302" s="35" t="e">
-        <f>$F302/$G302</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I302" t="e">
@@ -33239,7 +33308,7 @@
         <v/>
       </c>
       <c r="H303" s="35" t="e">
-        <f>$F303/$G303</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I303" t="e">
@@ -33258,7 +33327,7 @@
         <v/>
       </c>
       <c r="H304" s="35" t="e">
-        <f>$F304/$G304</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I304" t="e">
@@ -33277,7 +33346,7 @@
         <v/>
       </c>
       <c r="H305" s="35" t="e">
-        <f>$F305/$G305</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I305" t="e">
@@ -33296,7 +33365,7 @@
         <v/>
       </c>
       <c r="H306" s="35" t="e">
-        <f>$F306/$G306</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I306" t="e">
@@ -33315,7 +33384,7 @@
         <v/>
       </c>
       <c r="H307" s="35" t="e">
-        <f>$F307/$G307</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I307" t="e">
@@ -33334,7 +33403,7 @@
         <v/>
       </c>
       <c r="H308" s="35" t="e">
-        <f>$F308/$G308</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I308" t="e">
@@ -33353,7 +33422,7 @@
         <v/>
       </c>
       <c r="H309" s="35" t="e">
-        <f>$F309/$G309</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I309" t="e">
@@ -33372,7 +33441,7 @@
         <v/>
       </c>
       <c r="H310" s="35" t="e">
-        <f>$F310/$G310</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I310" t="e">
@@ -33391,7 +33460,7 @@
         <v/>
       </c>
       <c r="H311" s="35" t="e">
-        <f>$F311/$G311</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I311" t="e">
@@ -33410,7 +33479,7 @@
         <v/>
       </c>
       <c r="H312" s="35" t="e">
-        <f>$F312/$G312</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I312" t="e">
@@ -33429,7 +33498,7 @@
         <v/>
       </c>
       <c r="H313" s="35" t="e">
-        <f>$F313/$G313</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I313" t="e">
@@ -33448,7 +33517,7 @@
         <v/>
       </c>
       <c r="H314" s="35" t="e">
-        <f>$F314/$G314</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I314" t="e">
@@ -33467,7 +33536,7 @@
         <v/>
       </c>
       <c r="H315" s="35" t="e">
-        <f>$F315/$G315</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I315" t="e">
@@ -33486,7 +33555,7 @@
         <v/>
       </c>
       <c r="H316" s="35" t="e">
-        <f>$F316/$G316</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I316" t="e">
@@ -33505,7 +33574,7 @@
         <v/>
       </c>
       <c r="H317" s="35" t="e">
-        <f>$F317/$G317</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I317" t="e">
@@ -33524,7 +33593,7 @@
         <v/>
       </c>
       <c r="H318" s="35" t="e">
-        <f>$F318/$G318</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I318" t="e">
@@ -33543,7 +33612,7 @@
         <v/>
       </c>
       <c r="H319" s="35" t="e">
-        <f>$F319/$G319</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I319" t="e">
@@ -33562,7 +33631,7 @@
         <v/>
       </c>
       <c r="H320" s="35" t="e">
-        <f>$F320/$G320</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I320" t="e">
@@ -33581,7 +33650,7 @@
         <v/>
       </c>
       <c r="H321" s="35" t="e">
-        <f>$F321/$G321</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I321" t="e">
@@ -33600,7 +33669,7 @@
         <v/>
       </c>
       <c r="H322" s="35" t="e">
-        <f>$F322/$G322</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I322" t="e">
@@ -33619,7 +33688,7 @@
         <v/>
       </c>
       <c r="H323" s="35" t="e">
-        <f>$F323/$G323</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I323" t="e">
@@ -33638,7 +33707,7 @@
         <v/>
       </c>
       <c r="H324" s="35" t="e">
-        <f>$F324/$G324</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I324" t="e">
@@ -33657,7 +33726,7 @@
         <v/>
       </c>
       <c r="H325" s="35" t="e">
-        <f>$F325/$G325</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I325" t="e">
@@ -33676,7 +33745,7 @@
         <v/>
       </c>
       <c r="H326" s="35" t="e">
-        <f>$F326/$G326</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I326" t="e">
@@ -33695,7 +33764,7 @@
         <v/>
       </c>
       <c r="H327" s="35" t="e">
-        <f>$F327/$G327</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I327" t="e">
@@ -33714,7 +33783,7 @@
         <v/>
       </c>
       <c r="H328" s="35" t="e">
-        <f>$F328/$G328</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I328" t="e">
@@ -33733,7 +33802,7 @@
         <v/>
       </c>
       <c r="H329" s="35" t="e">
-        <f>$F329/$G329</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I329" t="e">
@@ -33752,7 +33821,7 @@
         <v/>
       </c>
       <c r="H330" s="35" t="e">
-        <f>$F330/$G330</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I330" t="e">
@@ -33771,7 +33840,7 @@
         <v/>
       </c>
       <c r="H331" s="35" t="e">
-        <f>$F331/$G331</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I331" t="e">
@@ -33790,7 +33859,7 @@
         <v/>
       </c>
       <c r="H332" s="35" t="e">
-        <f>$F332/$G332</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I332" t="e">
@@ -33809,7 +33878,7 @@
         <v/>
       </c>
       <c r="H333" s="35" t="e">
-        <f>$F333/$G333</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I333" t="e">
@@ -33828,7 +33897,7 @@
         <v/>
       </c>
       <c r="H334" s="35" t="e">
-        <f>$F334/$G334</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I334" t="e">
@@ -33847,7 +33916,7 @@
         <v/>
       </c>
       <c r="H335" s="35" t="e">
-        <f>$F335/$G335</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I335" t="e">
@@ -33866,7 +33935,7 @@
         <v/>
       </c>
       <c r="H336" s="35" t="e">
-        <f>$F336/$G336</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I336" t="e">
@@ -33885,7 +33954,7 @@
         <v/>
       </c>
       <c r="H337" s="35" t="e">
-        <f>$F337/$G337</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I337" t="e">
@@ -33904,7 +33973,7 @@
         <v/>
       </c>
       <c r="H338" s="35" t="e">
-        <f>$F338/$G338</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I338" t="e">
@@ -33923,7 +33992,7 @@
         <v/>
       </c>
       <c r="H339" s="35" t="e">
-        <f>$F339/$G339</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I339" t="e">
@@ -33942,7 +34011,7 @@
         <v/>
       </c>
       <c r="H340" s="35" t="e">
-        <f>$F340/$G340</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I340" t="e">
@@ -33961,7 +34030,7 @@
         <v/>
       </c>
       <c r="H341" s="35" t="e">
-        <f>$F341/$G341</f>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I341" t="e">
@@ -33980,7 +34049,7 @@
         <v/>
       </c>
       <c r="H342" s="35" t="e">
-        <f>$F342/$G342</f>
+        <f t="shared" ref="H342:H405" si="7">$F342/$G342</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I342" t="e">
@@ -33999,7 +34068,7 @@
         <v/>
       </c>
       <c r="H343" s="35" t="e">
-        <f>$F343/$G343</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I343" t="e">
@@ -34018,7 +34087,7 @@
         <v/>
       </c>
       <c r="H344" s="35" t="e">
-        <f>$F344/$G344</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I344" t="e">
@@ -34037,7 +34106,7 @@
         <v/>
       </c>
       <c r="H345" s="35" t="e">
-        <f>$F345/$G345</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I345" t="e">
@@ -34056,7 +34125,7 @@
         <v/>
       </c>
       <c r="H346" s="35" t="e">
-        <f>$F346/$G346</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I346" t="e">
@@ -34075,7 +34144,7 @@
         <v/>
       </c>
       <c r="H347" s="35" t="e">
-        <f>$F347/$G347</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I347" t="e">
@@ -34094,7 +34163,7 @@
         <v/>
       </c>
       <c r="H348" s="35" t="e">
-        <f>$F348/$G348</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I348" t="e">
@@ -34113,7 +34182,7 @@
         <v/>
       </c>
       <c r="H349" s="35" t="e">
-        <f>$F349/$G349</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I349" t="e">
@@ -34132,7 +34201,7 @@
         <v/>
       </c>
       <c r="H350" s="35" t="e">
-        <f>$F350/$G350</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I350" t="e">
@@ -34151,7 +34220,7 @@
         <v/>
       </c>
       <c r="H351" s="35" t="e">
-        <f>$F351/$G351</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I351" t="e">
@@ -34170,7 +34239,7 @@
         <v/>
       </c>
       <c r="H352" s="35" t="e">
-        <f>$F352/$G352</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I352" t="e">
@@ -34189,7 +34258,7 @@
         <v/>
       </c>
       <c r="H353" s="35" t="e">
-        <f>$F353/$G353</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I353" t="e">
@@ -34208,7 +34277,7 @@
         <v/>
       </c>
       <c r="H354" s="35" t="e">
-        <f>$F354/$G354</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I354" t="e">
@@ -34227,7 +34296,7 @@
         <v/>
       </c>
       <c r="H355" s="35" t="e">
-        <f>$F355/$G355</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I355" t="e">
@@ -34246,7 +34315,7 @@
         <v/>
       </c>
       <c r="H356" s="35" t="e">
-        <f>$F356/$G356</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I356" t="e">
@@ -34265,7 +34334,7 @@
         <v/>
       </c>
       <c r="H357" s="35" t="e">
-        <f>$F357/$G357</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I357" t="e">
@@ -34284,7 +34353,7 @@
         <v/>
       </c>
       <c r="H358" s="35" t="e">
-        <f>$F358/$G358</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I358" t="e">
@@ -34303,7 +34372,7 @@
         <v/>
       </c>
       <c r="H359" s="35" t="e">
-        <f>$F359/$G359</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I359" t="e">
@@ -34322,7 +34391,7 @@
         <v/>
       </c>
       <c r="H360" s="35" t="e">
-        <f>$F360/$G360</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I360" t="e">
@@ -34341,7 +34410,7 @@
         <v/>
       </c>
       <c r="H361" s="35" t="e">
-        <f>$F361/$G361</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I361" t="e">
@@ -34360,7 +34429,7 @@
         <v/>
       </c>
       <c r="H362" s="35" t="e">
-        <f>$F362/$G362</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I362" t="e">
@@ -34379,7 +34448,7 @@
         <v/>
       </c>
       <c r="H363" s="35" t="e">
-        <f>$F363/$G363</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I363" t="e">
@@ -34398,7 +34467,7 @@
         <v/>
       </c>
       <c r="H364" s="35" t="e">
-        <f>$F364/$G364</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I364" t="e">
@@ -34417,7 +34486,7 @@
         <v/>
       </c>
       <c r="H365" s="35" t="e">
-        <f>$F365/$G365</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I365" t="e">
@@ -34436,7 +34505,7 @@
         <v/>
       </c>
       <c r="H366" s="35" t="e">
-        <f>$F366/$G366</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I366" t="e">
@@ -34455,7 +34524,7 @@
         <v/>
       </c>
       <c r="H367" s="35" t="e">
-        <f>$F367/$G367</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I367" t="e">
@@ -34474,7 +34543,7 @@
         <v/>
       </c>
       <c r="H368" s="35" t="e">
-        <f>$F368/$G368</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I368" t="e">
@@ -34493,7 +34562,7 @@
         <v/>
       </c>
       <c r="H369" s="35" t="e">
-        <f>$F369/$G369</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I369" t="e">
@@ -34512,7 +34581,7 @@
         <v/>
       </c>
       <c r="H370" s="35" t="e">
-        <f>$F370/$G370</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I370" t="e">
@@ -34531,7 +34600,7 @@
         <v/>
       </c>
       <c r="H371" s="35" t="e">
-        <f>$F371/$G371</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I371" t="e">
@@ -34550,7 +34619,7 @@
         <v/>
       </c>
       <c r="H372" s="35" t="e">
-        <f>$F372/$G372</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I372" t="e">
@@ -34569,7 +34638,7 @@
         <v/>
       </c>
       <c r="H373" s="35" t="e">
-        <f>$F373/$G373</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I373" t="e">
@@ -34588,7 +34657,7 @@
         <v/>
       </c>
       <c r="H374" s="35" t="e">
-        <f>$F374/$G374</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I374" t="e">
@@ -34607,7 +34676,7 @@
         <v/>
       </c>
       <c r="H375" s="35" t="e">
-        <f>$F375/$G375</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I375" t="e">
@@ -34626,7 +34695,7 @@
         <v/>
       </c>
       <c r="H376" s="35" t="e">
-        <f>$F376/$G376</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I376" t="e">
@@ -34645,7 +34714,7 @@
         <v/>
       </c>
       <c r="H377" s="35" t="e">
-        <f>$F377/$G377</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I377" t="e">
@@ -34664,7 +34733,7 @@
         <v/>
       </c>
       <c r="H378" s="35" t="e">
-        <f>$F378/$G378</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I378" t="e">
@@ -34683,7 +34752,7 @@
         <v/>
       </c>
       <c r="H379" s="35" t="e">
-        <f>$F379/$G379</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I379" t="e">
@@ -34702,7 +34771,7 @@
         <v/>
       </c>
       <c r="H380" s="35" t="e">
-        <f>$F380/$G380</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I380" t="e">
@@ -34721,7 +34790,7 @@
         <v/>
       </c>
       <c r="H381" s="35" t="e">
-        <f>$F381/$G381</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I381" t="e">
@@ -34740,7 +34809,7 @@
         <v/>
       </c>
       <c r="H382" s="35" t="e">
-        <f>$F382/$G382</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I382" t="e">
@@ -34759,7 +34828,7 @@
         <v/>
       </c>
       <c r="H383" s="35" t="e">
-        <f>$F383/$G383</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I383" t="e">
@@ -34778,7 +34847,7 @@
         <v/>
       </c>
       <c r="H384" s="35" t="e">
-        <f>$F384/$G384</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I384" t="e">
@@ -34797,7 +34866,7 @@
         <v/>
       </c>
       <c r="H385" s="35" t="e">
-        <f>$F385/$G385</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I385" t="e">
@@ -34816,7 +34885,7 @@
         <v/>
       </c>
       <c r="H386" s="35" t="e">
-        <f>$F386/$G386</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I386" t="e">
@@ -34835,7 +34904,7 @@
         <v/>
       </c>
       <c r="H387" s="35" t="e">
-        <f>$F387/$G387</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I387" t="e">
@@ -34854,7 +34923,7 @@
         <v/>
       </c>
       <c r="H388" s="35" t="e">
-        <f>$F388/$G388</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I388" t="e">
@@ -34873,7 +34942,7 @@
         <v/>
       </c>
       <c r="H389" s="35" t="e">
-        <f>$F389/$G389</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I389" t="e">
@@ -34892,7 +34961,7 @@
         <v/>
       </c>
       <c r="H390" s="35" t="e">
-        <f>$F390/$G390</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I390" t="e">
@@ -34911,7 +34980,7 @@
         <v/>
       </c>
       <c r="H391" s="35" t="e">
-        <f>$F391/$G391</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I391" t="e">
@@ -34930,7 +34999,7 @@
         <v/>
       </c>
       <c r="H392" s="35" t="e">
-        <f>$F392/$G392</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I392" t="e">
@@ -34949,7 +35018,7 @@
         <v/>
       </c>
       <c r="H393" s="35" t="e">
-        <f>$F393/$G393</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I393" t="e">
@@ -34968,7 +35037,7 @@
         <v/>
       </c>
       <c r="H394" s="35" t="e">
-        <f>$F394/$G394</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I394" t="e">
@@ -34987,7 +35056,7 @@
         <v/>
       </c>
       <c r="H395" s="35" t="e">
-        <f>$F395/$G395</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I395" t="e">
@@ -35006,7 +35075,7 @@
         <v/>
       </c>
       <c r="H396" s="35" t="e">
-        <f>$F396/$G396</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I396" t="e">
@@ -35025,7 +35094,7 @@
         <v/>
       </c>
       <c r="H397" s="35" t="e">
-        <f>$F397/$G397</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I397" t="e">
@@ -35044,7 +35113,7 @@
         <v/>
       </c>
       <c r="H398" s="35" t="e">
-        <f>$F398/$G398</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I398" t="e">
@@ -35063,7 +35132,7 @@
         <v/>
       </c>
       <c r="H399" s="35" t="e">
-        <f>$F399/$G399</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I399" t="e">
@@ -35082,7 +35151,7 @@
         <v/>
       </c>
       <c r="H400" s="35" t="e">
-        <f>$F400/$G400</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I400" t="e">
@@ -35101,7 +35170,7 @@
         <v/>
       </c>
       <c r="H401" s="35" t="e">
-        <f>$F401/$G401</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I401" t="e">
@@ -35120,7 +35189,7 @@
         <v/>
       </c>
       <c r="H402" s="35" t="e">
-        <f>$F402/$G402</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I402" t="e">
@@ -35139,7 +35208,7 @@
         <v/>
       </c>
       <c r="H403" s="35" t="e">
-        <f>$F403/$G403</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I403" t="e">
@@ -35158,7 +35227,7 @@
         <v/>
       </c>
       <c r="H404" s="35" t="e">
-        <f>$F404/$G404</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I404" t="e">
@@ -35177,7 +35246,7 @@
         <v/>
       </c>
       <c r="H405" s="35" t="e">
-        <f>$F405/$G405</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I405" t="e">
@@ -35196,7 +35265,7 @@
         <v/>
       </c>
       <c r="H406" s="35" t="e">
-        <f>$F406/$G406</f>
+        <f t="shared" ref="H406:H433" si="8">$F406/$G406</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I406" t="e">
@@ -35215,7 +35284,7 @@
         <v/>
       </c>
       <c r="H407" s="35" t="e">
-        <f>$F407/$G407</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I407" t="e">
@@ -35234,7 +35303,7 @@
         <v/>
       </c>
       <c r="H408" s="35" t="e">
-        <f>$F408/$G408</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I408" t="e">
@@ -35253,7 +35322,7 @@
         <v/>
       </c>
       <c r="H409" s="35" t="e">
-        <f>$F409/$G409</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I409" t="e">
@@ -35272,7 +35341,7 @@
         <v/>
       </c>
       <c r="H410" s="35" t="e">
-        <f>$F410/$G410</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I410" t="e">
@@ -35291,7 +35360,7 @@
         <v/>
       </c>
       <c r="H411" s="35" t="e">
-        <f>$F411/$G411</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I411" t="e">
@@ -35310,7 +35379,7 @@
         <v/>
       </c>
       <c r="H412" s="35" t="e">
-        <f>$F412/$G412</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I412" t="e">
@@ -35329,7 +35398,7 @@
         <v/>
       </c>
       <c r="H413" s="35" t="e">
-        <f>$F413/$G413</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I413" t="e">
@@ -35348,7 +35417,7 @@
         <v/>
       </c>
       <c r="H414" s="35" t="e">
-        <f>$F414/$G414</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I414" t="e">
@@ -35367,7 +35436,7 @@
         <v/>
       </c>
       <c r="H415" s="35" t="e">
-        <f>$F415/$G415</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I415" t="e">
@@ -35386,7 +35455,7 @@
         <v/>
       </c>
       <c r="H416" s="35" t="e">
-        <f>$F416/$G416</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I416" t="e">
@@ -35405,7 +35474,7 @@
         <v/>
       </c>
       <c r="H417" s="35" t="e">
-        <f>$F417/$G417</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I417" t="e">
@@ -35424,7 +35493,7 @@
         <v/>
       </c>
       <c r="H418" s="35" t="e">
-        <f>$F418/$G418</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I418" t="e">
@@ -35443,7 +35512,7 @@
         <v/>
       </c>
       <c r="H419" s="35" t="e">
-        <f>$F419/$G419</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I419" t="e">
@@ -35462,7 +35531,7 @@
         <v/>
       </c>
       <c r="H420" s="35" t="e">
-        <f>$F420/$G420</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I420" t="e">
@@ -35481,7 +35550,7 @@
         <v/>
       </c>
       <c r="H421" s="35" t="e">
-        <f>$F421/$G421</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I421" t="e">
@@ -35500,7 +35569,7 @@
         <v/>
       </c>
       <c r="H422" s="35" t="e">
-        <f>$F422/$G422</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I422" t="e">
@@ -35519,7 +35588,7 @@
         <v/>
       </c>
       <c r="H423" s="35" t="e">
-        <f>$F423/$G423</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I423" t="e">
@@ -35538,7 +35607,7 @@
         <v/>
       </c>
       <c r="H424" s="35" t="e">
-        <f>$F424/$G424</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I424" t="e">
@@ -35557,7 +35626,7 @@
         <v/>
       </c>
       <c r="H425" s="35" t="e">
-        <f>$F425/$G425</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I425" t="e">
@@ -35576,7 +35645,7 @@
         <v/>
       </c>
       <c r="H426" s="35" t="e">
-        <f>$F426/$G426</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I426" t="e">
@@ -35595,7 +35664,7 @@
         <v/>
       </c>
       <c r="H427" s="35" t="e">
-        <f>$F427/$G427</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I427" t="e">
@@ -35614,7 +35683,7 @@
         <v/>
       </c>
       <c r="H428" s="35" t="e">
-        <f>$F428/$G428</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I428" t="e">
@@ -35633,7 +35702,7 @@
         <v/>
       </c>
       <c r="H429" s="35" t="e">
-        <f>$F429/$G429</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I429" t="e">
@@ -35652,7 +35721,7 @@
         <v/>
       </c>
       <c r="H430" s="35" t="e">
-        <f>$F430/$G430</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I430" t="e">
@@ -35671,7 +35740,7 @@
         <v/>
       </c>
       <c r="H431" s="35" t="e">
-        <f>$F431/$G431</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I431" t="e">
@@ -35690,7 +35759,7 @@
         <v/>
       </c>
       <c r="H432" s="35" t="e">
-        <f>$F432/$G432</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I432" t="e">
@@ -35709,7 +35778,7 @@
         <v/>
       </c>
       <c r="H433" s="35" t="e">
-        <f>$F433/$G433</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I433" t="e">
@@ -35957,6 +36026,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" xsi:nil="true"/>
@@ -35965,15 +36043,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -35996,6 +36065,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E919C03E-5A89-47CF-BA2C-50B5836FBD2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22229DF-FCAD-420A-8F03-88F31FF2AFD8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -36010,12 +36087,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E919C03E-5A89-47CF-BA2C-50B5836FBD2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/historico_dados/03 - Mar 2026.xlsx
+++ b/historico_dados/03 - Mar 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JFMELO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DD2604-5AD0-42C3-A5BF-5BAA5DF7C36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB39B66F-4134-4CAF-8DD7-3181CF10DEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="2" activeTab="7" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="2" activeTab="5" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
   </bookViews>
   <sheets>
     <sheet name="TURNOS" sheetId="16" r:id="rId1"/>
@@ -12597,7 +12597,7 @@
   <sheetPr codeName="Planilha7">
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15.26953125" customWidth="1"/>
@@ -12927,7 +12927,7 @@
         <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -12953,7 +12953,7 @@
         <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -13348,6 +13348,9 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E32" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/historico_dados/03 - Mar 2026.xlsx
+++ b/historico_dados/03 - Mar 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JFMELO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB39B66F-4134-4CAF-8DD7-3181CF10DEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD907C2D-7D17-45D0-A506-E6F6D7882F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="2" activeTab="5" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="2" activeTab="9" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
   </bookViews>
   <sheets>
     <sheet name="TURNOS" sheetId="16" r:id="rId1"/>
@@ -22,8 +22,8 @@
     <sheet name="TURMAS" sheetId="5" r:id="rId7"/>
     <sheet name="ALOCAÇÃO_DIÁRIA" sheetId="7" r:id="rId8"/>
     <sheet name="OCUPAÇÃO" sheetId="9" r:id="rId9"/>
-    <sheet name="FALTAS" sheetId="10" r:id="rId10"/>
-    <sheet name="NÃO_REGÊNCIA" sheetId="8" r:id="rId11"/>
+    <sheet name="NÃO_REGÊNCIA" sheetId="8" r:id="rId10"/>
+    <sheet name="FALTAS" sheetId="10" r:id="rId11"/>
     <sheet name="RESUMO" sheetId="11" r:id="rId12"/>
     <sheet name="PARÂMETROS" sheetId="12" r:id="rId13"/>
     <sheet name="MANUAL" sheetId="13" r:id="rId14"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="244">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -549,9 +549,6 @@
     <t>TIPO_ATIVIDADE</t>
   </si>
   <si>
-    <t>COMPROVANTE</t>
-  </si>
-  <si>
     <t>PAINEL DE CONTROLE - DIGITECH</t>
   </si>
   <si>
@@ -806,6 +803,12 @@
   <si>
     <t>FINALIZADO</t>
   </si>
+  <si>
+    <t>DATA_FIM</t>
+  </si>
+  <si>
+    <t>Outros</t>
+  </si>
 </sst>
 </file>
 
@@ -1054,7 +1057,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1146,11 +1149,15 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="67">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1178,6 +1185,9 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1606,26 +1616,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}" name="tblTurnos" displayName="tblTurnos" ref="A2:E5" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60" tableBorderDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}" name="tblTurnos" displayName="tblTurnos" ref="A2:E5" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62" tableBorderDxfId="61">
   <autoFilter ref="A2:E5" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{66C8A751-944C-4ED0-9B93-7EF7890BAC2C}" name="ID_TURNO" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{CE79B6B8-84BE-42CD-8597-D513FB5454F3}" name="TURNO" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{72B36434-A91F-4B46-ABFB-CA8660948243}" name="HORARIO_INICIO" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{39895036-CC40-4170-867E-4FB900291AD1}" name="HORARIO_FIM" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{883890C6-E58B-43F9-93BF-FE0182EAC856}" name="DESCRICAO" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{66C8A751-944C-4ED0-9B93-7EF7890BAC2C}" name="ID_TURNO" dataDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{CE79B6B8-84BE-42CD-8597-D513FB5454F3}" name="TURNO" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{72B36434-A91F-4B46-ABFB-CA8660948243}" name="HORARIO_INICIO" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{39895036-CC40-4170-867E-4FB900291AD1}" name="HORARIO_FIM" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{883890C6-E58B-43F9-93BF-FE0182EAC856}" name="DESCRICAO" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A986751A-B0FE-4DB2-A339-752A82C8EBB2}" name="tblNaoRegencia" displayName="tblNaoRegencia" ref="A1:G40" totalsRowShown="0">
+  <autoFilter ref="A1:G40" xr:uid="{A986751A-B0FE-4DB2-A339-752A82C8EBB2}"/>
+  <tableColumns count="7">
+    <tableColumn id="3" xr3:uid="{C41BC749-29FB-4B6F-9EA2-D96ADD02E462}" name="ID_INSTRUTOR" dataDxfId="5">
+      <calculatedColumnFormula>_xlfn.XLOOKUP($B2,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{365EBB65-AF80-4E7B-89A4-79CE5F2AB432}" name="INSTRUTOR"/>
+    <tableColumn id="9" xr3:uid="{D3DE3AAD-CD37-4E63-97AA-798CAE59423B}" name="DATA_INICIO"/>
+    <tableColumn id="10" xr3:uid="{DC38F51D-F55B-4FCE-9DEB-F22E95157356}" name="DATA_FIM"/>
+    <tableColumn id="4" xr3:uid="{11EF8702-E803-4685-B2C8-3A78BE4767F1}" name="HORAS_NAO_REGENCIA" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{78F32153-EFD3-4A0D-9B3E-4F5A0AC4EA03}" name="TIPO_ATIVIDADE"/>
+    <tableColumn id="6" xr3:uid="{C209715A-6D68-4CB2-BE03-6EB9D41B3128}" name="DESCRICAO"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{0F6C7BFB-45B8-4BFA-AB59-9109CD030669}" name="Tabela13" displayName="Tabela13" ref="A1:J11" totalsRowShown="0">
   <autoFilter ref="A1:J11" xr:uid="{0F6C7BFB-45B8-4BFA-AB59-9109CD030669}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{777D8F4B-4E54-4D25-85CD-95A1C29201CF}" name="ID_REGISTRO"/>
     <tableColumn id="2" xr3:uid="{1A2EBCBF-6DF1-4D28-BEBD-4DF70127CC32}" name="DATA_FALTA"/>
-    <tableColumn id="3" xr3:uid="{B600ED18-D3EA-436F-973D-8F725213B25C}" name="ID_INSTRUTOR" dataDxfId="6">
+    <tableColumn id="3" xr3:uid="{B600ED18-D3EA-436F-973D-8F725213B25C}" name="ID_INSTRUTOR" dataDxfId="8">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{D5F1B6E7-37B8-4C25-AB78-D9B4DF386F26}" name="INSTRUTOR"/>
@@ -1640,64 +1668,48 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A986751A-B0FE-4DB2-A339-752A82C8EBB2}" name="tblNaoRegencia" displayName="tblNaoRegencia" ref="A1:G40" totalsRowShown="0">
-  <autoFilter ref="A1:G40" xr:uid="{A986751A-B0FE-4DB2-A339-752A82C8EBB2}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E9DABB67-6AA0-43BF-B3CF-BAD955ACE729}" name="ID_REGISTRO"/>
-    <tableColumn id="2" xr3:uid="{BB8D80A5-1C0A-43CD-A22C-C2A2A8895922}" name="DATA"/>
-    <tableColumn id="3" xr3:uid="{C41BC749-29FB-4B6F-9EA2-D96ADD02E462}" name="ID_INSTRUTOR"/>
-    <tableColumn id="4" xr3:uid="{11EF8702-E803-4685-B2C8-3A78BE4767F1}" name="HORAS_NAO_REGENCIA"/>
-    <tableColumn id="5" xr3:uid="{78F32153-EFD3-4A0D-9B3E-4F5A0AC4EA03}" name="TIPO_ATIVIDADE"/>
-    <tableColumn id="6" xr3:uid="{C209715A-6D68-4CB2-BE03-6EB9D41B3128}" name="DESCRICAO"/>
-    <tableColumn id="7" xr3:uid="{8EAAF247-EE34-4B02-90DA-5B6AC1617728}" name="COMPROVANTE"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{75F20B93-93C1-46B3-8F69-45B7FBEB31A8}" name="Tabela16" displayName="Tabela16" ref="A10:C21" totalsRowShown="0">
   <autoFilter ref="A10:C21" xr:uid="{75F20B93-93C1-46B3-8F69-45B7FBEB31A8}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{864AACEE-78FA-40CC-AD13-56D3C344A2D4}" name="PARÂMETRO"/>
-    <tableColumn id="2" xr3:uid="{57E86055-2CCE-4631-9A08-ED866B3C8B9D}" name="VALOR" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{A0FFA1C2-5301-484A-A146-CFB1C2F7E495}" name="DESCRIÇÃO" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{57E86055-2CCE-4631-9A08-ED866B3C8B9D}" name="VALOR" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{A0FFA1C2-5301-484A-A146-CFB1C2F7E495}" name="DESCRIÇÃO" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}" name="tblModalidades" displayName="tblModalidades" ref="A2:D4" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}" name="tblModalidades" displayName="tblModalidades" ref="A2:D4" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A2:D4" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B42A8C1C-387F-4E3D-A54F-CF1D913A6676}" name="ID_MODALIDADE" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{409E0C8E-C00D-45B9-8113-E86B37049A97}" name="MODALIDADE" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{9B83D5E8-C0D6-41D3-A5EB-27263A3A1DDA}" name="TIPO" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{D7FE0EEE-44EA-4C6B-B889-B4C030F1B758}" name=" DESCRICAO" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{B42A8C1C-387F-4E3D-A54F-CF1D913A6676}" name="ID_MODALIDADE" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{409E0C8E-C00D-45B9-8113-E86B37049A97}" name="MODALIDADE" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{9B83D5E8-C0D6-41D3-A5EB-27263A3A1DDA}" name="TIPO" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{D7FE0EEE-44EA-4C6B-B889-B4C030F1B758}" name=" DESCRICAO" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}" name="tblCalendario" displayName="tblCalendario" ref="A1:G366" totalsRowShown="0" dataDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}" name="tblCalendario" displayName="tblCalendario" ref="A1:G366" totalsRowShown="0" dataDxfId="49">
   <autoFilter ref="A1:G366" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F779E569-925E-439D-B1E1-8D86C934DF94}" name="DATA" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{9910EA8A-79F0-4CBA-B0EA-76C6A01D1DA2}" name="DIA_SEMANA" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{F779E569-925E-439D-B1E1-8D86C934DF94}" name="DATA" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{9910EA8A-79F0-4CBA-B0EA-76C6A01D1DA2}" name="DIA_SEMANA" dataDxfId="47">
       <calculatedColumnFormula>TEXT(A2,"dddd")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B5623804-AA40-4BA7-B2EB-75E1D43E1DDA}" name="MÊS" dataDxfId="44">
+    <tableColumn id="3" xr3:uid="{B5623804-AA40-4BA7-B2EB-75E1D43E1DDA}" name="MÊS" dataDxfId="46">
       <calculatedColumnFormula>TEXT(A2,"mmmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{353E7915-D743-4718-B4A3-CE0D53F4A516}" name="ANO" dataDxfId="43">
+    <tableColumn id="4" xr3:uid="{353E7915-D743-4718-B4A3-CE0D53F4A516}" name="ANO" dataDxfId="45">
       <calculatedColumnFormula>YEAR(A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{816AC587-9819-42DF-80FD-264F991CF8F3}" name="TIPO_DIA" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{7A6D793C-B684-4E23-A357-D584AE0AC6FD}" name="DESCRICAO" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{5B786348-03B6-441E-A7B1-194F3AA43107}" name="DIA_UTIL" dataDxfId="40">
+    <tableColumn id="5" xr3:uid="{816AC587-9819-42DF-80FD-264F991CF8F3}" name="TIPO_DIA" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{7A6D793C-B684-4E23-A357-D584AE0AC6FD}" name="DESCRICAO" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{5B786348-03B6-441E-A7B1-194F3AA43107}" name="DIA_UTIL" dataDxfId="42">
       <calculatedColumnFormula>IF(OR(E2="Feriado",E2="Recesso",B2="domingo",B2="sábado"),"NÃO","SIM")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1706,41 +1718,41 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}" name="tblInstrutores" displayName="tblInstrutores" ref="A1:I14" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36" totalsRowBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}" name="tblInstrutores" displayName="tblInstrutores" ref="A1:I14" totalsRowShown="0" headerRowDxfId="41" dataDxfId="39" headerRowBorderDxfId="40" tableBorderDxfId="38" totalsRowBorderDxfId="37">
   <autoFilter ref="A1:I14" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G14">
     <sortCondition ref="B1:B14"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E0F79A67-2297-4B4A-A8E9-7102EE99B694}" name="ID" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{E0F79A67-2297-4B4A-A8E9-7102EE99B694}" name="ID" dataDxfId="36">
       <calculatedColumnFormula>IF(B2&lt;&gt;"",ROW()-1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{532A9770-E647-4D50-B202-8BBE5806648D}" name="NOME_COMPLETO" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{DD24D10E-34AA-4D8E-B5F7-9B0E7D84B23A}" name="NOME_PADRONIZADO" dataDxfId="32">
+    <tableColumn id="2" xr3:uid="{532A9770-E647-4D50-B202-8BBE5806648D}" name="NOME_COMPLETO" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{DD24D10E-34AA-4D8E-B5F7-9B0E7D84B23A}" name="NOME_PADRONIZADO" dataDxfId="34">
       <calculatedColumnFormula>UPPER(B2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0DC783F1-8A1B-443E-A9AF-DB40A28DED0F}" name="STATUS" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{8E33C3CA-EB70-43F9-B178-A5FD7FB25151}" name="TELEFONE" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{6BB804C3-6D00-4CBA-AADC-80AA2AA5F0B3}" name="EMAIL" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{066724F8-E631-4356-AF06-A44B57F600FB}" name="CARGA_HORARIA_SEMANAL" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{18D3697E-D2C6-4E06-9624-B784D6581D8D}" name="HABILITADO_EAD" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{0523A053-C6F6-4529-94E2-81C8ABD9D627}" name="OBSERVAÇÃO" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{0DC783F1-8A1B-443E-A9AF-DB40A28DED0F}" name="STATUS" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{8E33C3CA-EB70-43F9-B178-A5FD7FB25151}" name="TELEFONE" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{6BB804C3-6D00-4CBA-AADC-80AA2AA5F0B3}" name="EMAIL" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{066724F8-E631-4356-AF06-A44B57F600FB}" name="CARGA_HORARIA_SEMANAL" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{18D3697E-D2C6-4E06-9624-B784D6581D8D}" name="HABILITADO_EAD" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{0523A053-C6F6-4529-94E2-81C8ABD9D627}" name="OBSERVAÇÃO" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}" name="tblAmbientes" displayName="tblAmbientes" ref="A1:E17" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}" name="tblAmbientes" displayName="tblAmbientes" ref="A1:E17" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:E17" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4CC770AA-6DA6-4EFC-AAF1-5A329E637763}" name="ID" dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{4CC770AA-6DA6-4EFC-AAF1-5A329E637763}" name="ID" dataDxfId="25">
       <calculatedColumnFormula>IF(B2&lt;&gt;"",ROW()-1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B3952270-EACA-4683-9C35-CB58270B3617}" name="NOME_AMBIENTE" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{1B401582-0E5F-494F-8433-828BC136B12C}" name="TIPO" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{81780B59-8350-421A-B267-D808DA35B87C}" name="CAPACIDADE" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{7A3E5A22-F966-4BA3-A1AA-3C3AF64EA9D1}" name="VIRTUAL" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{B3952270-EACA-4683-9C35-CB58270B3617}" name="NOME_AMBIENTE" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{1B401582-0E5F-494F-8433-828BC136B12C}" name="TIPO" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{81780B59-8350-421A-B267-D808DA35B87C}" name="CAPACIDADE" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{7A3E5A22-F966-4BA3-A1AA-3C3AF64EA9D1}" name="VIRTUAL" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1750,14 +1762,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{27B64AF7-6011-40DE-B8EB-AFCA2AA948F7}" name="tblDisciplinas" displayName="tblDisciplinas" ref="A2:G29" totalsRowShown="0">
   <autoFilter ref="A2:G29" xr:uid="{27B64AF7-6011-40DE-B8EB-AFCA2AA948F7}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EAB3743F-4C6C-47DC-9FAE-3B30927E6D25}" name="ID_DISCIPLINA" dataDxfId="64">
+    <tableColumn id="1" xr3:uid="{EAB3743F-4C6C-47DC-9FAE-3B30927E6D25}" name="ID_DISCIPLINA" dataDxfId="66">
       <calculatedColumnFormula>IF(E3&lt;&gt;"",ROW()-2,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{AB44C0DC-4B9E-4D40-B9CB-D5B9E3AB1664}" name="ID_TURMA" dataDxfId="63">
+    <tableColumn id="7" xr3:uid="{AB44C0DC-4B9E-4D40-B9CB-D5B9E3AB1664}" name="ID_TURMA" dataDxfId="65">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{71F544AA-7A31-4153-B640-2C9D09A01400}" name="TURMA"/>
-    <tableColumn id="10" xr3:uid="{6CF7FD1A-08A6-4FC7-8349-E61A732E9B9A}" name="NOME_TURMA" dataDxfId="62">
+    <tableColumn id="10" xr3:uid="{6CF7FD1A-08A6-4FC7-8349-E61A732E9B9A}" name="NOME_TURMA" dataDxfId="64">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{912B15BB-5B7F-4D54-B4D5-F1F5D64871C5}" name="NOME_DISCIPLINA"/>
@@ -1777,7 +1789,7 @@
     </tableColumn>
     <tableColumn id="2" xr3:uid="{9042D9C0-8F8C-48B8-A00F-4C204966A3E0}" name="CODIGO_TURMA"/>
     <tableColumn id="3" xr3:uid="{52BE2282-DBEE-432A-AC2C-DC3B0ED8155A}" name="NOME_TURMA"/>
-    <tableColumn id="5" xr3:uid="{06615BCB-121E-4F31-B9B5-41FF315BB778}" name="TURNO_ID" dataDxfId="18">
+    <tableColumn id="5" xr3:uid="{06615BCB-121E-4F31-B9B5-41FF315BB778}" name="TURNO_ID" dataDxfId="20">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblTurmas[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"EAD")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{4EBD83E6-0B0C-4F35-A90C-A43846EF4AD7}" name="TURNO"/>
@@ -1785,11 +1797,11 @@
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblTurmas[[#This Row],[MODALIDADE]],tblModalidades[MODALIDADE],tblModalidades[ID_MODALIDADE],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{45019BB0-F00A-4841-B863-EADDA64FC073}" name="MODALIDADE"/>
-    <tableColumn id="7" xr3:uid="{3D7E20E2-253B-4213-AC29-E1EE298912E2}" name="INSTRUTOR_TITULAR_ID" dataDxfId="17">
+    <tableColumn id="7" xr3:uid="{3D7E20E2-253B-4213-AC29-E1EE298912E2}" name="INSTRUTOR_TITULAR_ID" dataDxfId="19">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblTurmas[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{726835D8-8590-4D8B-97A6-670FB141BB4A}" name="INSTRUTOR"/>
-    <tableColumn id="16" xr3:uid="{52F17429-0E2C-4104-A78C-B8A56B97D414}" name="INTERVALO" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{52F17429-0E2C-4104-A78C-B8A56B97D414}" name="INTERVALO" dataDxfId="18"/>
     <tableColumn id="8" xr3:uid="{7B506599-94E7-4BA6-923F-386276DF3202}" name="DATA_INICIO"/>
     <tableColumn id="9" xr3:uid="{866256CA-7D34-41C1-9129-54C37C321CC0}" name="DATA_TERMINO"/>
     <tableColumn id="10" xr3:uid="{0E26EE9C-AEBF-445F-8B55-F7FADC6B5484}" name="CARGA_HORARIA_TOTAL"/>
@@ -1810,21 +1822,21 @@
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{26F01CA8-27CA-45E7-9496-4DA4C5DFB112}" name="ID_REGISTRO"/>
     <tableColumn id="2" xr3:uid="{6088C19C-60C3-49FB-8F36-E5D675187300}" name="DATA"/>
-    <tableColumn id="3" xr3:uid="{3DC9D8EE-0F77-4D9D-9274-DA5AD82CB9F9}" name="ID_TURMA" dataDxfId="15">
+    <tableColumn id="3" xr3:uid="{3DC9D8EE-0F77-4D9D-9274-DA5AD82CB9F9}" name="ID_TURMA" dataDxfId="17">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{69C05D6F-11A8-41E4-BF05-975BC4334AAB}" name="TURMA"/>
-    <tableColumn id="4" xr3:uid="{97A3E5B6-9CDC-4E51-AE20-35E2DE45AA9A}" name="ID_DISCIPLINA" dataDxfId="14">
+    <tableColumn id="4" xr3:uid="{97A3E5B6-9CDC-4E51-AE20-35E2DE45AA9A}" name="ID_DISCIPLINA" dataDxfId="16">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{8DAD9F82-DD32-4FF1-98DE-3BDCE0BEF7CE}" name="DISCIPLINA"/>
     <tableColumn id="5" xr3:uid="{36091ABA-AD8F-4375-86D2-9948DD4B8EA9}" name="ID_INSTRUTOR">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3964019F-EE8B-4430-B64E-C4B65E0A0B14}" name="Nome do Instrutor" dataDxfId="13">
+    <tableColumn id="17" xr3:uid="{3964019F-EE8B-4430-B64E-C4B65E0A0B14}" name="Nome do Instrutor" dataDxfId="15">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9E706770-192A-4CAD-A05F-050FCE1A954E}" name="ID_AMBIENTE" dataDxfId="12">
+    <tableColumn id="6" xr3:uid="{9E706770-192A-4CAD-A05F-050FCE1A954E}" name="ID_AMBIENTE" dataDxfId="14">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{41027BFC-EF08-4BA8-8911-CFB5D8B98B49}" name="AMBIENTE"/>
@@ -1840,7 +1852,7 @@
     <tableColumn id="19" xr3:uid="{5BE338C7-2CC7-4995-926D-03143942C848}" name="MODALIDADE"/>
     <tableColumn id="9" xr3:uid="{A9B3487C-55C6-4A27-BFD0-0AB086E6F16B}" name="HORA_INICIO"/>
     <tableColumn id="10" xr3:uid="{C8D6EDFC-0B0B-4FA8-8394-B10AA39F7E29}" name="HORA_FIM"/>
-    <tableColumn id="11" xr3:uid="{BA775167-444E-4E8B-B869-8FA82AF18593}" name="HORAS_AULA" dataDxfId="11">
+    <tableColumn id="11" xr3:uid="{BA775167-444E-4E8B-B869-8FA82AF18593}" name="HORAS_AULA" dataDxfId="13">
       <calculatedColumnFormula>($P2-$O2)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{1EDB8525-12A6-4FFF-8C85-2E2B0308588A}" name="ALUNOS_PRESENTES"/>
@@ -1859,20 +1871,20 @@
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5D64B531-2B5A-41D2-B091-C2501106A810}" name="DATA"/>
-    <tableColumn id="2" xr3:uid="{E9D5B192-1664-4C44-B817-5E2787B1BC2A}" name="ID_AMBIENTE" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{E9D5B192-1664-4C44-B817-5E2787B1BC2A}" name="ID_AMBIENTE" dataDxfId="12">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{9B86429E-88A3-4A51-9ADE-42121DFF9A4F}" name="AMBIENTE"/>
-    <tableColumn id="3" xr3:uid="{A6F82553-3DDB-44D4-B09C-992245966256}" name="ID_TURNO" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{A6F82553-3DDB-44D4-B09C-992245966256}" name="ID_TURNO" dataDxfId="11">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{F6EE1A7F-593B-4E0D-9EB0-B6F92EECEB1A}" name="TURNO"/>
     <tableColumn id="4" xr3:uid="{1B094B40-F0E2-41B0-B80F-4FF2EF76E0D3}" name="VAGAS_OCUPADAS"/>
     <tableColumn id="5" xr3:uid="{1FD6B13D-1B7D-455A-B4FD-6C50EEF76002}" name="CAPACIDADE"/>
-    <tableColumn id="6" xr3:uid="{88504BEB-A991-46C1-882A-53CD6D3C4827}" name="PERCENTUAL_OCUPACAO" dataDxfId="8">
+    <tableColumn id="6" xr3:uid="{88504BEB-A991-46C1-882A-53CD6D3C4827}" name="PERCENTUAL_OCUPACAO" dataDxfId="10">
       <calculatedColumnFormula>$F2/$G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BA85A04D-3459-4AE3-9651-7E97C4D7BAE6}" name="STATUS_OCUPACAO" dataDxfId="7">
+    <tableColumn id="7" xr3:uid="{BA85A04D-3459-4AE3-9651-7E97C4D7BAE6}" name="STATUS_OCUPACAO" dataDxfId="9">
       <calculatedColumnFormula>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{482E2A7F-5074-4E85-B850-719BFEAA3756}" name="TIPO_AMBIENTE"/>
@@ -2280,6 +2292,414 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC70C86E-351D-46E2-B1CA-FA4E1FF141AE}">
+  <sheetPr codeName="Planilha11">
+    <tabColor theme="5" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.54296875" customWidth="1"/>
+    <col min="5" max="5" width="23.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <f>_xlfn.XLOOKUP($B2,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46108</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E2" s="44">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <f>_xlfn.XLOOKUP($B3,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46083</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46108</v>
+      </c>
+      <c r="E3" s="44">
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <f>_xlfn.XLOOKUP($B4,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46084</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46111</v>
+      </c>
+      <c r="E4" s="44">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <f>_xlfn.XLOOKUP($B5,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46092</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E5" s="44">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <f>_xlfn.XLOOKUP($B6,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46107</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46107</v>
+      </c>
+      <c r="E6" s="44">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="e">
+        <f>_xlfn.XLOOKUP($B7,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E7" s="44"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="e">
+        <f>_xlfn.XLOOKUP($B8,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E8" s="44"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="e">
+        <f>_xlfn.XLOOKUP($B9,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E9" s="44"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="e">
+        <f>_xlfn.XLOOKUP($B10,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E10" s="44"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="e">
+        <f>_xlfn.XLOOKUP($B11,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" s="44"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="e">
+        <f>_xlfn.XLOOKUP($B12,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E12" s="44"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="e">
+        <f>_xlfn.XLOOKUP($B13,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" s="44"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="e">
+        <f>_xlfn.XLOOKUP($B14,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="44"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="e">
+        <f>_xlfn.XLOOKUP($B15,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="44"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="e">
+        <f>_xlfn.XLOOKUP($B16,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="44"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="e">
+        <f>_xlfn.XLOOKUP($B17,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" s="44"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="e">
+        <f>_xlfn.XLOOKUP($B18,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E18" s="44"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="e">
+        <f>_xlfn.XLOOKUP($B19,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E19" s="44"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="e">
+        <f>_xlfn.XLOOKUP($B20,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E20" s="44"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="e">
+        <f>_xlfn.XLOOKUP($B21,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="44"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="e">
+        <f>_xlfn.XLOOKUP($B22,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E22" s="44"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="e">
+        <f>_xlfn.XLOOKUP($B23,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E23" s="44"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="e">
+        <f>_xlfn.XLOOKUP($B24,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E24" s="44"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="e">
+        <f>_xlfn.XLOOKUP($B25,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E25" s="44"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="e">
+        <f>_xlfn.XLOOKUP($B26,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E26" s="44"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="e">
+        <f>_xlfn.XLOOKUP($B27,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E27" s="44"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="e">
+        <f>_xlfn.XLOOKUP($B28,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E28" s="44"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="e">
+        <f>_xlfn.XLOOKUP($B29,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E29" s="44"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="e">
+        <f>_xlfn.XLOOKUP($B30,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E30" s="44"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="e">
+        <f>_xlfn.XLOOKUP($B31,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E31" s="44"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="e">
+        <f>_xlfn.XLOOKUP($B32,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E32" s="44"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="e">
+        <f>_xlfn.XLOOKUP($B33,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E33" s="44"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="e">
+        <f>_xlfn.XLOOKUP($B34,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E34" s="44"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="e">
+        <f>_xlfn.XLOOKUP($B35,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E35" s="44"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="e">
+        <f>_xlfn.XLOOKUP($B36,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E36" s="44"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="e">
+        <f>_xlfn.XLOOKUP($B37,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E37" s="44"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="e">
+        <f>_xlfn.XLOOKUP($B38,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E38" s="44"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="e">
+        <f>_xlfn.XLOOKUP($B39,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E39" s="44"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="e">
+        <f>_xlfn.XLOOKUP($B40,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E40" s="44"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F40" xr:uid="{6377533E-C9E5-44E7-A2B7-0BF25F3F89F1}">
+      <formula1>"Reunião Pedagógica, Capacitação, Planejamento, Correção, Outros"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{19C827CB-D1B7-438F-A826-696BB8365317}">
+          <x14:formula1>
+            <xm:f>INSTRUTORES!$B$2:$B$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B40</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684CBFF6-9D73-4BD7-B23B-101155BBD0C0}">
   <sheetPr codeName="Planilha10"/>
   <dimension ref="A1:M11"/>
@@ -2307,7 +2727,7 @@
         <v>138</v>
       </c>
       <c r="D1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E1" t="s">
         <v>121</v>
@@ -2445,189 +2865,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC70C86E-351D-46E2-B1CA-FA4E1FF141AE}">
-  <sheetPr codeName="Planilha11"/>
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
-    <col min="4" max="4" width="23.26953125" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B28" s="2"/>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B30" s="2"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B36" s="2"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B37" s="2"/>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B38" s="2"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B39" s="2"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B40" s="2"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E40" xr:uid="{6377533E-C9E5-44E7-A2B7-0BF25F3F89F1}">
-      <formula1>"Reunião Pedagógica, Capacitação, Planejamento, Correção, Outros"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G40" xr:uid="{DFED99B8-481A-4B62-9B7D-3B9D28038AEC}">
-      <formula1>"SIM, NÃO"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB5227ED-5C4E-419F-A8F5-7352F7381351}">
-          <x14:formula1>
-            <xm:f>INSTRUTORES!$A$2:$A$14</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C40</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D5CEDE-0B35-481C-9C61-8FE3DCD1B21E}">
   <sheetPr codeName="Planilha12">
@@ -2642,12 +2879,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B3" s="2">
         <f ca="1">TODAY()</f>
@@ -2656,15 +2893,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B6">
         <f>COUNTA(tblInstrutores[ID])</f>
@@ -2673,7 +2910,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B7">
         <f>COUNTA(tbl)</f>
@@ -2682,7 +2919,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B8">
         <f>COUNTIFS(tblAmbientes[VIRTUAL],"NÃO")</f>
@@ -2691,7 +2928,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B9">
         <f ca="1">COUNTIFS(tblAlocacao[DATA], TODAY())</f>
@@ -2700,7 +2937,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B10" t="e" cm="1">
         <f t="array" ref="B10">AVERAGE(tblOcupacao[PERCENTUAL_OCUPACAO],ROWS(tblOcupacao[PERCENTUAL_OCUPACAO]-1))</f>
@@ -2709,16 +2946,16 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B11">
         <f>SUM(tblNaoRegencia[HORAS_NAO_REGENCIA])</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B12" t="e">
         <f>SUM(tblNaoRegencia[HORAS_NAO_REGENCIA])/(SUM(tblAlocacao[HORAS_AULA])+SUM(tblNaoRegencia[HORAS_NAO_REGENCIA]))</f>
@@ -2727,15 +2964,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B15" s="4">
         <f>AVERAGEIFS(tblOcupacao[PERCENTUAL_OCUPACAO], tblOcupacao[ID_TURNO], 1)</f>
@@ -2744,7 +2981,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B16" s="4" t="e">
         <f>AVERAGEIFS(tblOcupacao[PERCENTUAL_OCUPACAO], tblOcupacao[ID_TURNO], 2)</f>
@@ -2753,7 +2990,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B17" s="4" t="e">
         <f>AVERAGEIFS(tblOcupacao[PERCENTUAL_OCUPACAO], tblOcupacao[ID_TURNO], 3)</f>
@@ -2778,10 +3015,10 @@
   <sheetData>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" t="s">
         <v>174</v>
-      </c>
-      <c r="B10" t="s">
-        <v>175</v>
       </c>
       <c r="C10" t="s">
         <v>0</v>
@@ -2789,62 +3026,62 @@
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B11" s="5">
         <v>0.7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B12" s="5">
         <v>0.85</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B13" s="5">
         <v>0.3</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B14">
         <v>44</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15">
         <v>7</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" s="1">
         <v>0.33333333333333331</v>
@@ -2853,7 +3090,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" s="1">
         <v>0.5</v>
@@ -2862,7 +3099,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B18" s="1">
         <v>0.54166666666666663</v>
@@ -2871,7 +3108,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B19" s="1">
         <v>0.70833333333333337</v>
@@ -2880,7 +3117,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B20" s="1">
         <v>0.75</v>
@@ -2889,7 +3126,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B21" s="1">
         <v>0.91666666666666663</v>
@@ -2926,130 +3163,130 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" s="37" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" s="37" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="37" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" s="37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4906,10 +5143,10 @@
         <v>2026</v>
       </c>
       <c r="E71" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>201</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>202</v>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="4"/>
@@ -11827,16 +12064,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:G366">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$E2="Feriado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$E2="Recesso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>OR($B2="sábado",$B2="domingo")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$G2="SIM"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11872,7 +12109,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C1" s="19" t="s">
         <v>50</v>
@@ -12011,7 +12248,7 @@
         <v>61</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -12187,7 +12424,7 @@
         <v>61</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -12247,7 +12484,7 @@
         <v>61</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -12611,7 +12848,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.6">
       <c r="A1" s="42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -12629,7 +12866,7 @@
         <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D2" t="s">
         <v>123</v>
@@ -12654,20 +12891,20 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D3" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Programador Full Stack</v>
       </c>
       <c r="E3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F3">
         <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -12680,20 +12917,20 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D4" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Programador Full Stack</v>
       </c>
       <c r="E4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F4">
         <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -12706,20 +12943,20 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D5" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Programador Full Stack</v>
       </c>
       <c r="E5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F5">
         <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -12732,20 +12969,20 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D6" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Programador Full Stack</v>
       </c>
       <c r="E6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F6">
         <v>60</v>
       </c>
       <c r="G6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -12758,20 +12995,20 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D7" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Programador Full Stack</v>
       </c>
       <c r="E7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F7">
         <v>60</v>
       </c>
       <c r="G7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -12784,20 +13021,20 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D8" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Programador Full Stack</v>
       </c>
       <c r="E8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F8">
         <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -12810,20 +13047,20 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D9" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Programador Full Stack</v>
       </c>
       <c r="E9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F9">
         <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -12836,20 +13073,20 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D10" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Programador Full Stack</v>
       </c>
       <c r="E10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F10">
         <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -12862,20 +13099,20 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D11" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Programador Full Stack</v>
       </c>
       <c r="E11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F11">
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -12888,20 +13125,20 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D12" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F12">
         <v>60</v>
       </c>
       <c r="G12" s="40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -12914,20 +13151,20 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D13" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F13">
         <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -12940,20 +13177,20 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D14" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F14">
         <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -12966,20 +13203,20 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D15" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F15">
         <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -12992,20 +13229,20 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D16" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F16">
         <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -13018,20 +13255,20 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D17" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F17">
         <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -13044,20 +13281,20 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D18" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F18">
         <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -13070,20 +13307,20 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F19">
         <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -13096,20 +13333,20 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F20">
         <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -13122,20 +13359,20 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D21" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F21">
         <v>60</v>
       </c>
       <c r="G21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -13148,20 +13385,20 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F22">
         <v>60</v>
       </c>
       <c r="G22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -13174,20 +13411,20 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F23">
         <v>60</v>
       </c>
       <c r="G23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -13200,20 +13437,20 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F24">
         <v>60</v>
       </c>
       <c r="G24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -13226,20 +13463,20 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E25" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F25">
         <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -13252,20 +13489,20 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F26">
         <v>60</v>
       </c>
       <c r="G26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -13278,20 +13515,20 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E27" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F27">
         <v>60</v>
       </c>
       <c r="G27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -13304,20 +13541,20 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F28">
         <v>60</v>
       </c>
       <c r="G28" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -13330,20 +13567,20 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F29">
         <v>60</v>
       </c>
       <c r="G29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -13432,10 +13669,10 @@
         <v>126</v>
       </c>
       <c r="I1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K1" t="s">
         <v>127</v>
@@ -13499,7 +13736,7 @@
         <v>364</v>
       </c>
       <c r="P2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
@@ -13508,10 +13745,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" t="s">
         <v>194</v>
-      </c>
-      <c r="C3" t="s">
-        <v>195</v>
       </c>
       <c r="D3">
         <f>_xlfn.XLOOKUP(tblTurmas[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"EAD")</f>
@@ -13553,7 +13790,7 @@
         <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
@@ -13562,10 +13799,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" t="s">
         <v>203</v>
-      </c>
-      <c r="C4" t="s">
-        <v>204</v>
       </c>
       <c r="D4">
         <f>_xlfn.XLOOKUP(tblTurmas[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"EAD")</f>
@@ -13607,7 +13844,7 @@
         <v>15</v>
       </c>
       <c r="P4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -13680,31 +13917,31 @@
         <v>121</v>
       </c>
       <c r="D1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E1" t="s">
         <v>134</v>
       </c>
       <c r="F1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G1" t="s">
         <v>138</v>
       </c>
       <c r="H1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I1" t="s">
         <v>139</v>
       </c>
       <c r="J1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K1" t="s">
         <v>2</v>
       </c>
       <c r="L1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M1" t="s">
         <v>14</v>
@@ -13743,14 +13980,14 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E2">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F2" s="40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G2">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -13796,7 +14033,7 @@
         <v>15</v>
       </c>
       <c r="S2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T2" t="s">
         <v>146</v>
@@ -13814,14 +14051,14 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E3">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G3">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -13867,7 +14104,7 @@
         <v>15</v>
       </c>
       <c r="S3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T3" t="s">
         <v>146</v>
@@ -13885,14 +14122,14 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E4">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G4">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -13938,7 +14175,7 @@
         <v>15</v>
       </c>
       <c r="S4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T4" t="s">
         <v>146</v>
@@ -13956,14 +14193,14 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E5">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G5">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14009,7 +14246,7 @@
         <v>15</v>
       </c>
       <c r="S5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T5" t="s">
         <v>146</v>
@@ -14027,14 +14264,14 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E6">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G6">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14080,7 +14317,7 @@
         <v>15</v>
       </c>
       <c r="S6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T6" t="s">
         <v>146</v>
@@ -14098,14 +14335,14 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E7">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G7">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14151,7 +14388,7 @@
         <v>15</v>
       </c>
       <c r="S7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T7" t="s">
         <v>146</v>
@@ -14169,13 +14406,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G8">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14221,7 +14458,7 @@
         <v>15</v>
       </c>
       <c r="S8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T8" t="s">
         <v>146</v>
@@ -14239,13 +14476,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G9">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14291,7 +14528,7 @@
         <v>15</v>
       </c>
       <c r="S9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T9" t="s">
         <v>146</v>
@@ -14309,13 +14546,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G10">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14361,7 +14598,7 @@
         <v>15</v>
       </c>
       <c r="S10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T10" t="s">
         <v>146</v>
@@ -14379,14 +14616,14 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E11" s="40">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>1</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G11">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14432,10 +14669,10 @@
         <v>22</v>
       </c>
       <c r="S11" t="s">
+        <v>191</v>
+      </c>
+      <c r="T11" t="s">
         <v>192</v>
-      </c>
-      <c r="T11" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -14450,14 +14687,14 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E12">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>1</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G12">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14503,7 +14740,7 @@
         <v>22</v>
       </c>
       <c r="S12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T12" t="s">
         <v>146</v>
@@ -14521,14 +14758,14 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E13">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>1</v>
       </c>
       <c r="F13" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G13">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14574,7 +14811,7 @@
         <v>22</v>
       </c>
       <c r="S13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T13" t="s">
         <v>146</v>
@@ -14592,14 +14829,14 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E14">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>1</v>
       </c>
       <c r="F14" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G14">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14645,7 +14882,7 @@
         <v>21</v>
       </c>
       <c r="S14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T14" t="s">
         <v>146</v>
@@ -14663,14 +14900,14 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E15">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>1</v>
       </c>
       <c r="F15" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G15">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14716,7 +14953,7 @@
         <v>21</v>
       </c>
       <c r="S15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T15" t="s">
         <v>146</v>
@@ -14734,14 +14971,14 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E16">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>1</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G16">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14787,7 +15024,7 @@
         <v>21</v>
       </c>
       <c r="S16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T16" t="s">
         <v>146</v>
@@ -14805,14 +15042,14 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E17">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>2</v>
       </c>
       <c r="F17" s="40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G17">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14858,7 +15095,7 @@
         <v>21</v>
       </c>
       <c r="S17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T17" t="s">
         <v>146</v>
@@ -14876,14 +15113,14 @@
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E18">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>2</v>
       </c>
       <c r="F18" s="40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G18">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14929,7 +15166,7 @@
         <v>22</v>
       </c>
       <c r="S18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T18" t="s">
         <v>146</v>
@@ -14947,14 +15184,14 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E19">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>2</v>
       </c>
       <c r="F19" s="40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G19">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15000,7 +15237,7 @@
         <v>20</v>
       </c>
       <c r="S19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T19" t="s">
         <v>146</v>
@@ -15018,14 +15255,14 @@
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E20">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>2</v>
       </c>
       <c r="F20" s="40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G20">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15071,7 +15308,7 @@
         <v>22</v>
       </c>
       <c r="S20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T20" t="s">
         <v>146</v>
@@ -15089,14 +15326,14 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E21">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>2</v>
       </c>
       <c r="F21" s="40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G21">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15142,7 +15379,7 @@
         <v>22</v>
       </c>
       <c r="S21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T21" t="s">
         <v>146</v>
@@ -15160,14 +15397,14 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>2</v>
       </c>
       <c r="F22" s="40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15213,7 +15450,7 @@
         <v>21</v>
       </c>
       <c r="S22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T22" t="s">
         <v>146</v>
@@ -15231,14 +15468,14 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>11</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15284,7 +15521,7 @@
         <v>15</v>
       </c>
       <c r="S23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T23" t="s">
         <v>146</v>
@@ -27200,7 +27437,7 @@
         <v>139</v>
       </c>
       <c r="C1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -27257,7 +27494,7 @@
         <v>ALTA</v>
       </c>
       <c r="J2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -27293,7 +27530,7 @@
         <v>ALTA</v>
       </c>
       <c r="J3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -27329,7 +27566,7 @@
         <v>ALTA</v>
       </c>
       <c r="J4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -27833,7 +28070,7 @@
         <v>MÉDIO</v>
       </c>
       <c r="J18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -27869,7 +28106,7 @@
         <v>MÉDIO</v>
       </c>
       <c r="J19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
@@ -27905,7 +28142,7 @@
         <v>MÉDIO</v>
       </c>
       <c r="J20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
@@ -27941,7 +28178,7 @@
         <v>MÉDIO</v>
       </c>
       <c r="J21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
@@ -35828,6 +36065,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9263e2f0-28c9-4773-a4ed-849e05f98a98">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100152AE8DDD420C04FB898D103CA4EB3CA" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="04db2ce75f02f3ad64b7aca797dc392c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9263e2f0-28c9-4773-a4ed-849e05f98a98" xmlns:ns3="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d4755cbcf05ae3986f3477a510a636" ns2:_="" ns3:_="">
     <xsd:import namespace="9263e2f0-28c9-4773-a4ed-849e05f98a98"/>
@@ -36028,27 +36285,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22229DF-FCAD-420A-8F03-88F31FF2AFD8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="97003019-d0ea-4b44-a32d-a1d0fc52ffd7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9263e2f0-28c9-4773-a4ed-849e05f98a98"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9263e2f0-28c9-4773-a4ed-849e05f98a98">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E919C03E-5A89-47CF-BA2C-50B5836FBD2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78557AB0-1243-4680-951E-A665D3F67E9D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36065,29 +36327,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E919C03E-5A89-47CF-BA2C-50B5836FBD2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22229DF-FCAD-420A-8F03-88F31FF2AFD8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="97003019-d0ea-4b44-a32d-a1d0fc52ffd7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9263e2f0-28c9-4773-a4ed-849e05f98a98"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/historico_dados/03 - Mar 2026.xlsx
+++ b/historico_dados/03 - Mar 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JFMELO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD907C2D-7D17-45D0-A506-E6F6D7882F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF6858D-64EC-463F-843B-6EFB45F406F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="2" activeTab="9" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="2" activeTab="3" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
   </bookViews>
   <sheets>
     <sheet name="TURNOS" sheetId="16" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="244">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -1057,7 +1057,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1142,22 +1142,22 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="67">
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1185,9 +1185,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1242,6 +1239,15 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="23" formatCode="h:mm\ AM/PM"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1584,10 +1590,7 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1616,14 +1619,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}" name="tblTurnos" displayName="tblTurnos" ref="A2:E5" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}" name="tblTurnos" displayName="tblTurnos" ref="A2:E5" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
   <autoFilter ref="A2:E5" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{66C8A751-944C-4ED0-9B93-7EF7890BAC2C}" name="ID_TURNO" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{CE79B6B8-84BE-42CD-8597-D513FB5454F3}" name="TURNO" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{72B36434-A91F-4B46-ABFB-CA8660948243}" name="HORARIO_INICIO" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{39895036-CC40-4170-867E-4FB900291AD1}" name="HORARIO_FIM" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{883890C6-E58B-43F9-93BF-FE0182EAC856}" name="DESCRICAO" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{66C8A751-944C-4ED0-9B93-7EF7890BAC2C}" name="ID_TURNO" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{CE79B6B8-84BE-42CD-8597-D513FB5454F3}" name="TURNO" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{72B36434-A91F-4B46-ABFB-CA8660948243}" name="HORARIO_INICIO" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{39895036-CC40-4170-867E-4FB900291AD1}" name="HORARIO_FIM" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{883890C6-E58B-43F9-93BF-FE0182EAC856}" name="DESCRICAO" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1633,13 +1636,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A986751A-B0FE-4DB2-A339-752A82C8EBB2}" name="tblNaoRegencia" displayName="tblNaoRegencia" ref="A1:G40" totalsRowShown="0">
   <autoFilter ref="A1:G40" xr:uid="{A986751A-B0FE-4DB2-A339-752A82C8EBB2}"/>
   <tableColumns count="7">
-    <tableColumn id="3" xr3:uid="{C41BC749-29FB-4B6F-9EA2-D96ADD02E462}" name="ID_INSTRUTOR" dataDxfId="5">
+    <tableColumn id="3" xr3:uid="{C41BC749-29FB-4B6F-9EA2-D96ADD02E462}" name="ID_INSTRUTOR" dataDxfId="66">
       <calculatedColumnFormula>_xlfn.XLOOKUP($B2,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{365EBB65-AF80-4E7B-89A4-79CE5F2AB432}" name="INSTRUTOR"/>
     <tableColumn id="9" xr3:uid="{D3DE3AAD-CD37-4E63-97AA-798CAE59423B}" name="DATA_INICIO"/>
     <tableColumn id="10" xr3:uid="{DC38F51D-F55B-4FCE-9DEB-F22E95157356}" name="DATA_FIM"/>
-    <tableColumn id="4" xr3:uid="{11EF8702-E803-4685-B2C8-3A78BE4767F1}" name="HORAS_NAO_REGENCIA" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{11EF8702-E803-4685-B2C8-3A78BE4767F1}" name="HORAS_NAO_REGENCIA" dataDxfId="65"/>
     <tableColumn id="5" xr3:uid="{78F32153-EFD3-4A0D-9B3E-4F5A0AC4EA03}" name="TIPO_ATIVIDADE"/>
     <tableColumn id="6" xr3:uid="{C209715A-6D68-4CB2-BE03-6EB9D41B3128}" name="DESCRICAO"/>
   </tableColumns>
@@ -1653,7 +1656,7 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{777D8F4B-4E54-4D25-85CD-95A1C29201CF}" name="ID_REGISTRO"/>
     <tableColumn id="2" xr3:uid="{1A2EBCBF-6DF1-4D28-BEBD-4DF70127CC32}" name="DATA_FALTA"/>
-    <tableColumn id="3" xr3:uid="{B600ED18-D3EA-436F-973D-8F725213B25C}" name="ID_INSTRUTOR" dataDxfId="8">
+    <tableColumn id="3" xr3:uid="{B600ED18-D3EA-436F-973D-8F725213B25C}" name="ID_INSTRUTOR" dataDxfId="6">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{D5F1B6E7-37B8-4C25-AB78-D9B4DF386F26}" name="INSTRUTOR"/>
@@ -1673,43 +1676,43 @@
   <autoFilter ref="A10:C21" xr:uid="{75F20B93-93C1-46B3-8F69-45B7FBEB31A8}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{864AACEE-78FA-40CC-AD13-56D3C344A2D4}" name="PARÂMETRO"/>
-    <tableColumn id="2" xr3:uid="{57E86055-2CCE-4631-9A08-ED866B3C8B9D}" name="VALOR" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{A0FFA1C2-5301-484A-A146-CFB1C2F7E495}" name="DESCRIÇÃO" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{57E86055-2CCE-4631-9A08-ED866B3C8B9D}" name="VALOR" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{A0FFA1C2-5301-484A-A146-CFB1C2F7E495}" name="DESCRIÇÃO" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}" name="tblModalidades" displayName="tblModalidades" ref="A2:D4" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}" name="tblModalidades" displayName="tblModalidades" ref="A2:D4" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A2:D4" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B42A8C1C-387F-4E3D-A54F-CF1D913A6676}" name="ID_MODALIDADE" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{409E0C8E-C00D-45B9-8113-E86B37049A97}" name="MODALIDADE" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{9B83D5E8-C0D6-41D3-A5EB-27263A3A1DDA}" name="TIPO" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{D7FE0EEE-44EA-4C6B-B889-B4C030F1B758}" name=" DESCRICAO" dataDxfId="50"/>
+    <tableColumn id="1" xr3:uid="{B42A8C1C-387F-4E3D-A54F-CF1D913A6676}" name="ID_MODALIDADE" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{409E0C8E-C00D-45B9-8113-E86B37049A97}" name="MODALIDADE" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{9B83D5E8-C0D6-41D3-A5EB-27263A3A1DDA}" name="TIPO" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{D7FE0EEE-44EA-4C6B-B889-B4C030F1B758}" name=" DESCRICAO" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}" name="tblCalendario" displayName="tblCalendario" ref="A1:G366" totalsRowShown="0" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}" name="tblCalendario" displayName="tblCalendario" ref="A1:G366" totalsRowShown="0" dataDxfId="50">
   <autoFilter ref="A1:G366" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F779E569-925E-439D-B1E1-8D86C934DF94}" name="DATA" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{9910EA8A-79F0-4CBA-B0EA-76C6A01D1DA2}" name="DIA_SEMANA" dataDxfId="47">
+    <tableColumn id="1" xr3:uid="{F779E569-925E-439D-B1E1-8D86C934DF94}" name="DATA" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{9910EA8A-79F0-4CBA-B0EA-76C6A01D1DA2}" name="DIA_SEMANA" dataDxfId="48">
       <calculatedColumnFormula>TEXT(A2,"dddd")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B5623804-AA40-4BA7-B2EB-75E1D43E1DDA}" name="MÊS" dataDxfId="46">
+    <tableColumn id="3" xr3:uid="{B5623804-AA40-4BA7-B2EB-75E1D43E1DDA}" name="MÊS" dataDxfId="47">
       <calculatedColumnFormula>TEXT(A2,"mmmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{353E7915-D743-4718-B4A3-CE0D53F4A516}" name="ANO" dataDxfId="45">
+    <tableColumn id="4" xr3:uid="{353E7915-D743-4718-B4A3-CE0D53F4A516}" name="ANO" dataDxfId="46">
       <calculatedColumnFormula>YEAR(A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{816AC587-9819-42DF-80FD-264F991CF8F3}" name="TIPO_DIA" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{7A6D793C-B684-4E23-A357-D584AE0AC6FD}" name="DESCRICAO" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{5B786348-03B6-441E-A7B1-194F3AA43107}" name="DIA_UTIL" dataDxfId="42">
+    <tableColumn id="5" xr3:uid="{816AC587-9819-42DF-80FD-264F991CF8F3}" name="TIPO_DIA" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{7A6D793C-B684-4E23-A357-D584AE0AC6FD}" name="DESCRICAO" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{5B786348-03B6-441E-A7B1-194F3AA43107}" name="DIA_UTIL" dataDxfId="43">
       <calculatedColumnFormula>IF(OR(E2="Feriado",E2="Recesso",B2="domingo",B2="sábado"),"NÃO","SIM")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1718,41 +1721,41 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}" name="tblInstrutores" displayName="tblInstrutores" ref="A1:I14" totalsRowShown="0" headerRowDxfId="41" dataDxfId="39" headerRowBorderDxfId="40" tableBorderDxfId="38" totalsRowBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}" name="tblInstrutores" displayName="tblInstrutores" ref="A1:I14" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
   <autoFilter ref="A1:I14" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G14">
     <sortCondition ref="B1:B14"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E0F79A67-2297-4B4A-A8E9-7102EE99B694}" name="ID" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{E0F79A67-2297-4B4A-A8E9-7102EE99B694}" name="ID" dataDxfId="37">
       <calculatedColumnFormula>IF(B2&lt;&gt;"",ROW()-1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{532A9770-E647-4D50-B202-8BBE5806648D}" name="NOME_COMPLETO" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{DD24D10E-34AA-4D8E-B5F7-9B0E7D84B23A}" name="NOME_PADRONIZADO" dataDxfId="34">
+    <tableColumn id="2" xr3:uid="{532A9770-E647-4D50-B202-8BBE5806648D}" name="NOME_COMPLETO" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{DD24D10E-34AA-4D8E-B5F7-9B0E7D84B23A}" name="NOME_PADRONIZADO" dataDxfId="35">
       <calculatedColumnFormula>UPPER(B2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0DC783F1-8A1B-443E-A9AF-DB40A28DED0F}" name="STATUS" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{8E33C3CA-EB70-43F9-B178-A5FD7FB25151}" name="TELEFONE" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{6BB804C3-6D00-4CBA-AADC-80AA2AA5F0B3}" name="EMAIL" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{066724F8-E631-4356-AF06-A44B57F600FB}" name="CARGA_HORARIA_SEMANAL" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{18D3697E-D2C6-4E06-9624-B784D6581D8D}" name="HABILITADO_EAD" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{0523A053-C6F6-4529-94E2-81C8ABD9D627}" name="OBSERVAÇÃO" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{0DC783F1-8A1B-443E-A9AF-DB40A28DED0F}" name="STATUS" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{8E33C3CA-EB70-43F9-B178-A5FD7FB25151}" name="TELEFONE" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{6BB804C3-6D00-4CBA-AADC-80AA2AA5F0B3}" name="EMAIL" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{066724F8-E631-4356-AF06-A44B57F600FB}" name="CARGA_HORARIA_SEMANAL" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{18D3697E-D2C6-4E06-9624-B784D6581D8D}" name="HABILITADO_EAD" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{0523A053-C6F6-4529-94E2-81C8ABD9D627}" name="OBSERVAÇÃO" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}" name="tblAmbientes" displayName="tblAmbientes" ref="A1:E17" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}" name="tblAmbientes" displayName="tblAmbientes" ref="A1:E17" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
   <autoFilter ref="A1:E17" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4CC770AA-6DA6-4EFC-AAF1-5A329E637763}" name="ID" dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{4CC770AA-6DA6-4EFC-AAF1-5A329E637763}" name="ID" dataDxfId="26">
       <calculatedColumnFormula>IF(B2&lt;&gt;"",ROW()-1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B3952270-EACA-4683-9C35-CB58270B3617}" name="NOME_AMBIENTE" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{1B401582-0E5F-494F-8433-828BC136B12C}" name="TIPO" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{81780B59-8350-421A-B267-D808DA35B87C}" name="CAPACIDADE" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{7A3E5A22-F966-4BA3-A1AA-3C3AF64EA9D1}" name="VIRTUAL" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{B3952270-EACA-4683-9C35-CB58270B3617}" name="NOME_AMBIENTE" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{1B401582-0E5F-494F-8433-828BC136B12C}" name="TIPO" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{81780B59-8350-421A-B267-D808DA35B87C}" name="CAPACIDADE" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{7A3E5A22-F966-4BA3-A1AA-3C3AF64EA9D1}" name="VIRTUAL" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1762,14 +1765,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{27B64AF7-6011-40DE-B8EB-AFCA2AA948F7}" name="tblDisciplinas" displayName="tblDisciplinas" ref="A2:G29" totalsRowShown="0">
   <autoFilter ref="A2:G29" xr:uid="{27B64AF7-6011-40DE-B8EB-AFCA2AA948F7}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EAB3743F-4C6C-47DC-9FAE-3B30927E6D25}" name="ID_DISCIPLINA" dataDxfId="66">
+    <tableColumn id="1" xr3:uid="{EAB3743F-4C6C-47DC-9FAE-3B30927E6D25}" name="ID_DISCIPLINA" dataDxfId="21">
       <calculatedColumnFormula>IF(E3&lt;&gt;"",ROW()-2,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{AB44C0DC-4B9E-4D40-B9CB-D5B9E3AB1664}" name="ID_TURMA" dataDxfId="65">
+    <tableColumn id="7" xr3:uid="{AB44C0DC-4B9E-4D40-B9CB-D5B9E3AB1664}" name="ID_TURMA" dataDxfId="20">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{71F544AA-7A31-4153-B640-2C9D09A01400}" name="TURMA"/>
-    <tableColumn id="10" xr3:uid="{6CF7FD1A-08A6-4FC7-8349-E61A732E9B9A}" name="NOME_TURMA" dataDxfId="64">
+    <tableColumn id="10" xr3:uid="{6CF7FD1A-08A6-4FC7-8349-E61A732E9B9A}" name="NOME_TURMA" dataDxfId="19">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{912B15BB-5B7F-4D54-B4D5-F1F5D64871C5}" name="NOME_DISCIPLINA"/>
@@ -1789,7 +1792,7 @@
     </tableColumn>
     <tableColumn id="2" xr3:uid="{9042D9C0-8F8C-48B8-A00F-4C204966A3E0}" name="CODIGO_TURMA"/>
     <tableColumn id="3" xr3:uid="{52BE2282-DBEE-432A-AC2C-DC3B0ED8155A}" name="NOME_TURMA"/>
-    <tableColumn id="5" xr3:uid="{06615BCB-121E-4F31-B9B5-41FF315BB778}" name="TURNO_ID" dataDxfId="20">
+    <tableColumn id="5" xr3:uid="{06615BCB-121E-4F31-B9B5-41FF315BB778}" name="TURNO_ID" dataDxfId="18">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblTurmas[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"EAD")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{4EBD83E6-0B0C-4F35-A90C-A43846EF4AD7}" name="TURNO"/>
@@ -1797,11 +1800,11 @@
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblTurmas[[#This Row],[MODALIDADE]],tblModalidades[MODALIDADE],tblModalidades[ID_MODALIDADE],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{45019BB0-F00A-4841-B863-EADDA64FC073}" name="MODALIDADE"/>
-    <tableColumn id="7" xr3:uid="{3D7E20E2-253B-4213-AC29-E1EE298912E2}" name="INSTRUTOR_TITULAR_ID" dataDxfId="19">
+    <tableColumn id="7" xr3:uid="{3D7E20E2-253B-4213-AC29-E1EE298912E2}" name="INSTRUTOR_TITULAR_ID" dataDxfId="17">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblTurmas[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{726835D8-8590-4D8B-97A6-670FB141BB4A}" name="INSTRUTOR"/>
-    <tableColumn id="16" xr3:uid="{52F17429-0E2C-4104-A78C-B8A56B97D414}" name="INTERVALO" dataDxfId="18"/>
+    <tableColumn id="16" xr3:uid="{52F17429-0E2C-4104-A78C-B8A56B97D414}" name="INTERVALO" dataDxfId="16"/>
     <tableColumn id="8" xr3:uid="{7B506599-94E7-4BA6-923F-386276DF3202}" name="DATA_INICIO"/>
     <tableColumn id="9" xr3:uid="{866256CA-7D34-41C1-9129-54C37C321CC0}" name="DATA_TERMINO"/>
     <tableColumn id="10" xr3:uid="{0E26EE9C-AEBF-445F-8B55-F7FADC6B5484}" name="CARGA_HORARIA_TOTAL"/>
@@ -1822,21 +1825,21 @@
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{26F01CA8-27CA-45E7-9496-4DA4C5DFB112}" name="ID_REGISTRO"/>
     <tableColumn id="2" xr3:uid="{6088C19C-60C3-49FB-8F36-E5D675187300}" name="DATA"/>
-    <tableColumn id="3" xr3:uid="{3DC9D8EE-0F77-4D9D-9274-DA5AD82CB9F9}" name="ID_TURMA" dataDxfId="17">
+    <tableColumn id="3" xr3:uid="{3DC9D8EE-0F77-4D9D-9274-DA5AD82CB9F9}" name="ID_TURMA" dataDxfId="15">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{69C05D6F-11A8-41E4-BF05-975BC4334AAB}" name="TURMA"/>
-    <tableColumn id="4" xr3:uid="{97A3E5B6-9CDC-4E51-AE20-35E2DE45AA9A}" name="ID_DISCIPLINA" dataDxfId="16">
+    <tableColumn id="4" xr3:uid="{97A3E5B6-9CDC-4E51-AE20-35E2DE45AA9A}" name="ID_DISCIPLINA" dataDxfId="14">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{8DAD9F82-DD32-4FF1-98DE-3BDCE0BEF7CE}" name="DISCIPLINA"/>
     <tableColumn id="5" xr3:uid="{36091ABA-AD8F-4375-86D2-9948DD4B8EA9}" name="ID_INSTRUTOR">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3964019F-EE8B-4430-B64E-C4B65E0A0B14}" name="Nome do Instrutor" dataDxfId="15">
+    <tableColumn id="17" xr3:uid="{3964019F-EE8B-4430-B64E-C4B65E0A0B14}" name="Nome do Instrutor" dataDxfId="13">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9E706770-192A-4CAD-A05F-050FCE1A954E}" name="ID_AMBIENTE" dataDxfId="14">
+    <tableColumn id="6" xr3:uid="{9E706770-192A-4CAD-A05F-050FCE1A954E}" name="ID_AMBIENTE" dataDxfId="12">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{41027BFC-EF08-4BA8-8911-CFB5D8B98B49}" name="AMBIENTE"/>
@@ -1852,7 +1855,7 @@
     <tableColumn id="19" xr3:uid="{5BE338C7-2CC7-4995-926D-03143942C848}" name="MODALIDADE"/>
     <tableColumn id="9" xr3:uid="{A9B3487C-55C6-4A27-BFD0-0AB086E6F16B}" name="HORA_INICIO"/>
     <tableColumn id="10" xr3:uid="{C8D6EDFC-0B0B-4FA8-8394-B10AA39F7E29}" name="HORA_FIM"/>
-    <tableColumn id="11" xr3:uid="{BA775167-444E-4E8B-B869-8FA82AF18593}" name="HORAS_AULA" dataDxfId="13">
+    <tableColumn id="11" xr3:uid="{BA775167-444E-4E8B-B869-8FA82AF18593}" name="HORAS_AULA" dataDxfId="11">
       <calculatedColumnFormula>($P2-$O2)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{1EDB8525-12A6-4FFF-8C85-2E2B0308588A}" name="ALUNOS_PRESENTES"/>
@@ -1871,20 +1874,20 @@
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5D64B531-2B5A-41D2-B091-C2501106A810}" name="DATA"/>
-    <tableColumn id="2" xr3:uid="{E9D5B192-1664-4C44-B817-5E2787B1BC2A}" name="ID_AMBIENTE" dataDxfId="12">
+    <tableColumn id="2" xr3:uid="{E9D5B192-1664-4C44-B817-5E2787B1BC2A}" name="ID_AMBIENTE" dataDxfId="10">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{9B86429E-88A3-4A51-9ADE-42121DFF9A4F}" name="AMBIENTE"/>
-    <tableColumn id="3" xr3:uid="{A6F82553-3DDB-44D4-B09C-992245966256}" name="ID_TURNO" dataDxfId="11">
+    <tableColumn id="3" xr3:uid="{A6F82553-3DDB-44D4-B09C-992245966256}" name="ID_TURNO" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{F6EE1A7F-593B-4E0D-9EB0-B6F92EECEB1A}" name="TURNO"/>
     <tableColumn id="4" xr3:uid="{1B094B40-F0E2-41B0-B80F-4FF2EF76E0D3}" name="VAGAS_OCUPADAS"/>
     <tableColumn id="5" xr3:uid="{1FD6B13D-1B7D-455A-B4FD-6C50EEF76002}" name="CAPACIDADE"/>
-    <tableColumn id="6" xr3:uid="{88504BEB-A991-46C1-882A-53CD6D3C4827}" name="PERCENTUAL_OCUPACAO" dataDxfId="10">
+    <tableColumn id="6" xr3:uid="{88504BEB-A991-46C1-882A-53CD6D3C4827}" name="PERCENTUAL_OCUPACAO" dataDxfId="8">
       <calculatedColumnFormula>$F2/$G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BA85A04D-3459-4AE3-9651-7E97C4D7BAE6}" name="STATUS_OCUPACAO" dataDxfId="9">
+    <tableColumn id="7" xr3:uid="{BA85A04D-3459-4AE3-9651-7E97C4D7BAE6}" name="STATUS_OCUPACAO" dataDxfId="7">
       <calculatedColumnFormula>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{482E2A7F-5074-4E85-B850-719BFEAA3756}" name="TIPO_AMBIENTE"/>
@@ -2344,7 +2347,7 @@
       <c r="D2" s="2">
         <v>46108</v>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="42">
         <v>8</v>
       </c>
       <c r="F2" t="s">
@@ -2365,7 +2368,7 @@
       <c r="D3" s="2">
         <v>46108</v>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="42">
         <v>50</v>
       </c>
       <c r="F3" t="s">
@@ -2386,7 +2389,7 @@
       <c r="D4" s="2">
         <v>46111</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="42">
         <v>19</v>
       </c>
       <c r="F4" t="s">
@@ -2407,7 +2410,7 @@
       <c r="D5" s="2">
         <v>46092</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="42">
         <v>2</v>
       </c>
       <c r="F5" t="s">
@@ -2428,7 +2431,7 @@
       <c r="D6" s="2">
         <v>46107</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="42">
         <v>1</v>
       </c>
       <c r="F6" t="s">
@@ -2440,238 +2443,238 @@
         <f>_xlfn.XLOOKUP($B7,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E7" s="44"/>
+      <c r="E7" s="42"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="e">
         <f>_xlfn.XLOOKUP($B8,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E8" s="44"/>
+      <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="e">
         <f>_xlfn.XLOOKUP($B9,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E9" s="44"/>
+      <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="e">
         <f>_xlfn.XLOOKUP($B10,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E10" s="44"/>
+      <c r="E10" s="42"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="e">
         <f>_xlfn.XLOOKUP($B11,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E11" s="44"/>
+      <c r="E11" s="42"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="e">
         <f>_xlfn.XLOOKUP($B12,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E12" s="44"/>
+      <c r="E12" s="42"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="e">
         <f>_xlfn.XLOOKUP($B13,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E13" s="44"/>
+      <c r="E13" s="42"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="e">
         <f>_xlfn.XLOOKUP($B14,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E14" s="44"/>
+      <c r="E14" s="42"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="e">
         <f>_xlfn.XLOOKUP($B15,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E15" s="44"/>
+      <c r="E15" s="42"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="e">
         <f>_xlfn.XLOOKUP($B16,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E16" s="44"/>
+      <c r="E16" s="42"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="e">
         <f>_xlfn.XLOOKUP($B17,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E17" s="44"/>
+      <c r="E17" s="42"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="e">
         <f>_xlfn.XLOOKUP($B18,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E18" s="44"/>
+      <c r="E18" s="42"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="e">
         <f>_xlfn.XLOOKUP($B19,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E19" s="44"/>
+      <c r="E19" s="42"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="e">
         <f>_xlfn.XLOOKUP($B20,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E20" s="44"/>
+      <c r="E20" s="42"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="e">
         <f>_xlfn.XLOOKUP($B21,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E21" s="44"/>
+      <c r="E21" s="42"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="e">
         <f>_xlfn.XLOOKUP($B22,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E22" s="44"/>
+      <c r="E22" s="42"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="e">
         <f>_xlfn.XLOOKUP($B23,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E23" s="44"/>
+      <c r="E23" s="42"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="e">
         <f>_xlfn.XLOOKUP($B24,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E24" s="44"/>
+      <c r="E24" s="42"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="e">
         <f>_xlfn.XLOOKUP($B25,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E25" s="44"/>
+      <c r="E25" s="42"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="e">
         <f>_xlfn.XLOOKUP($B26,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E26" s="44"/>
+      <c r="E26" s="42"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="e">
         <f>_xlfn.XLOOKUP($B27,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E27" s="44"/>
+      <c r="E27" s="42"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="e">
         <f>_xlfn.XLOOKUP($B28,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E28" s="44"/>
+      <c r="E28" s="42"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="e">
         <f>_xlfn.XLOOKUP($B29,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E29" s="44"/>
+      <c r="E29" s="42"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="e">
         <f>_xlfn.XLOOKUP($B30,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E30" s="44"/>
+      <c r="E30" s="42"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="e">
         <f>_xlfn.XLOOKUP($B31,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E31" s="44"/>
+      <c r="E31" s="42"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="e">
         <f>_xlfn.XLOOKUP($B32,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E32" s="44"/>
+      <c r="E32" s="42"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="e">
         <f>_xlfn.XLOOKUP($B33,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E33" s="44"/>
+      <c r="E33" s="42"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="e">
         <f>_xlfn.XLOOKUP($B34,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E34" s="44"/>
+      <c r="E34" s="42"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="e">
         <f>_xlfn.XLOOKUP($B35,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E35" s="44"/>
+      <c r="E35" s="42"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="e">
         <f>_xlfn.XLOOKUP($B36,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E36" s="44"/>
+      <c r="E36" s="42"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="e">
         <f>_xlfn.XLOOKUP($B37,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E37" s="44"/>
+      <c r="E37" s="42"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="e">
         <f>_xlfn.XLOOKUP($B38,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E38" s="44"/>
+      <c r="E38" s="42"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="e">
         <f>_xlfn.XLOOKUP($B39,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E39" s="44"/>
+      <c r="E39" s="42"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="e">
         <f>_xlfn.XLOOKUP($B40,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</f>
         <v>#N/A</v>
       </c>
-      <c r="E40" s="44"/>
+      <c r="E40" s="42"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2702,7 +2705,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684CBFF6-9D73-4BD7-B23B-101155BBD0C0}">
   <sheetPr codeName="Planilha10"/>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2716,7 +2719,7 @@
     <col min="10" max="10" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>137</v>
       </c>
@@ -2748,88 +2751,78 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="M2" s="36"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" s="2"/>
       <c r="C3" t="str">
         <f>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
         <v/>
       </c>
-      <c r="M3" s="37"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" s="2"/>
       <c r="C4" t="str">
         <f>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
         <v/>
       </c>
       <c r="H4" s="2"/>
-      <c r="M4" s="36"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="2"/>
       <c r="C5" t="str">
         <f>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
         <v/>
       </c>
       <c r="H5" s="2"/>
-      <c r="M5" s="37"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="2"/>
       <c r="C6" t="str">
         <f>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
         <v/>
       </c>
       <c r="H6" s="2"/>
-      <c r="M6" s="36"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
       <c r="C7" t="str">
         <f>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
         <v/>
       </c>
       <c r="H7" s="2"/>
-      <c r="M7" s="37"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2"/>
       <c r="C8" t="str">
         <f>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
         <v/>
       </c>
-      <c r="M8" s="36"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="2"/>
       <c r="C9" t="str">
         <f>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
         <v/>
       </c>
       <c r="H9" s="2"/>
-      <c r="M9" s="37"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B10" s="2"/>
       <c r="C10" t="str">
         <f>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
         <v/>
       </c>
       <c r="H10" s="2"/>
-      <c r="M10" s="36"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B11" s="2"/>
       <c r="C11" t="str">
         <f>_xlfn.XLOOKUP(Tabela13[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
         <v/>
       </c>
-      <c r="M11" s="37"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2851,7 +2844,7 @@
           <x14:formula1>
             <xm:f>INSTRUTORES!$A$2:$A$14</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G11 M2:M11</xm:sqref>
+          <xm:sqref>G2:G11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E08B1D67-B5D4-4029-89A4-74118992E57B}">
           <x14:formula1>
@@ -2888,7 +2881,7 @@
       </c>
       <c r="B3" s="2">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -12064,16 +12057,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:G366">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$E2="Feriado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$E2="Recesso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>OR($B2="sábado",$B2="domingo")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>$G2="SIM"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12483,9 +12476,7 @@
       <c r="H13" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="10" t="s">
-        <v>198</v>
-      </c>
+      <c r="I13" s="45"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="18">
@@ -12847,15 +12838,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.6">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -36065,26 +36056,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9263e2f0-28c9-4773-a4ed-849e05f98a98">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100152AE8DDD420C04FB898D103CA4EB3CA" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="04db2ce75f02f3ad64b7aca797dc392c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9263e2f0-28c9-4773-a4ed-849e05f98a98" xmlns:ns3="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d4755cbcf05ae3986f3477a510a636" ns2:_="" ns3:_="">
     <xsd:import namespace="9263e2f0-28c9-4773-a4ed-849e05f98a98"/>
@@ -36285,32 +36256,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22229DF-FCAD-420A-8F03-88F31FF2AFD8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="97003019-d0ea-4b44-a32d-a1d0fc52ffd7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9263e2f0-28c9-4773-a4ed-849e05f98a98"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E919C03E-5A89-47CF-BA2C-50B5836FBD2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9263e2f0-28c9-4773-a4ed-849e05f98a98">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78557AB0-1243-4680-951E-A665D3F67E9D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36327,4 +36293,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E919C03E-5A89-47CF-BA2C-50B5836FBD2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22229DF-FCAD-420A-8F03-88F31FF2AFD8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="97003019-d0ea-4b44-a32d-a1d0fc52ffd7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9263e2f0-28c9-4773-a4ed-849e05f98a98"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/historico_dados/03 - Mar 2026.xlsx
+++ b/historico_dados/03 - Mar 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JFMELO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF6858D-64EC-463F-843B-6EFB45F406F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A82A9DD-CB7C-4C40-B238-D189558633B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="2" activeTab="3" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="729" firstSheet="6" activeTab="7" xr2:uid="{BDCD7524-1CC9-4D12-94EE-1D81A0CE0740}"/>
   </bookViews>
   <sheets>
     <sheet name="TURNOS" sheetId="16" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="247">
   <si>
     <t>DESCRIÇÃO</t>
   </si>
@@ -660,9 +660,6 @@
     <t>QUA04382026U003</t>
   </si>
   <si>
-    <t>Programador Full Stack</t>
-  </si>
-  <si>
     <t>Em andamento</t>
   </si>
   <si>
@@ -670,9 +667,6 @@
   </si>
   <si>
     <t xml:space="preserve">SALA DE AULA </t>
-  </si>
-  <si>
-    <t>FÉRIAS</t>
   </si>
   <si>
     <t>CEDIDO AO MARACANÃ</t>
@@ -808,6 +802,21 @@
   </si>
   <si>
     <t>Outros</t>
+  </si>
+  <si>
+    <t>Visita</t>
+  </si>
+  <si>
+    <t>Evot Tecnologia - 10h às 12h</t>
+  </si>
+  <si>
+    <t>Reunião</t>
+  </si>
+  <si>
+    <t>Diretoria Forsea e Firjan - 10h</t>
+  </si>
+  <si>
+    <t>Programador Full Stack - PMERJ</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1066,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1150,9 +1159,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1206,6 +1212,12 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1275,6 +1287,107 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
@@ -1488,113 +1601,6 @@
       </border>
       <protection locked="0" hidden="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1619,14 +1625,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}" name="tblTurnos" displayName="tblTurnos" ref="A2:E5" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}" name="tblTurnos" displayName="tblTurnos" ref="A2:E5" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51" tableBorderDxfId="50">
   <autoFilter ref="A2:E5" xr:uid="{9CB1CAD2-0991-4AFA-A8C5-85F5500ACC1A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{66C8A751-944C-4ED0-9B93-7EF7890BAC2C}" name="ID_TURNO" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{CE79B6B8-84BE-42CD-8597-D513FB5454F3}" name="TURNO" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{72B36434-A91F-4B46-ABFB-CA8660948243}" name="HORARIO_INICIO" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{39895036-CC40-4170-867E-4FB900291AD1}" name="HORARIO_FIM" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{883890C6-E58B-43F9-93BF-FE0182EAC856}" name="DESCRICAO" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{66C8A751-944C-4ED0-9B93-7EF7890BAC2C}" name="ID_TURNO" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{CE79B6B8-84BE-42CD-8597-D513FB5454F3}" name="TURNO" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{72B36434-A91F-4B46-ABFB-CA8660948243}" name="HORARIO_INICIO" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{39895036-CC40-4170-867E-4FB900291AD1}" name="HORARIO_FIM" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{883890C6-E58B-43F9-93BF-FE0182EAC856}" name="DESCRICAO" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1636,13 +1642,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A986751A-B0FE-4DB2-A339-752A82C8EBB2}" name="tblNaoRegencia" displayName="tblNaoRegencia" ref="A1:G40" totalsRowShown="0">
   <autoFilter ref="A1:G40" xr:uid="{A986751A-B0FE-4DB2-A339-752A82C8EBB2}"/>
   <tableColumns count="7">
-    <tableColumn id="3" xr3:uid="{C41BC749-29FB-4B6F-9EA2-D96ADD02E462}" name="ID_INSTRUTOR" dataDxfId="66">
+    <tableColumn id="3" xr3:uid="{C41BC749-29FB-4B6F-9EA2-D96ADD02E462}" name="ID_INSTRUTOR" dataDxfId="8">
       <calculatedColumnFormula>_xlfn.XLOOKUP($B2,tblInstrutores[NOME_COMPLETO],tblInstrutores[ID])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{365EBB65-AF80-4E7B-89A4-79CE5F2AB432}" name="INSTRUTOR"/>
     <tableColumn id="9" xr3:uid="{D3DE3AAD-CD37-4E63-97AA-798CAE59423B}" name="DATA_INICIO"/>
     <tableColumn id="10" xr3:uid="{DC38F51D-F55B-4FCE-9DEB-F22E95157356}" name="DATA_FIM"/>
-    <tableColumn id="4" xr3:uid="{11EF8702-E803-4685-B2C8-3A78BE4767F1}" name="HORAS_NAO_REGENCIA" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{11EF8702-E803-4685-B2C8-3A78BE4767F1}" name="HORAS_NAO_REGENCIA" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{78F32153-EFD3-4A0D-9B3E-4F5A0AC4EA03}" name="TIPO_ATIVIDADE"/>
     <tableColumn id="6" xr3:uid="{C209715A-6D68-4CB2-BE03-6EB9D41B3128}" name="DESCRICAO"/>
   </tableColumns>
@@ -1684,35 +1690,35 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}" name="tblModalidades" displayName="tblModalidades" ref="A2:D4" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}" name="tblModalidades" displayName="tblModalidades" ref="A2:D4" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
   <autoFilter ref="A2:D4" xr:uid="{43641B7E-1E4B-4F99-8245-A48C23AE54BB}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B42A8C1C-387F-4E3D-A54F-CF1D913A6676}" name="ID_MODALIDADE" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{409E0C8E-C00D-45B9-8113-E86B37049A97}" name="MODALIDADE" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{9B83D5E8-C0D6-41D3-A5EB-27263A3A1DDA}" name="TIPO" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{D7FE0EEE-44EA-4C6B-B889-B4C030F1B758}" name=" DESCRICAO" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{B42A8C1C-387F-4E3D-A54F-CF1D913A6676}" name="ID_MODALIDADE" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{409E0C8E-C00D-45B9-8113-E86B37049A97}" name="MODALIDADE" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{9B83D5E8-C0D6-41D3-A5EB-27263A3A1DDA}" name="TIPO" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{D7FE0EEE-44EA-4C6B-B889-B4C030F1B758}" name=" DESCRICAO" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}" name="tblCalendario" displayName="tblCalendario" ref="A1:G366" totalsRowShown="0" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}" name="tblCalendario" displayName="tblCalendario" ref="A1:G366" totalsRowShown="0" dataDxfId="38">
   <autoFilter ref="A1:G366" xr:uid="{2AD56904-85CF-4C47-A092-1CC4D719D317}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F779E569-925E-439D-B1E1-8D86C934DF94}" name="DATA" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{9910EA8A-79F0-4CBA-B0EA-76C6A01D1DA2}" name="DIA_SEMANA" dataDxfId="48">
+    <tableColumn id="1" xr3:uid="{F779E569-925E-439D-B1E1-8D86C934DF94}" name="DATA" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{9910EA8A-79F0-4CBA-B0EA-76C6A01D1DA2}" name="DIA_SEMANA" dataDxfId="36">
       <calculatedColumnFormula>TEXT(A2,"dddd")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B5623804-AA40-4BA7-B2EB-75E1D43E1DDA}" name="MÊS" dataDxfId="47">
+    <tableColumn id="3" xr3:uid="{B5623804-AA40-4BA7-B2EB-75E1D43E1DDA}" name="MÊS" dataDxfId="35">
       <calculatedColumnFormula>TEXT(A2,"mmmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{353E7915-D743-4718-B4A3-CE0D53F4A516}" name="ANO" dataDxfId="46">
+    <tableColumn id="4" xr3:uid="{353E7915-D743-4718-B4A3-CE0D53F4A516}" name="ANO" dataDxfId="34">
       <calculatedColumnFormula>YEAR(A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{816AC587-9819-42DF-80FD-264F991CF8F3}" name="TIPO_DIA" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{7A6D793C-B684-4E23-A357-D584AE0AC6FD}" name="DESCRICAO" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{5B786348-03B6-441E-A7B1-194F3AA43107}" name="DIA_UTIL" dataDxfId="43">
+    <tableColumn id="5" xr3:uid="{816AC587-9819-42DF-80FD-264F991CF8F3}" name="TIPO_DIA" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{7A6D793C-B684-4E23-A357-D584AE0AC6FD}" name="DESCRICAO" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{5B786348-03B6-441E-A7B1-194F3AA43107}" name="DIA_UTIL" dataDxfId="31">
       <calculatedColumnFormula>IF(OR(E2="Feriado",E2="Recesso",B2="domingo",B2="sábado"),"NÃO","SIM")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1721,41 +1727,41 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}" name="tblInstrutores" displayName="tblInstrutores" ref="A1:I14" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}" name="tblInstrutores" displayName="tblInstrutores" ref="A1:I14" totalsRowShown="0" headerRowDxfId="66" dataDxfId="64" headerRowBorderDxfId="65" tableBorderDxfId="63" totalsRowBorderDxfId="62">
   <autoFilter ref="A1:I14" xr:uid="{10D39EA4-9F67-4E18-B764-60076E4485F8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G14">
     <sortCondition ref="B1:B14"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E0F79A67-2297-4B4A-A8E9-7102EE99B694}" name="ID" dataDxfId="37">
+    <tableColumn id="1" xr3:uid="{E0F79A67-2297-4B4A-A8E9-7102EE99B694}" name="ID" dataDxfId="61">
       <calculatedColumnFormula>IF(B2&lt;&gt;"",ROW()-1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{532A9770-E647-4D50-B202-8BBE5806648D}" name="NOME_COMPLETO" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{DD24D10E-34AA-4D8E-B5F7-9B0E7D84B23A}" name="NOME_PADRONIZADO" dataDxfId="35">
+    <tableColumn id="2" xr3:uid="{532A9770-E647-4D50-B202-8BBE5806648D}" name="NOME_COMPLETO" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{DD24D10E-34AA-4D8E-B5F7-9B0E7D84B23A}" name="NOME_PADRONIZADO" dataDxfId="59">
       <calculatedColumnFormula>UPPER(B2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0DC783F1-8A1B-443E-A9AF-DB40A28DED0F}" name="STATUS" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{8E33C3CA-EB70-43F9-B178-A5FD7FB25151}" name="TELEFONE" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{6BB804C3-6D00-4CBA-AADC-80AA2AA5F0B3}" name="EMAIL" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{066724F8-E631-4356-AF06-A44B57F600FB}" name="CARGA_HORARIA_SEMANAL" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{18D3697E-D2C6-4E06-9624-B784D6581D8D}" name="HABILITADO_EAD" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{0523A053-C6F6-4529-94E2-81C8ABD9D627}" name="OBSERVAÇÃO" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{0DC783F1-8A1B-443E-A9AF-DB40A28DED0F}" name="STATUS" dataDxfId="58"/>
+    <tableColumn id="9" xr3:uid="{8E33C3CA-EB70-43F9-B178-A5FD7FB25151}" name="TELEFONE" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{6BB804C3-6D00-4CBA-AADC-80AA2AA5F0B3}" name="EMAIL" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{066724F8-E631-4356-AF06-A44B57F600FB}" name="CARGA_HORARIA_SEMANAL" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{18D3697E-D2C6-4E06-9624-B784D6581D8D}" name="HABILITADO_EAD" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{0523A053-C6F6-4529-94E2-81C8ABD9D627}" name="OBSERVAÇÃO" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}" name="tblAmbientes" displayName="tblAmbientes" ref="A1:E17" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}" name="tblAmbientes" displayName="tblAmbientes" ref="A1:E17" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:E17" xr:uid="{DFA01504-D869-4496-AFB3-1B2D28A46752}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4CC770AA-6DA6-4EFC-AAF1-5A329E637763}" name="ID" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{4CC770AA-6DA6-4EFC-AAF1-5A329E637763}" name="ID" dataDxfId="28">
       <calculatedColumnFormula>IF(B2&lt;&gt;"",ROW()-1,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B3952270-EACA-4683-9C35-CB58270B3617}" name="NOME_AMBIENTE" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{1B401582-0E5F-494F-8433-828BC136B12C}" name="TIPO" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{81780B59-8350-421A-B267-D808DA35B87C}" name="CAPACIDADE" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{7A3E5A22-F966-4BA3-A1AA-3C3AF64EA9D1}" name="VIRTUAL" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{B3952270-EACA-4683-9C35-CB58270B3617}" name="NOME_AMBIENTE" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{1B401582-0E5F-494F-8433-828BC136B12C}" name="TIPO" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{81780B59-8350-421A-B267-D808DA35B87C}" name="CAPACIDADE" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{7A3E5A22-F966-4BA3-A1AA-3C3AF64EA9D1}" name="VIRTUAL" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1765,14 +1771,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{27B64AF7-6011-40DE-B8EB-AFCA2AA948F7}" name="tblDisciplinas" displayName="tblDisciplinas" ref="A2:G29" totalsRowShown="0">
   <autoFilter ref="A2:G29" xr:uid="{27B64AF7-6011-40DE-B8EB-AFCA2AA948F7}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EAB3743F-4C6C-47DC-9FAE-3B30927E6D25}" name="ID_DISCIPLINA" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{EAB3743F-4C6C-47DC-9FAE-3B30927E6D25}" name="ID_DISCIPLINA" dataDxfId="23">
       <calculatedColumnFormula>IF(E3&lt;&gt;"",ROW()-2,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{AB44C0DC-4B9E-4D40-B9CB-D5B9E3AB1664}" name="ID_TURMA" dataDxfId="20">
+    <tableColumn id="7" xr3:uid="{AB44C0DC-4B9E-4D40-B9CB-D5B9E3AB1664}" name="ID_TURMA" dataDxfId="22">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{71F544AA-7A31-4153-B640-2C9D09A01400}" name="TURMA"/>
-    <tableColumn id="10" xr3:uid="{6CF7FD1A-08A6-4FC7-8349-E61A732E9B9A}" name="NOME_TURMA" dataDxfId="19">
+    <tableColumn id="10" xr3:uid="{6CF7FD1A-08A6-4FC7-8349-E61A732E9B9A}" name="NOME_TURMA" dataDxfId="21">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{912B15BB-5B7F-4D54-B4D5-F1F5D64871C5}" name="NOME_DISCIPLINA"/>
@@ -1792,7 +1798,7 @@
     </tableColumn>
     <tableColumn id="2" xr3:uid="{9042D9C0-8F8C-48B8-A00F-4C204966A3E0}" name="CODIGO_TURMA"/>
     <tableColumn id="3" xr3:uid="{52BE2282-DBEE-432A-AC2C-DC3B0ED8155A}" name="NOME_TURMA"/>
-    <tableColumn id="5" xr3:uid="{06615BCB-121E-4F31-B9B5-41FF315BB778}" name="TURNO_ID" dataDxfId="18">
+    <tableColumn id="5" xr3:uid="{06615BCB-121E-4F31-B9B5-41FF315BB778}" name="TURNO_ID" dataDxfId="20">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblTurmas[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"EAD")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{4EBD83E6-0B0C-4F35-A90C-A43846EF4AD7}" name="TURNO"/>
@@ -1800,11 +1806,11 @@
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblTurmas[[#This Row],[MODALIDADE]],tblModalidades[MODALIDADE],tblModalidades[ID_MODALIDADE],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{45019BB0-F00A-4841-B863-EADDA64FC073}" name="MODALIDADE"/>
-    <tableColumn id="7" xr3:uid="{3D7E20E2-253B-4213-AC29-E1EE298912E2}" name="INSTRUTOR_TITULAR_ID" dataDxfId="17">
+    <tableColumn id="7" xr3:uid="{3D7E20E2-253B-4213-AC29-E1EE298912E2}" name="INSTRUTOR_TITULAR_ID" dataDxfId="19">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblTurmas[[#This Row],[INSTRUTOR]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{726835D8-8590-4D8B-97A6-670FB141BB4A}" name="INSTRUTOR"/>
-    <tableColumn id="16" xr3:uid="{52F17429-0E2C-4104-A78C-B8A56B97D414}" name="INTERVALO" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{52F17429-0E2C-4104-A78C-B8A56B97D414}" name="INTERVALO" dataDxfId="18"/>
     <tableColumn id="8" xr3:uid="{7B506599-94E7-4BA6-923F-386276DF3202}" name="DATA_INICIO"/>
     <tableColumn id="9" xr3:uid="{866256CA-7D34-41C1-9129-54C37C321CC0}" name="DATA_TERMINO"/>
     <tableColumn id="10" xr3:uid="{0E26EE9C-AEBF-445F-8B55-F7FADC6B5484}" name="CARGA_HORARIA_TOTAL"/>
@@ -1825,21 +1831,21 @@
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{26F01CA8-27CA-45E7-9496-4DA4C5DFB112}" name="ID_REGISTRO"/>
     <tableColumn id="2" xr3:uid="{6088C19C-60C3-49FB-8F36-E5D675187300}" name="DATA"/>
-    <tableColumn id="3" xr3:uid="{3DC9D8EE-0F77-4D9D-9274-DA5AD82CB9F9}" name="ID_TURMA" dataDxfId="15">
+    <tableColumn id="3" xr3:uid="{3DC9D8EE-0F77-4D9D-9274-DA5AD82CB9F9}" name="ID_TURMA" dataDxfId="17">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{69C05D6F-11A8-41E4-BF05-975BC4334AAB}" name="TURMA"/>
-    <tableColumn id="4" xr3:uid="{97A3E5B6-9CDC-4E51-AE20-35E2DE45AA9A}" name="ID_DISCIPLINA" dataDxfId="14">
+    <tableColumn id="4" xr3:uid="{97A3E5B6-9CDC-4E51-AE20-35E2DE45AA9A}" name="ID_DISCIPLINA" dataDxfId="16">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{8DAD9F82-DD32-4FF1-98DE-3BDCE0BEF7CE}" name="DISCIPLINA"/>
     <tableColumn id="5" xr3:uid="{36091ABA-AD8F-4375-86D2-9948DD4B8EA9}" name="ID_INSTRUTOR">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3964019F-EE8B-4430-B64E-C4B65E0A0B14}" name="Nome do Instrutor" dataDxfId="13">
+    <tableColumn id="17" xr3:uid="{3964019F-EE8B-4430-B64E-C4B65E0A0B14}" name="Nome do Instrutor" dataDxfId="15">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9E706770-192A-4CAD-A05F-050FCE1A954E}" name="ID_AMBIENTE" dataDxfId="12">
+    <tableColumn id="6" xr3:uid="{9E706770-192A-4CAD-A05F-050FCE1A954E}" name="ID_AMBIENTE" dataDxfId="14">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{41027BFC-EF08-4BA8-8911-CFB5D8B98B49}" name="AMBIENTE"/>
@@ -1855,7 +1861,7 @@
     <tableColumn id="19" xr3:uid="{5BE338C7-2CC7-4995-926D-03143942C848}" name="MODALIDADE"/>
     <tableColumn id="9" xr3:uid="{A9B3487C-55C6-4A27-BFD0-0AB086E6F16B}" name="HORA_INICIO"/>
     <tableColumn id="10" xr3:uid="{C8D6EDFC-0B0B-4FA8-8394-B10AA39F7E29}" name="HORA_FIM"/>
-    <tableColumn id="11" xr3:uid="{BA775167-444E-4E8B-B869-8FA82AF18593}" name="HORAS_AULA" dataDxfId="11">
+    <tableColumn id="11" xr3:uid="{BA775167-444E-4E8B-B869-8FA82AF18593}" name="HORAS_AULA" dataDxfId="13">
       <calculatedColumnFormula>($P2-$O2)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{1EDB8525-12A6-4FFF-8C85-2E2B0308588A}" name="ALUNOS_PRESENTES"/>
@@ -1874,20 +1880,20 @@
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{5D64B531-2B5A-41D2-B091-C2501106A810}" name="DATA"/>
-    <tableColumn id="2" xr3:uid="{E9D5B192-1664-4C44-B817-5E2787B1BC2A}" name="ID_AMBIENTE" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{E9D5B192-1664-4C44-B817-5E2787B1BC2A}" name="ID_AMBIENTE" dataDxfId="12">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{9B86429E-88A3-4A51-9ADE-42121DFF9A4F}" name="AMBIENTE"/>
-    <tableColumn id="3" xr3:uid="{A6F82553-3DDB-44D4-B09C-992245966256}" name="ID_TURNO" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{A6F82553-3DDB-44D4-B09C-992245966256}" name="ID_TURNO" dataDxfId="11">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{F6EE1A7F-593B-4E0D-9EB0-B6F92EECEB1A}" name="TURNO"/>
     <tableColumn id="4" xr3:uid="{1B094B40-F0E2-41B0-B80F-4FF2EF76E0D3}" name="VAGAS_OCUPADAS"/>
     <tableColumn id="5" xr3:uid="{1FD6B13D-1B7D-455A-B4FD-6C50EEF76002}" name="CAPACIDADE"/>
-    <tableColumn id="6" xr3:uid="{88504BEB-A991-46C1-882A-53CD6D3C4827}" name="PERCENTUAL_OCUPACAO" dataDxfId="8">
+    <tableColumn id="6" xr3:uid="{88504BEB-A991-46C1-882A-53CD6D3C4827}" name="PERCENTUAL_OCUPACAO" dataDxfId="10">
       <calculatedColumnFormula>$F2/$G2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{BA85A04D-3459-4AE3-9651-7E97C4D7BAE6}" name="STATUS_OCUPACAO" dataDxfId="7">
+    <tableColumn id="7" xr3:uid="{BA85A04D-3459-4AE3-9651-7E97C4D7BAE6}" name="STATUS_OCUPACAO" dataDxfId="9">
       <calculatedColumnFormula>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{482E2A7F-5074-4E85-B850-719BFEAA3756}" name="TIPO_AMBIENTE"/>
@@ -2315,13 +2321,13 @@
         <v>138</v>
       </c>
       <c r="B1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C1" t="s">
         <v>127</v>
       </c>
       <c r="D1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E1" t="s">
         <v>155</v>
@@ -2351,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2372,7 +2378,7 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2393,7 +2399,7 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -2414,7 +2420,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2435,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -2730,7 +2736,7 @@
         <v>138</v>
       </c>
       <c r="D1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E1" t="s">
         <v>121</v>
@@ -2881,7 +2887,7 @@
       </c>
       <c r="B3" s="2">
         <f ca="1">TODAY()</f>
-        <v>46113</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2969,7 +2975,7 @@
       </c>
       <c r="B15" s="4">
         <f>AVERAGEIFS(tblOcupacao[PERCENTUAL_OCUPACAO], tblOcupacao[ID_TURNO], 1)</f>
-        <v>0.77976190476190477</v>
+        <v>0.76234567901234562</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -3159,127 +3165,127 @@
         <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="37" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="36" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="37" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="36" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="37" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="36" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="37" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="36" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="37" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" s="37" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" s="37" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="37" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" s="37" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -5136,10 +5142,10 @@
         <v>2026</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="4"/>
@@ -5764,8 +5770,12 @@
         <f t="shared" si="7"/>
         <v>2026</v>
       </c>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
+      <c r="E98" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>243</v>
+      </c>
       <c r="G98" t="str">
         <f t="shared" si="4"/>
         <v>SIM</v>
@@ -5787,8 +5797,12 @@
         <f t="shared" si="7"/>
         <v>2026</v>
       </c>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
+      <c r="E99" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>245</v>
+      </c>
       <c r="G99" t="str">
         <f t="shared" si="4"/>
         <v>SIM</v>
@@ -12102,7 +12116,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C1" s="19" t="s">
         <v>50</v>
@@ -12240,9 +12254,7 @@
       <c r="H5" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>198</v>
-      </c>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="18">
@@ -12417,7 +12429,7 @@
         <v>61</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -12476,7 +12488,7 @@
       <c r="H13" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="45"/>
+      <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="18">
@@ -12839,7 +12851,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.6">
       <c r="A1" s="44" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B1" s="44"/>
       <c r="C1" s="44"/>
@@ -12857,7 +12869,7 @@
         <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
         <v>123</v>
@@ -12886,16 +12898,16 @@
       </c>
       <c r="D3" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
-        <v>Programador Full Stack</v>
+        <v>Programador Full Stack - PMERJ</v>
       </c>
       <c r="E3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F3">
         <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -12912,16 +12924,16 @@
       </c>
       <c r="D4" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
-        <v>Programador Full Stack</v>
+        <v>Programador Full Stack - PMERJ</v>
       </c>
       <c r="E4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F4">
         <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -12938,16 +12950,16 @@
       </c>
       <c r="D5" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
-        <v>Programador Full Stack</v>
+        <v>Programador Full Stack - PMERJ</v>
       </c>
       <c r="E5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F5">
         <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -12964,16 +12976,16 @@
       </c>
       <c r="D6" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
-        <v>Programador Full Stack</v>
+        <v>Programador Full Stack - PMERJ</v>
       </c>
       <c r="E6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F6">
         <v>60</v>
       </c>
       <c r="G6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -12990,16 +13002,16 @@
       </c>
       <c r="D7" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
-        <v>Programador Full Stack</v>
+        <v>Programador Full Stack - PMERJ</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F7">
         <v>60</v>
       </c>
       <c r="G7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -13016,16 +13028,16 @@
       </c>
       <c r="D8" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
-        <v>Programador Full Stack</v>
+        <v>Programador Full Stack - PMERJ</v>
       </c>
       <c r="E8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F8">
         <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -13042,16 +13054,16 @@
       </c>
       <c r="D9" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
-        <v>Programador Full Stack</v>
+        <v>Programador Full Stack - PMERJ</v>
       </c>
       <c r="E9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F9">
         <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -13068,16 +13080,16 @@
       </c>
       <c r="D10" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
-        <v>Programador Full Stack</v>
+        <v>Programador Full Stack - PMERJ</v>
       </c>
       <c r="E10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F10">
         <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -13094,16 +13106,16 @@
       </c>
       <c r="D11" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
-        <v>Programador Full Stack</v>
+        <v>Programador Full Stack - PMERJ</v>
       </c>
       <c r="E11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F11">
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -13116,20 +13128,20 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D12" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F12">
         <v>60</v>
       </c>
       <c r="G12" s="40" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -13142,20 +13154,20 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D13" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F13">
         <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -13168,20 +13180,20 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D14" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E14" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F14">
         <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -13194,20 +13206,20 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D15" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F15">
         <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -13220,20 +13232,20 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D16" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F16">
         <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -13246,20 +13258,20 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D17" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E17" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F17">
         <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -13272,20 +13284,20 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D18" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F18">
         <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -13298,20 +13310,20 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F19">
         <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -13324,20 +13336,20 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F20">
         <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -13350,20 +13362,20 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D21" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F21">
         <v>60</v>
       </c>
       <c r="G21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -13376,20 +13388,20 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F22">
         <v>60</v>
       </c>
       <c r="G22" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -13402,20 +13414,20 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F23">
         <v>60</v>
       </c>
       <c r="G23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -13428,20 +13440,20 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F24">
         <v>60</v>
       </c>
       <c r="G24" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -13454,20 +13466,20 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E25" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F25">
         <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -13480,20 +13492,20 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F26">
         <v>60</v>
       </c>
       <c r="G26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -13506,20 +13518,20 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E27" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F27">
         <v>60</v>
       </c>
       <c r="G27" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -13532,20 +13544,20 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F28">
         <v>60</v>
       </c>
       <c r="G28" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -13558,20 +13570,20 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(tblDisciplinas[[#This Row],[TURMA]], tblTurmas[CODIGO_TURMA], tblTurmas[NOME_TURMA],"")</f>
         <v>Desenvolvedor de Soluções Integradas com TI - M - TechNip</v>
       </c>
       <c r="E29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F29">
         <v>60</v>
       </c>
       <c r="G29" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -13660,10 +13672,10 @@
         <v>126</v>
       </c>
       <c r="I1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K1" t="s">
         <v>127</v>
@@ -13727,7 +13739,7 @@
         <v>364</v>
       </c>
       <c r="P2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
@@ -13739,7 +13751,7 @@
         <v>193</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="D3">
         <f>_xlfn.XLOOKUP(tblTurmas[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"EAD")</f>
@@ -13781,7 +13793,7 @@
         <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
@@ -13790,10 +13802,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D4">
         <f>_xlfn.XLOOKUP(tblTurmas[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"EAD")</f>
@@ -13835,7 +13847,7 @@
         <v>15</v>
       </c>
       <c r="P4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -13908,31 +13920,31 @@
         <v>121</v>
       </c>
       <c r="D1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E1" t="s">
         <v>134</v>
       </c>
       <c r="F1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G1" t="s">
         <v>138</v>
       </c>
       <c r="H1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I1" t="s">
         <v>139</v>
       </c>
       <c r="J1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K1" t="s">
         <v>2</v>
       </c>
       <c r="L1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M1" t="s">
         <v>14</v>
@@ -13971,14 +13983,14 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E2">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F2" s="40" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G2">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14042,14 +14054,14 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E3">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G3">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14113,14 +14125,14 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E4">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G4">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14184,14 +14196,14 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E5">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G5">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14255,14 +14267,14 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E6">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G6">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14326,14 +14338,14 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E7">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>10</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G7">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14397,13 +14409,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G8">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14467,13 +14479,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G9">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14537,13 +14549,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G10">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14597,32 +14609,32 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2">
-        <v>46091</v>
+        <v>46108</v>
       </c>
       <c r="C11">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="40">
+        <v>200</v>
+      </c>
+      <c r="E11">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="G11">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H11" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v>Deilson dos Santos de Aquino</v>
+        <v>Raphael Barreto de Oliveira</v>
       </c>
       <c r="I11">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
@@ -14647,31 +14659,31 @@
         <v>18</v>
       </c>
       <c r="O11" s="32">
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="P11" s="32">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="Q11" s="33">
         <f>($P11-$O11)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>0.23958333333333329</v>
+        <v>0.15625000000000003</v>
       </c>
       <c r="R11">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="S11" t="s">
         <v>191</v>
       </c>
       <c r="T11" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="C12">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -14680,12 +14692,12 @@
       <c r="D12" t="s">
         <v>193</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="40">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
         <v>1</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G12">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14734,15 +14746,15 @@
         <v>191</v>
       </c>
       <c r="T12" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" s="2">
-        <v>46093</v>
+        <v>46092</v>
       </c>
       <c r="C13">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -14756,7 +14768,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="40" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G13">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14810,10 +14822,10 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="C14">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -14827,7 +14839,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="40" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G14">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14870,7 +14882,7 @@
         <v>0.23958333333333329</v>
       </c>
       <c r="R14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S14" t="s">
         <v>191</v>
@@ -14881,10 +14893,10 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="C15">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -14898,7 +14910,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="40" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G15">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -14952,10 +14964,10 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="C16">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -14969,7 +14981,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G16">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15023,10 +15035,10 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="C17">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -15037,10 +15049,10 @@
       </c>
       <c r="E17">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="40" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="G17">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15094,10 +15106,10 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B18" s="2">
-        <v>46104</v>
+        <v>46100</v>
       </c>
       <c r="C18">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -15111,7 +15123,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G18">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15154,7 +15166,7 @@
         <v>0.23958333333333329</v>
       </c>
       <c r="R18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S18" t="s">
         <v>191</v>
@@ -15165,10 +15177,10 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="C19">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -15182,7 +15194,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G19">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15225,7 +15237,7 @@
         <v>0.23958333333333329</v>
       </c>
       <c r="R19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="S19" t="s">
         <v>191</v>
@@ -15236,10 +15248,10 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="C20">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -15253,7 +15265,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G20">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15296,7 +15308,7 @@
         <v>0.23958333333333329</v>
       </c>
       <c r="R20">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S20" t="s">
         <v>191</v>
@@ -15307,10 +15319,10 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="C21">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -15324,7 +15336,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G21">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15378,10 +15390,10 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="C22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
@@ -15395,7 +15407,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G22">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
@@ -15438,7 +15450,7 @@
         <v>0.23958333333333329</v>
       </c>
       <c r="R22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S22" t="s">
         <v>191</v>
@@ -15449,32 +15461,32 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="G23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H23" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v>Raphael Barreto de Oliveira</v>
+        <v>Deilson dos Santos de Aquino</v>
       </c>
       <c r="I23">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
@@ -15499,17 +15511,17 @@
         <v>18</v>
       </c>
       <c r="O23" s="32">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="P23" s="32">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="Q23" s="33">
         <f>($P23-$O23)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>0.15625000000000003</v>
+        <v>0.23958333333333329</v>
       </c>
       <c r="R23">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="S23" t="s">
         <v>191</v>
@@ -15522,270 +15534,426 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" t="str">
+      <c r="B24" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C24">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v/>
-      </c>
-      <c r="E24" t="str">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="40"/>
-      <c r="G24" t="str">
+        <v>2</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="G24">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H24" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v/>
-      </c>
-      <c r="I24" t="str">
+        <v>Deilson dos Santos de Aquino</v>
+      </c>
+      <c r="I24">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="K24" t="str">
+        <v>4</v>
+      </c>
+      <c r="J24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K24">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],['#VALOR!]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L24" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="M24" t="str">
+        <v>MANHÃ</v>
+      </c>
+      <c r="M24">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[MODALIDADE]], tblModalidades[MODALIDADE], tblModalidades[ID_MODALIDADE],"")</f>
-        <v/>
-      </c>
-      <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="N24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" s="32">
+        <v>0.375</v>
+      </c>
+      <c r="P24" s="32">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q24" s="33">
         <f>($P24-$O24)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>#VALUE!</v>
+        <v>0.23958333333333329</v>
+      </c>
+      <c r="R24">
+        <v>21</v>
+      </c>
+      <c r="S24" t="s">
+        <v>191</v>
+      </c>
+      <c r="T24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" t="str">
+      <c r="B25" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C25">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v/>
-      </c>
-      <c r="E25" t="str">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E25">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="40"/>
-      <c r="G25" t="str">
+        <v>3</v>
+      </c>
+      <c r="F25" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="G25">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H25" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v/>
-      </c>
-      <c r="I25" t="str">
+        <v>Deilson dos Santos de Aquino</v>
+      </c>
+      <c r="I25">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="K25" t="str">
+        <v>4</v>
+      </c>
+      <c r="J25" t="s">
+        <v>106</v>
+      </c>
+      <c r="K25">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],['#VALOR!]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L25" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="M25" t="str">
+        <v>MANHÃ</v>
+      </c>
+      <c r="M25">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[MODALIDADE]], tblModalidades[MODALIDADE], tblModalidades[ID_MODALIDADE],"")</f>
-        <v/>
-      </c>
-      <c r="O25" s="32"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="N25" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="32">
+        <v>0.375</v>
+      </c>
+      <c r="P25" s="32">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q25" s="33">
         <f>($P25-$O25)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>#VALUE!</v>
+        <v>0.23958333333333329</v>
+      </c>
+      <c r="R25">
+        <v>21</v>
+      </c>
+      <c r="S25" t="s">
+        <v>191</v>
+      </c>
+      <c r="T25" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" t="str">
+      <c r="B26" s="2">
+        <v>46111</v>
+      </c>
+      <c r="C26">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v/>
-      </c>
-      <c r="E26" t="str">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>200</v>
+      </c>
+      <c r="E26">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="40"/>
-      <c r="G26" t="str">
+        <v>12</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="G26">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="H26" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v/>
-      </c>
-      <c r="I26" t="str">
+        <v>Raphael Barreto de Oliveira</v>
+      </c>
+      <c r="I26">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="K26" t="str">
+        <v>8</v>
+      </c>
+      <c r="J26" t="s">
+        <v>110</v>
+      </c>
+      <c r="K26">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],['#VALOR!]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L26" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="M26" t="str">
+        <v>MANHÃ</v>
+      </c>
+      <c r="M26">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[MODALIDADE]], tblModalidades[MODALIDADE], tblModalidades[ID_MODALIDADE],"")</f>
-        <v/>
-      </c>
-      <c r="O26" s="32"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="N26" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P26" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="Q26" s="33">
         <f>($P26-$O26)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>#VALUE!</v>
+        <v>0.15625000000000003</v>
+      </c>
+      <c r="R26">
+        <v>15</v>
+      </c>
+      <c r="S26" t="s">
+        <v>191</v>
+      </c>
+      <c r="T26" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" t="str">
+      <c r="B27" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C27">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v/>
-      </c>
-      <c r="E27" t="str">
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
+        <v>200</v>
+      </c>
+      <c r="E27">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="40"/>
-      <c r="G27" t="str">
+        <v>12</v>
+      </c>
+      <c r="F27" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="G27">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="H27" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v/>
-      </c>
-      <c r="I27" t="str">
+        <v>Raphael Barreto de Oliveira</v>
+      </c>
+      <c r="I27">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="K27" t="str">
+        <v>8</v>
+      </c>
+      <c r="J27" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],['#VALOR!]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L27" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="M27" t="str">
+        <v>MANHÃ</v>
+      </c>
+      <c r="M27">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[MODALIDADE]], tblModalidades[MODALIDADE], tblModalidades[ID_MODALIDADE],"")</f>
-        <v/>
-      </c>
-      <c r="O27" s="32"/>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="N27" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P27" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="Q27" s="33">
         <f>($P27-$O27)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>#VALUE!</v>
+        <v>0.15625000000000003</v>
+      </c>
+      <c r="R27">
+        <v>15</v>
+      </c>
+      <c r="S27" t="s">
+        <v>191</v>
+      </c>
+      <c r="T27" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" t="str">
+      <c r="B28" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C28">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v/>
-      </c>
-      <c r="E28" t="str">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="40"/>
-      <c r="G28" t="str">
+        <v>12</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="G28">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="H28" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v/>
-      </c>
-      <c r="I28" t="str">
+        <v>Raphael Barreto de Oliveira</v>
+      </c>
+      <c r="I28">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="K28" t="str">
+        <v>8</v>
+      </c>
+      <c r="J28" t="s">
+        <v>110</v>
+      </c>
+      <c r="K28">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],['#VALOR!]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L28" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="M28" t="str">
+        <v>MANHÃ</v>
+      </c>
+      <c r="M28">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[MODALIDADE]], tblModalidades[MODALIDADE], tblModalidades[ID_MODALIDADE],"")</f>
-        <v/>
-      </c>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="N28" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P28" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="Q28" s="33">
         <f>($P28-$O28)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>#VALUE!</v>
+        <v>0.15625000000000003</v>
+      </c>
+      <c r="R28">
+        <v>14</v>
+      </c>
+      <c r="S28" t="s">
+        <v>191</v>
+      </c>
+      <c r="T28" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" t="str">
+      <c r="B29" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C29">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[ID_TURMA],"")</f>
-        <v/>
-      </c>
-      <c r="E29" t="str">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[DISCIPLINA]],tblDisciplinas[NOME_DISCIPLINA],tblDisciplinas[ID_DISCIPLINA],"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="40"/>
-      <c r="G29" t="str">
+        <v>12</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="G29">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[Nome do Instrutor]],tblInstrutores[NOME_COMPLETO],tblInstrutores[ID],"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="H29" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INSTRUTOR],"")</f>
-        <v/>
-      </c>
-      <c r="I29" t="str">
+        <v>Raphael Barreto de Oliveira</v>
+      </c>
+      <c r="I29">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="K29" t="str">
+        <v>8</v>
+      </c>
+      <c r="J29" t="s">
+        <v>110</v>
+      </c>
+      <c r="K29">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],['#VALOR!]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L29" t="str">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="M29" t="str">
+        <v>MANHÃ</v>
+      </c>
+      <c r="M29">
         <f>_xlfn.XLOOKUP(tblAlocacao[[#This Row],[MODALIDADE]], tblModalidades[MODALIDADE], tblModalidades[ID_MODALIDADE],"")</f>
-        <v/>
-      </c>
-      <c r="O29" s="32"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="N29" t="s">
+        <v>18</v>
+      </c>
+      <c r="O29" s="32">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P29" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="Q29" s="33">
         <f>($P29-$O29)-_xlfn.XLOOKUP(tblAlocacao[[#This Row],[TURMA]],tblTurmas[CODIGO_TURMA],tblTurmas[INTERVALO],"")</f>
-        <v>#VALUE!</v>
+        <v>0.15625000000000003</v>
+      </c>
+      <c r="R29">
+        <v>15</v>
+      </c>
+      <c r="S29" t="s">
+        <v>191</v>
+      </c>
+      <c r="T29" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.35">
@@ -27428,7 +27596,7 @@
         <v>139</v>
       </c>
       <c r="C1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -27485,7 +27653,7 @@
         <v>ALTA</v>
       </c>
       <c r="J2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -27521,7 +27689,7 @@
         <v>ALTA</v>
       </c>
       <c r="J3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -27557,7 +27725,7 @@
         <v>ALTA</v>
       </c>
       <c r="J4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -28061,7 +28229,7 @@
         <v>MÉDIO</v>
       </c>
       <c r="J18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -28097,7 +28265,7 @@
         <v>MÉDIO</v>
       </c>
       <c r="J19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
@@ -28133,7 +28301,7 @@
         <v>MÉDIO</v>
       </c>
       <c r="J20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
@@ -28169,7 +28337,7 @@
         <v>MÉDIO</v>
       </c>
       <c r="J21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
@@ -28209,120 +28377,222 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="35" t="e">
+      <c r="A23" s="2">
+        <v>46112</v>
+      </c>
+      <c r="B23">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>24</v>
+      </c>
+      <c r="H23" s="35">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I23" t="e">
-        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
-        <v>#DIV/0!</v>
+        <v>0.875</v>
+      </c>
+      <c r="I23" t="str">
+        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
+        <v>ALTA</v>
+      </c>
+      <c r="J23" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-      <c r="B24" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="35" t="e">
+      <c r="A24" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B24">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>24</v>
+      </c>
+      <c r="H24" s="35">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I24" t="e">
-        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
-        <v>#DIV/0!</v>
+        <v>0.875</v>
+      </c>
+      <c r="I24" t="str">
+        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
+        <v>ALTA</v>
+      </c>
+      <c r="J24" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="35" t="e">
+      <c r="A25" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B25">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>24</v>
+      </c>
+      <c r="H25" s="35">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I25" t="e">
-        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
-        <v>#DIV/0!</v>
+        <v>0.625</v>
+      </c>
+      <c r="I25" t="str">
+        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
+        <v>MÉDIO</v>
+      </c>
+      <c r="J25" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
-      <c r="B26" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="35" t="e">
+      <c r="A26" s="2">
+        <v>46112</v>
+      </c>
+      <c r="B26">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>24</v>
+      </c>
+      <c r="H26" s="35">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I26" t="e">
-        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
-        <v>#DIV/0!</v>
+        <v>0.625</v>
+      </c>
+      <c r="I26" t="str">
+        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
+        <v>MÉDIO</v>
+      </c>
+      <c r="J26" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="2"/>
-      <c r="B27" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="D27" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="35" t="e">
+      <c r="A27" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B27">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>24</v>
+      </c>
+      <c r="H27" s="35">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I27" t="e">
-        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
-        <v>#DIV/0!</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I27" t="str">
+        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
+        <v>MÉDIO</v>
+      </c>
+      <c r="J27" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="2"/>
-      <c r="B28" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="35" t="e">
+      <c r="A28" s="2">
+        <v>46114</v>
+      </c>
+      <c r="B28">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28">
+        <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[TURNO]],tblTurnos[TURNO],tblTurnos[ID_TURNO],"")</f>
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>24</v>
+      </c>
+      <c r="H28" s="35">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I28" t="e">
-        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+        <v>0.625</v>
+      </c>
+      <c r="I28" t="str">
+        <f>IF(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.75,"ALTA",IF(AND(tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&lt;0.74,tblOcupacao[[#This Row],[PERCENTUAL_OCUPACAO]]&gt;0.5),"MÉDIO","BAIXO"))</f>
+        <v>MÉDIO</v>
+      </c>
+      <c r="J28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" t="str">
         <f>_xlfn.XLOOKUP(tblOcupacao[[#This Row],[AMBIENTE]],tblAmbientes[NOME_AMBIENTE],tblAmbientes[ID],"")</f>
@@ -36056,6 +36326,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9263e2f0-28c9-4773-a4ed-849e05f98a98">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100152AE8DDD420C04FB898D103CA4EB3CA" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="04db2ce75f02f3ad64b7aca797dc392c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9263e2f0-28c9-4773-a4ed-849e05f98a98" xmlns:ns3="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9d4755cbcf05ae3986f3477a510a636" ns2:_="" ns3:_="">
     <xsd:import namespace="9263e2f0-28c9-4773-a4ed-849e05f98a98"/>
@@ -36256,27 +36546,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22229DF-FCAD-420A-8F03-88F31FF2AFD8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="97003019-d0ea-4b44-a32d-a1d0fc52ffd7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9263e2f0-28c9-4773-a4ed-849e05f98a98"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="97003019-d0ea-4b44-a32d-a1d0fc52ffd7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9263e2f0-28c9-4773-a4ed-849e05f98a98">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E919C03E-5A89-47CF-BA2C-50B5836FBD2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78557AB0-1243-4680-951E-A665D3F67E9D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36293,29 +36588,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E919C03E-5A89-47CF-BA2C-50B5836FBD2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22229DF-FCAD-420A-8F03-88F31FF2AFD8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="97003019-d0ea-4b44-a32d-a1d0fc52ffd7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9263e2f0-28c9-4773-a4ed-849e05f98a98"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>